--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'2. Scope and Rates'!$A$4:$AN$145</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr fullCalcOnLoad="1" iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3294" uniqueCount="1302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3307" uniqueCount="1316">
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.2 (September 2026)</t>
   </si>
@@ -3931,6 +3931,48 @@
   </si>
   <si>
     <t xml:space="preserve">Inside the alteration and basement rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.5 5.11. No source recorded in v4.5. Ext Works (added v5.3) = the NB Std rate; a ground-mount frame or car-park canopy is not included — add it under Other / specialist scope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.5 5.12. No source recorded in v4.5. Ext Works (added v5.3) = the NB Std rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB EW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB EX EW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2.3 has ≥4 M&amp;E items (M&amp;E-heavy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.3 (September 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The app reads this workbook through its v5 loader (sheets by name, columns by header text, Settings tables by ▶ marker). The v4.5 app cannot read it, so publish it only with, or after, that code change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Question numbers in the percentage rules follow the screen labels: Q2.2 = level of intervention, Q2.3 = scope of works.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">▶ range_widths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estimate range around the mid-point, by confidence grade (A–D). Low × mid = bottom, High × mid = top</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Values from the September 2026 workbook spec (illustrative) — review against real outturns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5.3 — 23 Sept 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gaps filled: Solar PV and Battery storage Ext Works rates (= NB Std); External works only pre-ticks (site clearance, surface water drainage, paving, soft landscaping, fences — the app's previous External works preset); ▶ range_widths added on '3. Settings' (illustrative); percentage rule and golden rules updated to Q2.2 = level of intervention, Q2.3 = scope.</t>
   </si>
 </sst>
 </file>
@@ -4698,7 +4740,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -4708,7 +4750,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5354,13 +5396,13 @@
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2"/>
       <c r="B90" s="3" t="s">
-        <v>125</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="2"/>
       <c r="B91" s="3" t="s">
-        <v>126</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5372,41 +5414,49 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B95" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B96" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B99" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -15504,13 +15554,13 @@
         <v>1200</v>
       </c>
       <c r="AA101" s="28" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="AB101" s="34" t="s">
         <v>83</v>
       </c>
       <c r="AC101" s="3" t="s">
-        <v>759</v>
+        <v>1302</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>641</v>
@@ -15612,13 +15662,13 @@
         <v>650</v>
       </c>
       <c r="AA102" s="28" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="AB102" s="34" t="s">
         <v>83</v>
       </c>
       <c r="AC102" s="3" t="s">
-        <v>767</v>
+        <v>1303</v>
       </c>
       <c r="AD102" s="3" t="s">
         <v>641</v>
@@ -17530,7 +17580,7 @@
         <v>872</v>
       </c>
       <c r="AE121" s="40" t="s">
-        <v>728</v>
+        <v>1304</v>
       </c>
       <c r="AF121" s="40" t="s">
         <v>192</v>
@@ -17636,7 +17686,7 @@
         <v>878</v>
       </c>
       <c r="AE122" s="3" t="s">
-        <v>270</v>
+        <v>1305</v>
       </c>
       <c r="AF122" s="3" t="s">
         <v>192</v>
@@ -18522,7 +18572,7 @@
         <v>878</v>
       </c>
       <c r="AE131" s="3" t="s">
-        <v>728</v>
+        <v>1304</v>
       </c>
       <c r="AF131" s="3" t="s">
         <v>192</v>
@@ -18840,7 +18890,7 @@
         <v>878</v>
       </c>
       <c r="AE134" s="3" t="s">
-        <v>728</v>
+        <v>1304</v>
       </c>
       <c r="AF134" s="3" t="s">
         <v>192</v>
@@ -19338,7 +19388,7 @@
         <v>872</v>
       </c>
       <c r="AE139" s="3" t="s">
-        <v>187</v>
+        <v>1040</v>
       </c>
       <c r="AF139" s="3" t="s">
         <v>192</v>
@@ -20019,7 +20069,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G189"/>
+  <dimension ref="A1:G196"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
@@ -20070,7 +20120,7 @@
         <v>997</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>500</v>
+        <v>613</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>998</v>
@@ -22078,7 +22128,7 @@
         <v>1205</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>1223</v>
+        <v>1306</v>
       </c>
       <c r="E144" s="3" t="n">
         <v>1.5</v>
@@ -22906,6 +22956,80 @@
       </c>
       <c r="E189" s="3" t="s">
         <v>1000</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="4" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+      <c r="F191" s="5"/>
+      <c r="G191" s="5"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="25" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B192" s="25" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C192" s="25" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D192" s="25" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C193" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C194" s="3" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C196" s="3" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3307" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="1327">
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.2 (September 2026)</t>
   </si>
@@ -3973,6 +3973,39 @@
   </si>
   <si>
     <t xml:space="preserve">Gaps filled: Solar PV and Battery storage Ext Works rates (= NB Std); External works only pre-ticks (site clearance, surface water drainage, paving, soft landscaping, fences — the app's previous External works preset); ▶ range_widths added on '3. Settings' (illustrative); percentage rule and golden rules updated to Q2.2 = level of intervention, Q2.3 = scope.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B,CV,WV,WS,DY,ST,WR,HR,TF,SY1,SY2,SY3,SY4,SY5,SY6,SY7,SY8,SY9,SY10,SY11,SY12,SY13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M,SK,WN,WA,BL,OL,PR,BB,LA,FY,CW,CH,L,CA,SY14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GU,RH,TN,ME,CT,BN,PO,SO,RG,SL,OX,HP,MK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EH,G,FK,KY,DD,PH,AB,IV,KW,PA,KA,ML,TD,DG,HS,ZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regional location factor by postcode area, or by district where an area is split (e.g. SY10). West Midlands is the default. South West added in v5.4 — its factors are an AI estimate, verify against BCIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South West</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BS,BA,BH,DT,EX,GL,PL,SN,SP,TA,TQ,TR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.4 (September 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5.4 — 24 Sept 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regions: South West added (BS, BA, BH, DT, EX, GL, PL, SN, SP, TA, TQ, TR — factors 0.94 / 1.00 / 0.97 are an AI estimate, verify against BCIS); missing areas added (L and CA North West, MK South East, TF West Midlands, HS and ZE Scotland); Shropshire districts SY1–SY13 West Midlands and SY14 North West, the rest of SY stays Wales. Found by the 21-report test run: Bristol, Cotswolds and Liverpool were priced at the West Midlands default.</t>
   </si>
 </sst>
 </file>
@@ -4740,7 +4773,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C99"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -4750,7 +4783,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1307</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5414,49 +5447,57 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
-        <v>1314</v>
+        <v>1325</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>1315</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B96" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B97" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
+    <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B98" s="3" t="s">
         <v>133</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B100" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -20120,7 +20161,7 @@
         <v>997</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>998</v>
@@ -20131,7 +20172,7 @@
         <v>999</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>1000</v>
+        <v>1321</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -20646,7 +20687,7 @@
         <v>1070</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1071</v>
+        <v>1320</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
@@ -20710,7 +20751,7 @@
         <v>1080</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>1081</v>
+        <v>1318</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>1.05</v>
@@ -20744,7 +20785,7 @@
         <v>1084</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>1085</v>
+        <v>1316</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0.92</v>
@@ -20795,7 +20836,7 @@
         <v>1090</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>1091</v>
+        <v>1317</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0.9</v>
@@ -20846,7 +20887,7 @@
         <v>1096</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>1097</v>
+        <v>1319</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0.93</v>
@@ -20873,6 +20914,23 @@
       </c>
       <c r="E60" s="3" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0.97</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\AppData\Local\Temp\claude\C--Users-nabil-estates-ai-tool\dabfa264-632a-467f-bca3-d20315440194\scratchpad\build\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3195DDB5-609B-44BC-95F7-77A89C0572BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C215B59C-5C55-471D-A7A4-2530608F6CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="41340" yWindow="2940" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4081" uniqueCount="1634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4084" uniqueCount="1635">
   <si>
     <t>3. Settings</t>
   </si>
@@ -4932,7 +4932,10 @@
     <t>v5.6 — 28 Sept 2026</t>
   </si>
   <si>
-    <t>Owner's review of v5.5: rates edited by the owner (roof, internal doors, toilets, fixed joinery, signage, AV, loose furniture, heating High, water, cooling, controls, lighting, fire alarm, sprinklers, solar PV); frame, upper floors and stairs no longer offered on refurbishment. Toilets: one rate for every building use (HOS and HEA variants removed). Changing Places Standard £45,000. Showers 900 / 1,400 / 2,500. Bathroom pods and bin store removed (bin store's old code 8.12 retired). Tea point renamed Staff kitchenette (non-domestic). Mezzanine offered on Fit-out, not Refurbishment.</t>
+    <t>Yes = the option chosen unless the user picks another. Building-use codes (e.g. RES STU) = the default for those uses only, ahead of Yes — Kitchens defaults to a domestic kitchen on residential and student buildings and a staff kitchenette everywhere else.</t>
+  </si>
+  <si>
+    <t>Owner's review of v5.5: rates edited by the owner (roof, internal doors, toilets, fixed joinery, signage, AV, loose furniture, heating High, water, cooling, controls, lighting, fire alarm, sprinklers, solar PV); frame, upper floors and stairs no longer offered on refurbishment. Toilets: one rate for every building use (HOS and HEA variants removed). Changing Places Standard £45,000. Showers 900 / 1,400 / 2,500. Bathroom pods and bin store removed (bin store's old code 8.12 retired). Tea point renamed Staff kitchenette (non-domestic). Mezzanine offered on Fit-out, not Refurbishment. Kitchens: staff kitchenette is the default on non-domestic buildings, domestic kitchen on residential and student (Default option now takes building-use codes).</t>
   </si>
 </sst>
 </file>
@@ -5553,7 +5556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -5915,376 +5918,385 @@
       </c>
       <c r="C43" s="33"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C44" s="33"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B45" s="17" t="s">
         <v>1594</v>
-      </c>
-      <c r="C44" s="33"/>
-    </row>
-    <row r="45" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A45" s="15" t="s">
-        <v>1595</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>1596</v>
       </c>
       <c r="C45" s="33"/>
     </row>
     <row r="46" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C46" s="33"/>
+    </row>
+    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
         <v>1597</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B47" s="17" t="s">
         <v>1598</v>
-      </c>
-      <c r="C46" s="33"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>1600</v>
       </c>
       <c r="C47" s="33"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C48" s="33"/>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C49" s="33"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B50" s="17" t="s">
         <v>1603</v>
       </c>
-      <c r="C49" s="33"/>
-    </row>
-    <row r="50" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
+      <c r="C50" s="33"/>
+    </row>
+    <row r="51" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B51" s="17" t="s">
         <v>1604</v>
-      </c>
-      <c r="C50" s="33"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
-        <v>1605</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>1606</v>
       </c>
       <c r="C51" s="33"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>46</v>
+        <v>1605</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="C52" s="33"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
-        <v>1608</v>
+        <v>46</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="C53" s="33"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A54" s="15" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C54" s="33"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B55" s="17" t="s">
         <v>1610</v>
       </c>
-      <c r="C54" s="33"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="15"/>
-      <c r="B55" s="17"/>
       <c r="C55" s="33"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="15"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="33"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="34"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="15" t="s">
+      <c r="B57" s="16"/>
+      <c r="C57" s="34"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="15" t="s">
         <v>1611</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="33">
+      <c r="B58" s="17"/>
+      <c r="C58" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O146&lt;&gt;"")*(COUNTIF('2. Rates'!O6:O146,'2. Rates'!O6:O146)&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="15" t="s">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="15" t="s">
         <v>1612</v>
       </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="33">
+      <c r="B59" s="17"/>
+      <c r="C59" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O146&lt;&gt;"")*(COUNTIF('4. Scope rules'!A91:A223,'2. Rates'!O6:O146)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="15" t="s">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="15" t="s">
         <v>1613</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="33">
+      <c r="B60" s="17"/>
+      <c r="C60" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A91:A223&lt;&gt;"")*(COUNTIF('2. Rates'!O6:O146,'4. Scope rules'!A91:A223)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="15" t="s">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="15" t="s">
         <v>1614</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="33">
+      <c r="B61" s="17"/>
+      <c r="C61" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A91:A223&lt;&gt;"")*(COUNTIF('4. Scope rules'!A6:A87,'4. Scope rules'!B91:B223)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="15" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="15" t="s">
         <v>1615</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="33">
+      <c r="B62" s="17"/>
+      <c r="C62" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O146&lt;&gt;"")*('2. Rates'!M6:M146=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="15" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="15" t="s">
         <v>1616</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="33">
+      <c r="B63" s="17"/>
+      <c r="C63" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*(ROUND('4. Scope rules'!M6:M87+'4. Scope rules'!O6:O87,4)&lt;&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="33">
+      <c r="B64" s="17"/>
+      <c r="C64" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*(COUNTIFS('4. Scope rules'!B91:B223,'4. Scope rules'!A6:A87,'4. Scope rules'!E91:E223,"Yes")=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="15" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="15" t="s">
         <v>1617</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="33">
+      <c r="B65" s="17"/>
+      <c r="C65" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*('4. Scope rules'!F6:F87="One")*(COUNTIFS('4. Scope rules'!B91:B223,'4. Scope rules'!A6:A87,'4. Scope rules'!E91:E223,"Yes")&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="15" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
         <v>1618</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="33">
+      <c r="B66" s="17"/>
+      <c r="C66" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*('4. Scope rules'!G6:G87=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="15" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="33">
+      <c r="B67" s="17"/>
+      <c r="C67" s="33">
         <f>SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!H6:H87,"NB",""),"EX",""),"RF",""),"FO",""),"EW",""),"DM",""),"OM",""),"—","")))&gt;0))+SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!I6:I87,"NB",""),"EX",""),"RF",""),"FO",""),"EW",""),"DM",""),"OM",""),"—","")))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="33">
+      <c r="B68" s="17"/>
+      <c r="C68" s="33">
         <f>SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!J6:J87,"RES",""),"STU",""),"OFF",""),"EDU",""),"HEA",""),"RET",""),"IND",""),"HOS",""),"MIX",""),"OTH",""),"ALL","")))&gt;0))+SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('2. Rates'!D6:D146,"RES",""),"STU",""),"OFF",""),"EDU",""),"HEA",""),"RET",""),"IND",""),"HOS",""),"MIX",""),"OTH",""),"ALL","")))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="33">
+      <c r="B69" s="17"/>
+      <c r="C69" s="33">
         <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*(COUNTIFS('3. Settings'!A96:A123,'3. Settings'!A96:A123,'3. Settings'!B96:B123,"ALL")=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="33">
+      <c r="B70" s="17"/>
+      <c r="C70" s="33">
         <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*('3. Settings'!C96:C123=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="15"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="33"/>
-    </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="15"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="33"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="34"/>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="15" t="s">
+      <c r="B72" s="16"/>
+      <c r="C72" s="34"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="33">
+      <c r="B73" s="17"/>
+      <c r="C73" s="33">
         <f>COUNTA('4. Scope rules'!A6:A87)</f>
         <v>82</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="15" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="15" t="s">
         <v>1619</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="33">
+      <c r="B74" s="17"/>
+      <c r="C74" s="33">
         <f>COUNTA('2. Rates'!O6:O146)</f>
         <v>133</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="15"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="33"/>
-    </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="15"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="33"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B75" s="16"/>
-      <c r="C75" s="34"/>
-    </row>
-    <row r="76" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="17" t="s">
+      <c r="B76" s="16"/>
+      <c r="C76" s="34"/>
+    </row>
+    <row r="77" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A77" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B76" s="17" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C76" s="60"/>
-    </row>
-    <row r="77" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A77" s="15" t="s">
+      <c r="B77" s="17" t="s">
+        <v>1634</v>
+      </c>
+      <c r="C77" s="60"/>
+    </row>
+    <row r="78" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A78" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B78" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C77" s="33"/>
-    </row>
-    <row r="78" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A78" s="15" t="s">
+      <c r="C78" s="33"/>
+    </row>
+    <row r="79" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A79" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B79" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C78" s="33"/>
-    </row>
-    <row r="79" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A79" s="15" t="s">
+      <c r="C79" s="33"/>
+    </row>
+    <row r="80" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A80" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B80" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C79" s="33"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="15" t="s">
+      <c r="C80" s="33"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B81" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C80" s="33"/>
-    </row>
-    <row r="81" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A81" s="15" t="s">
+      <c r="C81" s="33"/>
+    </row>
+    <row r="82" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A82" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B82" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C81" s="33"/>
-    </row>
-    <row r="82" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
+      <c r="C82" s="33"/>
+    </row>
+    <row r="83" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B83" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C82" s="33"/>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C83" s="33"/>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A84" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="33"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C84" s="33"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="15"/>
-      <c r="B85" s="17"/>
       <c r="C85" s="33"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="15"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20362,7 +20374,7 @@
         <v>274</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>66</v>
+        <v>456</v>
       </c>
       <c r="F123" s="15" t="s">
         <v>107</v>
@@ -20397,7 +20409,9 @@
       <c r="D124" s="15" t="s">
         <v>1627</v>
       </c>
-      <c r="E124" s="15"/>
+      <c r="E124" s="15" t="s">
+        <v>66</v>
+      </c>
       <c r="F124" s="15" t="s">
         <v>107</v>
       </c>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="1713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1726">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5170,6 +5170,45 @@
   </si>
   <si>
     <t>Lakeside S&amp;F tender returns (29 Sept 2026): five bids, four used (median ÷ 0.94 West Midlands factor, on 3,306 m² measured floor area). Changed, Refurb &amp; Fit-out columns only: strip-out £45 → £55; bathrooms £900 / £2,000 / £3,500 → £1,150 / £2,500 / £4,400; domestic kitchens £3,500 / £6,000 / £10,000 → £3,100 / £5,300 / £8,850; residential power (5.7b) £70 / £108 / £185 → £95 / £150 / £255. Added: residential rows (RES STU) for floor finishes (3.2c £50), ceilings (3.3b £30), data incl. TV aerial (5.14b £25) and builder's work (5.26b £27); options Roof — Loft insulation only (2.5b, £32/m² roof) and Ventilation — Extract fans only (5.3b, £19). Ratios: m2_per_dwelling 80 → 66, bathrooms_per_dwelling 1.2 → 1.0. New 'Tender check' column on '2. Rates' and price source 'Tender – Lakeside S&amp;F (Sep 2026)'. Confirmed and kept: wall finishes, water (visible fittings), fire alarm, data, fire stopping (Basic).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loft insulation only: £32 — see 2.5b. CS: £313 (bids £288–£338) per m² of roof re-covered (699 m², less than the footprint) for a flat warm-roof overlay on the kept asphalt: AVCL, 120 mm PIR, two-layer felt, insulated upstands, new copings, ballast relaid. Scaffold extra (see 2.7). Claycroft pitched re-roof £627–£704.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £40 (bids £38–£43) for insulated render to part of the façade of an occupied 4-storey building. With the brick remedials under it (see 7.1a): £81 (bids £59–£102). Scaffold extra (see 2.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £176 (bids £161–£191) for triple-glazed windows, curtain walling and doors on a whole 4-storey building (openings ≈ 13% of GIFA, ≈ £1,330/m² of opening), incl. take-out, closers, fire barriers, reveals, boards and decs (≈ 30% on top of supply and fit). At High. The low bid left out the curtain walling. Scaffold for envelope works (in the bids' prelims): £35 (bids £29–£41) per m² GIFA, extra to 2.5a, 2.6 and 2.7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £188 (bids £176–£200) for the whole M&amp;E package of an air source heat pump conversion of an occupied academic building: heat pumps replacing gas boilers, LTHW alterations, coils to 6 AHUs, radiators, BMS and ventilation (no breakdown). Std 5.1b + 5.5 = £93.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential rewire: £27 — see 5.26b. CS: £6.5 (bids £5–£8), 2.5–4.6% of M&amp;E, for a heat pump conversion (plant room, pipework and radiators).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £40 (bids £21–£60) for brick remedials before rendering: slab edges exposed, new stainless steel angles and cavity trays, remedial ties, movement joints, repointing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender check (this row's unit, on this workbook's basis. Unlabelled = Lakeside S&amp;F, Sep 2026: median of 4 bids ÷ 0.94. CS = Computer Science decarbonisation, Mar 2024: 2 bids × 1.07 ÷ 0.94)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.8 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026) converted to this workbook's basis: the median of the four credible bids (BSN, Chiel, Harrabin, William Gough with its kitchen error corrected; Watkin Jones excluded at twice the field) ÷ 0.94 West Midlands factor, per this row's unit, on 3,306 m² measured floor area (49 flats, the Warden's house and nine stair cores). Excludes the contractors' preliminaries and OH&amp;P. Lines starting 'CS:' are the Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; two bids, so the mean): tender × 1.07 (to Q3 2026) ÷ 0.94, on about 4,170 m² GIA measured from the tender plans and 699 m² of roof. Evidence only: no rate was changed for them in v5.8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5.8 — 1 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on about 4,170 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £150; a scaffold item of about £35/m² GIFA for envelope works; triple glazing priced at High.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
   </si>
 </sst>
 </file>
@@ -5790,7 +5829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C89"/>
+  <dimension ref="A1:C90"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -5801,7 +5840,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1707</v>
+        <v>1720</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -5963,12 +6002,12 @@
       </c>
       <c r="C20" s="33"/>
     </row>
-    <row r="21" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>1708</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1709</v>
+        <v>1721</v>
       </c>
       <c r="C21" s="33"/>
     </row>
@@ -6466,98 +6505,107 @@
     </row>
     <row r="79" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A79" s="17" t="s">
-        <v>1711</v>
+        <v>1722</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1712</v>
+        <v>1723</v>
       </c>
       <c r="C79" s="60"/>
     </row>
     <row r="80" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A80" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C80" s="60"/>
+    </row>
+    <row r="81" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A81" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B81" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C80" s="60"/>
-    </row>
-    <row r="81" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A81" s="15" t="s">
+      <c r="C81" s="60"/>
+    </row>
+    <row r="82" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A82" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B82" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C81" s="33"/>
-    </row>
-    <row r="82" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
+      <c r="C82" s="33"/>
+    </row>
+    <row r="83" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B83" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C82" s="33"/>
-    </row>
-    <row r="83" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
+      <c r="C83" s="33"/>
+    </row>
+    <row r="84" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A84" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B84" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C83" s="33"/>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="15" t="s">
+      <c r="C84" s="33"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C84" s="33"/>
-    </row>
-    <row r="85" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
+      <c r="C85" s="33"/>
+    </row>
+    <row r="86" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A86" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C85" s="33"/>
-    </row>
-    <row r="86" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
+      <c r="C86" s="33"/>
+    </row>
+    <row r="87" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A87" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B87" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C86" s="33"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C87" s="33"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A88" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C88" s="33"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C88" s="33"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="15"/>
-      <c r="B89" s="17"/>
       <c r="C89" s="33"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="15"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6651,7 +6699,7 @@
         <v>1623</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>1690</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -7375,7 +7423,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="102" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>1669</v>
       </c>
@@ -7422,7 +7470,7 @@
         <v>182</v>
       </c>
       <c r="Q25" s="22" t="s">
-        <v>1676</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
@@ -7468,7 +7516,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
         <v>197</v>
       </c>
@@ -7512,8 +7560,11 @@
       <c r="O27" s="24" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="Q27" s="22" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>203</v>
       </c>
@@ -7556,6 +7607,9 @@
       </c>
       <c r="O28" s="24" t="s">
         <v>193</v>
+      </c>
+      <c r="Q28" s="22" t="s">
+        <v>1715</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -9068,7 +9122,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A64" s="55" t="s">
         <v>1027</v>
       </c>
@@ -9117,6 +9171,9 @@
       <c r="O64" s="59" t="s">
         <v>376</v>
       </c>
+      <c r="Q64" s="22" t="s">
+        <v>1716</v>
+      </c>
     </row>
     <row r="65" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A65" s="55" t="s">
@@ -11713,7 +11770,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:17" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="21" t="s">
         <v>1675</v>
       </c>
@@ -11756,7 +11813,7 @@
         <v>736</v>
       </c>
       <c r="Q123" s="22" t="s">
-        <v>1688</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
@@ -11823,7 +11880,7 @@
       <c r="N125" s="26"/>
       <c r="O125" s="27"/>
     </row>
-    <row r="126" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:17" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A126" s="23" t="s">
         <v>1435</v>
       </c>
@@ -11866,6 +11923,9 @@
       <c r="N126" s="22"/>
       <c r="O126" s="24" t="s">
         <v>613</v>
+      </c>
+      <c r="Q126" s="22" t="s">
+        <v>1718</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
@@ -13041,7 +13101,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>428</v>
+        <v>1724</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -13052,7 +13112,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1705</v>
+        <v>1725</v>
       </c>
       <c r="C7" s="2"/>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1730">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5209,6 +5209,18 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £176 (bids £161–£191) for triple-glazed windows, curtain walling and doors on a whole 4-storey building (openings ≈ 13% of GIFA, ≈ £1,330/m² of opening), incl. take-out, closers, fire barriers, reveals, boards and decs (≈ 30% on top of supply and fit). At High. The low bid left out the curtain walling. Scaffold for envelope works (in the bids' prelims): £35 (bids £29–£41) per m² GIFA, extra to 2.5a, 2.6 and 2.7. Out-turn: window design development added £86k (3.3% of the contract sum) after award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £188 (bids £176–£200) for the whole M&amp;E package of an air source heat pump conversion of an occupied academic building: heat pumps replacing gas boilers, LTHW alterations, coils to 6 AHUs, radiators, BMS and ventilation (no breakdown). Std 5.1b + 5.5 = £93. Heat pumps: 3 × 118 kW (N+1, about 240 kW duty, about 58 W/m² after the fabric works), so about £1,800–2,100 per kW installed for the whole M&amp;E package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026) converted to this workbook's basis: the median of the four credible bids (BSN, Chiel, Harrabin, William Gough with its kitchen error corrected; Watkin Jones excluded at twice the field) ÷ 0.94 West Midlands factor, per this row's unit, on 3,306 m² measured floor area (49 flats, the Warden's house and nine stair cores). Excludes the contractors' preliminaries and OH&amp;P. Lines starting 'CS:' are the Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; two bids, so the mean): tender × 1.07 (to Q3 2026) ÷ 0.94, on about 4,170 m² GIA measured from the tender plans and 699 m² of roof. Evidence only: no rate was changed for them in v5.8. Final out-turn (financial statement, July 2026): construction £2.73m, +3.4% on a £2.64m contract; total project £3.13m excl. VAT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on about 4,170 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £150; a scaffold item of about £35/m² GIFA for envelope works; triple glazing priced at High. Updated 2 Oct 2026 with the final out-turn and CPW's heat pump sizes.</t>
   </si>
 </sst>
 </file>
@@ -6007,7 +6019,7 @@
         <v>1708</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="C21" s="33"/>
     </row>
@@ -6508,7 +6520,7 @@
         <v>1722</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1723</v>
+        <v>1729</v>
       </c>
       <c r="C79" s="60"/>
     </row>
@@ -7564,7 +7576,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>203</v>
       </c>
@@ -7609,7 +7621,7 @@
         <v>193</v>
       </c>
       <c r="Q28" s="22" t="s">
-        <v>1715</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -9122,7 +9134,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A64" s="55" t="s">
         <v>1027</v>
       </c>
@@ -9172,7 +9184,7 @@
         <v>376</v>
       </c>
       <c r="Q64" s="22" t="s">
-        <v>1716</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1738">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5221,6 +5221,30 @@
   </si>
   <si>
     <t xml:space="preserve">Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on about 4,170 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £150; a scaffold item of about £35/m² GIFA for envelope works; triple glazing priced at High. Updated 2 Oct 2026 with the final out-turn and CPW's heat pump sizes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £48 (bids £45–£51) for insulated render to part of the façade of an occupied 4-storey building. With the brick remedials under it (see 7.1a): £97 (bids £70–£122). Scaffold extra (see 2.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £210 (bids £192–£228) for triple-glazed windows, curtain walling and doors on a whole 4-storey building (openings ≈ 16% of GIFA, ≈ £1,330/m² of opening), incl. take-out, closers, fire barriers, reveals, boards and decs (≈ 30% on top of supply and fit). 17% above High. The low bid left out the curtain walling. Scaffold for envelope works (in the bids' prelims): £42 (bids £35–£49) per m² GIFA, extra to 2.5a, 2.6 and 2.7. Out-turn: window design development added £86k (3.3% of the contract sum) after award.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £224 (bids £210–£238) for the whole M&amp;E package of an air source heat pump conversion of an occupied academic building: heat pumps replacing gas boilers, LTHW alterations, coils to 6 AHUs, about 160 radiators, BMS and ventilation (no breakdown). Std 5.1b + 5.5 = £93. Heat pumps: 3 × 118 kW (N+1, about 240 kW duty, about 69 W/m² after the fabric works), so about £1,800–2,100 per kW installed for the whole M&amp;E package.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential rewire: £27 — see 5.26b. CS: £8 (bids £6–£10), 2.5–4.6% of M&amp;E, for a heat pump conversion (plant room, pipework and radiators).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CS: £48 (bids £25–£71) for brick remedials before rendering: slab edges exposed, new stainless steel angles and cavity trays, remedial ties, movement joints, repointing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026) converted to this workbook's basis: the median of the four credible bids (BSN, Chiel, Harrabin, William Gough with its kitchen error corrected; Watkin Jones excluded at twice the field) ÷ 0.94 West Midlands factor, per this row's unit, on 3,306 m² measured floor area (49 flats, the Warden's house and nine stair cores). Excludes the contractors' preliminaries and OH&amp;P. Lines starting 'CS:' are the Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; two bids, so the mean): tender × 1.07 (to Q3 2026) ÷ 0.94, on 3,495 m² GIA (UoW Estates CAD outlines) and 699 m² of roof. Evidence only: no rate was changed for them in v5.8. Final out-turn (financial statement, July 2026): construction £2.73m, +3.4% on a £2.64m contract; total project £3.13m excl. VAT.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on 3,495 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £150; a scaffold item of about £35/m² GIFA for envelope works; triple glazing priced at High. Updated 2 Oct 2026 with the final out-turn and CPW's heat pump sizes, and the per-m² figures recalculated on the Estates GIA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on 3,495 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs, with the final out-turn (July 2026) and CPW's heat pump sizes. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £190; a scaffold item of about £40/m² GIFA for envelope works; triple glazing about £210/m² GIFA (an option, or High).</t>
   </si>
 </sst>
 </file>
@@ -6019,7 +6043,7 @@
         <v>1708</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1728</v>
+        <v>1735</v>
       </c>
       <c r="C21" s="33"/>
     </row>
@@ -6520,7 +6544,7 @@
         <v>1722</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1729</v>
+        <v>1737</v>
       </c>
       <c r="C79" s="60"/>
     </row>
@@ -7573,7 +7597,7 @@
         <v>188</v>
       </c>
       <c r="Q27" s="22" t="s">
-        <v>1714</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="165.75" x14ac:dyDescent="0.2">
@@ -7621,7 +7645,7 @@
         <v>193</v>
       </c>
       <c r="Q28" s="22" t="s">
-        <v>1726</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -9134,7 +9158,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="127.5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A64" s="55" t="s">
         <v>1027</v>
       </c>
@@ -9184,7 +9208,7 @@
         <v>376</v>
       </c>
       <c r="Q64" s="22" t="s">
-        <v>1727</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="65" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -11825,7 +11849,7 @@
         <v>736</v>
       </c>
       <c r="Q123" s="22" t="s">
-        <v>1717</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
@@ -11937,7 +11961,7 @@
         <v>613</v>
       </c>
       <c r="Q126" s="22" t="s">
-        <v>1718</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4217" uniqueCount="1730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="1744">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5221,6 +5221,48 @@
   </si>
   <si>
     <t xml:space="preserve">Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on about 4,170 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £150; a scaffold item of about £35/m² GIFA for envelope works; triple glazing priced at High. Updated 2 Oct 2026 with the final out-turn and CPW's heat pump sizes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender check (this row's unit, on this workbook's basis. Unlabelled = Lakeside S&amp;F, Sep 2026: median of 4 bids ÷ 0.94. CS = Computer Science decarbonisation, Mar 2024: 2 bids × 1.07 ÷ 0.94. WF = Whitefields demolition, Total Reclaims contract 2026: line items × 1.014 ÷ 0.94 — the figure is also in column R)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitefields rate (£ per this row's unit, this workbook's basis: Total Reclaims contract 2026, excl. the contractor's prelims and OH&amp;P, ÷ 0.94 × 1.014. Evidence only — the app does not read it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £10.1 on the contract (Total Reclaims, £28,050 to the asbestos BoQ) over 3,000 m² GIA assumed (1,995 m² measured footprint × 1.5 storeys). Five bids on the same BoQ: £10.1–£53, median £15.8. The R&amp;D survey (£9,400) was a fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £91 per m² demolished on the contract, 3,000 m² GIA assumed (1,995 m² measured footprint × 1.5 storeys): soft strip, demolish, slabs and foundations £43; disconnecting and cutting back drainage, water, gas, electrical and telecoms, plus Trinity / Honeywell fire alarm, security and metering removal, £49. Core demolition across five bids £43–£87 (median £57). Excludes the water-main replacement (0.7) and the contractor's own £15k provisional sums for the Trinity / Honeywell work, which those quotes replace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £40 per m² footprint on the contract (1,995 m² footprint): replacing the ductile iron water main that crosses the site in MDPE, with temporary water, trenching, stone surround and tarmac reinstatement (£74k). £49 with the changes pending at FS 16, Jul 2026 (trial pits on the district heating and water mains, out-of-hours water works: £16.7k).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £2.2 per m² over the 7,715 m² red line (contract £15.4k): topsoil and grass seed to the UoW Grounds specification only — no planting or maintenance. Five bids £2.2–£11.7, median £3.4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.9 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026) converted to this workbook's basis: the median of the four credible bids (BSN, Chiel, Harrabin, William Gough with its kitchen error corrected; Watkin Jones excluded at twice the field) ÷ 0.94 West Midlands factor, per this row's unit, on 3,306 m² measured floor area (49 flats, the Warden's house and nine stair cores). Excludes the contractors' preliminaries and OH&amp;P. Lines starting 'CS:' are the Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; two bids, so the mean): tender × 1.07 (to Q3 2026) ÷ 0.94, on about 4,170 m² GIA measured from the tender plans and 699 m² of roof. Evidence only: no rate was changed for them in v5.8. Final out-turn (financial statement, July 2026): construction £2.73m, +3.4% on a £2.64m contract; total project £3.13m excl. VAT. WF lines: Whitefields demolition (17 blocks, UoW main campus), the Total Reclaims contract (tendered Feb 2026, Option 2) — the figure is also in column R, Whitefields rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whitefields rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column R on '2. Rates': the Whitefields demolition contract figure for that row (Total Reclaims, £525,676; AFC £532,445 at FS 16, Jul 2026), in the row's unit and on this workbook's basis — line items without the contractor's prelims and OH&amp;P, ÷ 0.94 West Midlands factor, × 1.014 to Q3 2026. m² GIFA and m² demolished use 3,000 m² GIA (assumed: 1,995 m² measured footprint × 1.5 storeys); m² footprint uses 1,995 m²; soft landscaping uses the 7,715 m² red line. Evidence only: the app does not read this column and no rate changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5.9 — 2 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. New column R 'Whitefields rate' on '2. Rates' and WF lines in Tender check, from the Whitefields demolition contract (Total Reclaims £525,676; AFC £532,445 at FS 16, Jul 2026; 3,000 m² GIA assumed): 0.1 asbestos £10.1/m² GIFA; 0.2 demolition incl. disconnections £91/m² demolished; 0.7 service diversions £40/m² footprint (water-main replacement); 8.10 topsoil and seed £2.2/m². Not on '2. Rates': the contractor's prelims incl. hoarding were 16.8% of works and OH&amp;P 15%; professional fees 28% of construction (ecology and environmental monitoring £67k), UoW Estates fees 4%, contingency 7%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-02</t>
   </si>
 </sst>
 </file>
@@ -5841,7 +5883,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -5852,7 +5894,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1720</v>
+        <v>1736</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -6019,13 +6061,17 @@
         <v>1708</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1728</v>
+        <v>1737</v>
       </c>
       <c r="C21" s="33"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="15"/>
-      <c r="B22" s="17"/>
+    <row r="22" spans="1:3" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="15" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>1739</v>
+      </c>
       <c r="C22" s="33"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -6515,109 +6561,118 @@
       <c r="B78" s="16"/>
       <c r="C78" s="34"/>
     </row>
-    <row r="79" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="17" t="s">
-        <v>1722</v>
+        <v>1740</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1729</v>
+        <v>1741</v>
       </c>
       <c r="C79" s="60"/>
     </row>
     <row r="80" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A80" s="17" t="s">
-        <v>1711</v>
+        <v>1722</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>1712</v>
+        <v>1729</v>
       </c>
       <c r="C80" s="60"/>
     </row>
     <row r="81" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C81" s="60"/>
+    </row>
+    <row r="82" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B82" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C81" s="60"/>
-    </row>
-    <row r="82" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A82" s="15" t="s">
+      <c r="C82" s="60"/>
+    </row>
+    <row r="83" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A83" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B83" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C82" s="33"/>
-    </row>
-    <row r="83" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
+      <c r="C83" s="33"/>
+    </row>
+    <row r="84" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A84" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B84" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C83" s="33"/>
-    </row>
-    <row r="84" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A84" s="15" t="s">
+      <c r="C84" s="33"/>
+    </row>
+    <row r="85" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A85" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C84" s="33"/>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
+      <c r="C85" s="33"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C85" s="33"/>
-    </row>
-    <row r="86" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
+      <c r="C86" s="33"/>
+    </row>
+    <row r="87" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A87" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B87" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="33"/>
-    </row>
-    <row r="87" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
+      <c r="C87" s="33"/>
+    </row>
+    <row r="88" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A88" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B88" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C87" s="33"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C88" s="33"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C89" s="33"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B90" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C89" s="33"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="15"/>
-      <c r="B90" s="17"/>
       <c r="C90" s="33"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="15"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6626,7 +6681,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61613224-FE41-4C03-8B46-4109509C3076}">
-  <dimension ref="A1:Q152"/>
+  <dimension ref="A1:R152"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="8" customWidth="1"/>
@@ -6643,7 +6698,8 @@
     <col min="15" max="15" width="11.7109375" style="8" customWidth="1"/>
     <col min="16" max="16" width="25.85546875" style="8" customWidth="1"/>
     <col min="17" max="17" width="44.7109375" style="8" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="8"/>
+    <col min="18" max="18" width="16.7109375" style="8" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.25">
@@ -6661,7 +6717,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>756</v>
       </c>
@@ -6711,7 +6767,10 @@
         <v>1623</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>1719</v>
+        <v>1730</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>1731</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -6733,7 +6792,7 @@
       <c r="N6" s="19"/>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:16" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>72</v>
       </c>
@@ -6771,8 +6830,14 @@
       <c r="O7" s="24" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="Q7" s="22" t="s">
+        <v>1732</v>
+      </c>
+      <c r="R7" s="22">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>82</v>
       </c>
@@ -6810,6 +6875,12 @@
       <c r="O8" s="24" t="s">
         <v>73</v>
       </c>
+      <c r="Q8" s="22" t="s">
+        <v>1733</v>
+      </c>
+      <c r="R8" s="22">
+        <v>91.4</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
@@ -6968,7 +7039,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>119</v>
       </c>
@@ -7003,6 +7074,12 @@
       <c r="N13" s="22"/>
       <c r="O13" s="24" t="s">
         <v>113</v>
+      </c>
+      <c r="Q13" s="22" t="s">
+        <v>1734</v>
+      </c>
+      <c r="R13" s="22">
+        <v>40.2</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -12692,7 +12769,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="145" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A145" s="21" t="s">
         <v>696</v>
       </c>
@@ -12735,6 +12812,12 @@
       </c>
       <c r="O145" s="24" t="s">
         <v>697</v>
+      </c>
+      <c r="Q145" s="22" t="s">
+        <v>1735</v>
+      </c>
+      <c r="R145" s="22">
+        <v>2.2</v>
       </c>
     </row>
     <row r="146" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -13113,7 +13196,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>1724</v>
+        <v>1742</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -13124,7 +13207,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1725</v>
+        <v>1743</v>
       </c>
       <c r="C7" s="2"/>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="1752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1782">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5287,6 +5287,96 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender check (this row's unit, on this workbook's basis. Unlabelled = Lakeside S&amp;F, Sep 2026: median of 4 bids ÷ 0.94. CS = Computer Science decarbonisation, Mar 2024: 2 bids × 1.07 ÷ 0.94. WF = Whitefields demolition, Total Reclaims contract 2026: line items × 1.014 ÷ 0.94 — the figure is also in column R. CC = Claycroft refurbishment, Morgan Sindall G4 contract May 2025: packages × 1.034 ÷ 0.94 — the figure is also in column S)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claycroft rate (£ per this row's unit, this workbook's basis: Morgan Sindall G4 contract, May 2025 — sub-contract packages excl. Morgan Sindall's prelims, risk, fee and design, × 1.034 ÷ 0.94, on 17,172 m² GIA measured. 2.10 fire stopping is the forecast out-turn (Mace Val 16, Sep 2026). Evidence only — the app does not read it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£54 (bids £36–£56) for a partial strip-out: finishes, fittings, redundant electrics and protection CC: £51.4 on the Claycroft G4 contract (Cawarden, £801,990): full strip-out of three occupied student blocks, 17,172 m² GIA. Three bids £802k–£928k.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loft insulation only: £32 — see 2.5b. CS: £313 (bids £288–£338) per m² of roof re-covered (699 m², less than the footprint) for a flat warm-roof overlay on the kept asphalt: AVCL, 120 mm PIR, two-layer felt, insulated upstands, new copings, ballast relaid. Scaffold extra (see 2.7). Claycroft pitched re-roof £627–£704. CC: £517 per m² of roof plan (5,747 m² footprint) on the G4 contract: strip concrete tiles, top-hat spacers, Euroclad secret-fix metal over-roof, hips and verges, new eaves, gutters and soffits (£596 per m of eaves), incl. Metclad's design and prelims; excl. the bay-window cladding and scaffold (scaffold £99 per m² of plan). Forecast out-turn with roof timber remedials £601. Tiled like-for-like alternative about £460 (Stage 3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£13.5 (bids £7–£32) for local fire stopping only — in line with Basic £15 CC: £96 forecast out-turn (Mace Val 16, Sep 2026; £88 if the Claycroft 2 CE replaces its provisional sum), against £22 for the £350k provisional sum in the G4 contract. By block: Claycroft 1 £53 (final); Claycroft 3 £76 (measured: about 18 seals per bed at about £42 each; access 22% of the cost); Claycroft 2 £135–£155 (under review). Excludes £1.30m of compartment-wall head remediation on Claycroft 3, which included a 16-week delay.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£72 (bids £60–£84) incl. bathroom wall cladding, kitchen tiling and full redecoration — confirms £75 CC: £99 on the G4 contract: decoration (RE Martin, £1.02m; three bids £1.02m–£1.16m), making good (£274k) and PVC hygienic wall cladding (£251k). Includes painting ceilings and doors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£51 (bids £48–£59). New build columns copied from 3.2a CC: £38 on the G4 contract: carpet and vinyl (Active, £506k; three bids £506k–£660k), Claycroft 2 corridor and lobby floors (£88k) and screed (£4.5k).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£30 (bids £21–£36). New build columns copied from 3.3a CC: £70 on the G4 contract: ceilings and partitions package (Ace, £1.10m; three bids £1.10m–£1.23m) — replacement plasterboard ceilings (two layers of fire-line board on top floors), stair soffits and some partitions, not split. Claycroft replaced its ceilings, so compare with 3.3a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£2,563 per bathroom (bids £2,322–£4,440); standard suite alone £2,460. New build columns not changed CC: £3,869 per bathroom on the G4 contract, Claycroft 1 (135 bathroom units): IPS and vanity (Inscape) plus WC, basin and bath with taps, incl. assisted-bathroom changes. Water and drainage connections are in 5.2a; PVC wall cladding is in 3.1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC: £64 on the G4 contract: joinery package (Mansard, £994k; two bids £994k–£1.04m) — bathroom joinery (boxings, bath panels, shelves) 67%, bedroom joinery (wardrobe alterations, shelving) 21%, other incl. signage 12%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC: £39 on the G4 contract: domestic hot and cold water (riser pipework and valves, bathroom connections, DHW plate heat exchangers and pumps) and drainage (bathroom connections to stacks, SVP terminations). A partial replacement, not a full installation. Sanitaryware is in 4.2a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential extract-only scope: £18.5 — see 5.3b CC: forecast out-turn £92 (Mace Val 16) for bathroom extract incl. new ductwork and roof-mounted fans added by CE in Claycroft 1 (£182k) and Claycroft 2 (£865k). The contract figure is on 5.3b.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£18.5 (bids £13–£23), incl. the electrical connection to each fan CC: £28 on the G4 contract: new branch connections, dampers and grilles to the existing bathroom extract, duct cleaning and flow checks, plus fire dampers (£124k). Forecast out-turn £92 once new ductwork and roof fans were added — see 5.3a.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC: £4.3 on the G4 contract: interfaces from the existing BEMS to the new fire alarm and DHW controls only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Power + lighting £186 (bids £157–£253) less lighting 5.8a £33 = £153; incl. landlord panels and sub-mains per block. New build columns not changed CC: £158 on the G4 contract: full rewire — LV switch panels and distribution boards (£1.10m), containment (£366k), small power (£669k), isolation and strip-out of the old installation (£158k) and earthing. Electrical total with lighting, fire alarm and data: £355.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not separable in the tender — checked together with 5.7b CC: £113 on the G4 contract for general, emergency and external lighting together (£1.66m, not split) — compare with 5.8a + 5.9 (£33 + £10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£18.6 (bids £18–£21), residential — confirms £18 CC: £65 on the G4 contract: new fire alarm throughout three blocks of student flats (£949k). Disabled refuge and assisted-WC alarms add £8.5 (not in this figure).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£24.5 incl. TV aerial system (bids £22–£39). New build columns copied from 5.14a CC: £19 on the G4 contract: voice and data (£284k); no TV aerial system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not comparable: the tender only had doorbells and door-entry infrastructure CC: £4.5 on the G4 contract: access control (£52k) and CCTV (£14k) only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC: £112,850 per lift on the G4 contract: one passenger lift removed and replaced in Claycroft 3 (Morris Vermaport, £102,588 incl. design).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£27 (bids £18–£55): chasing and making good for a full rewire of occupied flats. New build columns copied from 5.26a CC: £11 on the G4 contract: builder's work assessed by Morgan Sindall at 2.2% of M&amp;E (£172k); more builder's work is priced inside the M&amp;E lines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CC: no contract figure. The forecast out-turn (Mace Val 16) adds £2.65m of structural and fabric defect remediation, £164 on this basis — mostly a £2.14m budget for Claycroft 2, found only as each block was opened up.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.10 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026) converted to this workbook's basis: the median of the four credible bids (BSN, Chiel, Harrabin, William Gough with its kitchen error corrected; Watkin Jones excluded at twice the field) ÷ 0.94 West Midlands factor, per this row's unit, on 3,306 m² measured floor area (49 flats, the Warden's house and nine stair cores). Excludes the contractors' preliminaries and OH&amp;P. Lines starting 'CS:' are the Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; two bids, so the mean): tender × 1.07 (to Q3 2026) ÷ 0.94, on 3,495 m² GIA (UoW Estates CAD outlines) and 699 m² of roof. Evidence only: no rate was changed for them in v5.8. Final out-turn (financial statement, July 2026): construction £2.73m, +3.4% on a £2.64m contract; total project £3.13m excl. VAT. WF lines: Whitefields demolition (17 blocks, UoW main campus), the Total Reclaims contract (tendered Feb 2026, Option 2) — the figure is also in column R, Whitefields rate. CC lines: the Claycroft student residences refurbishment (679 beds, three occupied blocks, UoW main campus), Morgan Sindall G4 contract (May 2025, SCAPE) — the figure is also in column S, Claycroft rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claycroft rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column S on '2. Rates': the Claycroft student residences refurbishment figure for that row (Morgan Sindall, Tier 1, SCAPE Lot 4, NEC ECC; G4 contract £20,955,523, May 2025), in the row's unit and on this workbook's basis — sub-contract package values without Morgan Sindall's prelims, risk, fee and design, × 1.034 to Q3 2026, ÷ 0.94 West Midlands factor. m² GIFA uses 17,172 m² GIA and m² roof the 5,747 m² footprint, both measured from the UoW Estates fire plans; bathrooms use Claycroft 1 (135 bathroom units). M&amp;E rows include their share (6.5%) of the M&amp;E design, prelims and testing. 2.10 fire stopping is the forecast out-turn (Mace Val 16, Sep 2026; ÷ 0.94, not rebased), because the contract held only a £350k provisional sum. Evidence only: the app does not read this column and no rate changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5.10 — 3 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. New column S 'Claycroft rate' on '2. Rates' and CC lines in Tender check, from the Claycroft refurbishment (Morgan Sindall G4 contract £20.96m, May 2025; Mace Val 16 forecast final account £27.96m, +33%; 17,172 m² GIA measured, 679 beds): strip-out £51; metal over-roof £517/m² roof; fire stopping £96 (out-turn); wall finishes £99; floor finishes £38; ceilings £70; bathrooms £3,869 each; fixed joinery £64; water and drainage £39; extract £28; power £158; lighting incl. emergency £113; fire alarm £65; data £19; passenger lift £112,850; BWIC £11. Not on '2. Rates': scaffold £33/m² GIA; Morgan Sindall prelims 11.3% of works, fee 2.2%, risk 2.8%, design 2.1%; client risk and contingency 21.5% of contract, exceeded by the forecast growth (structural and fabric defects £2.65m, fire stopping incl. compartment-wall heads £2.63m, M&amp;E £1.40m, roof £0.55m).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-03</t>
   </si>
 </sst>
 </file>
@@ -5907,7 +5997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C91"/>
+  <dimension ref="A1:C93"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -5918,7 +6008,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1744</v>
+        <v>1774</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -6080,12 +6170,12 @@
       </c>
       <c r="C20" s="33"/>
     </row>
-    <row r="21" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="142.25" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>1708</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1745</v>
+        <v>1775</v>
       </c>
       <c r="C21" s="33"/>
     </row>
@@ -6098,605 +6188,623 @@
       </c>
       <c r="C22" s="33"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+    <row r="23" spans="1:3" ht="91.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="15" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C23" s="33"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="13" t="s">
         <v>1568</v>
       </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="34"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="15" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C24" s="33"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="34"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>1098</v>
+        <v>1076</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="C25" s="33"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="C26" s="33"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>1179</v>
+        <v>1118</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="C27" s="33"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="C28" s="33"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C29" s="33"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="15" t="s">
         <v>1637</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B30" s="17" t="s">
         <v>1710</v>
       </c>
-      <c r="C29" s="33"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="15"/>
-      <c r="B30" s="17"/>
       <c r="C30" s="33"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="15"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="33"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="34"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="15" t="s">
-        <v>1574</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C32" s="33"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="34"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
-        <v>8</v>
+        <v>1574</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="C33" s="33"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>1577</v>
+        <v>8</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="C34" s="33"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
-        <v>1579</v>
-      </c>
-      <c r="B35" s="32" t="s">
-        <v>1580</v>
+        <v>1577</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>1578</v>
       </c>
       <c r="C35" s="33"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="B36" s="32" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="C36" s="33"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>1583</v>
+        <v>1581</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>1582</v>
       </c>
       <c r="C37" s="33"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C38" s="33"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B39" s="17" t="s">
         <v>1584</v>
       </c>
-      <c r="C38" s="33"/>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="15"/>
-      <c r="B39" s="17"/>
       <c r="C39" s="33"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="15"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="33"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="13" t="s">
         <v>1585</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="34"/>
-    </row>
-    <row r="41" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A41" s="15" t="s">
-        <v>1586</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>1587</v>
-      </c>
-      <c r="C41" s="33"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="34"/>
     </row>
     <row r="42" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C42" s="33"/>
+    </row>
+    <row r="43" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="15" t="s">
         <v>1588</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B43" s="17" t="s">
         <v>3</v>
-      </c>
-      <c r="C42" s="33"/>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="15" t="s">
-        <v>1589</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>1590</v>
       </c>
       <c r="C43" s="33"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="C44" s="33"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C45" s="33"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B46" s="17" t="s">
         <v>1593</v>
       </c>
-      <c r="C45" s="33"/>
-    </row>
-    <row r="46" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A46" s="15" t="s">
+      <c r="C46" s="33"/>
+    </row>
+    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B47" s="17" t="s">
         <v>1633</v>
       </c>
-      <c r="C46" s="33"/>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+      <c r="C47" s="33"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B48" s="17" t="s">
         <v>1594</v>
-      </c>
-      <c r="C47" s="33"/>
-    </row>
-    <row r="48" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
-        <v>1595</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>1596</v>
       </c>
       <c r="C48" s="33"/>
     </row>
     <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C49" s="33"/>
+    </row>
+    <row r="50" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A50" s="15" t="s">
         <v>1597</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B50" s="17" t="s">
         <v>1598</v>
-      </c>
-      <c r="C49" s="33"/>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="15" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>1600</v>
       </c>
       <c r="C50" s="33"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C51" s="33"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C52" s="33"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B53" s="17" t="s">
         <v>1603</v>
       </c>
-      <c r="C52" s="33"/>
-    </row>
-    <row r="53" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
+      <c r="C53" s="33"/>
+    </row>
+    <row r="54" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A54" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B54" s="17" t="s">
         <v>1604</v>
-      </c>
-      <c r="C53" s="33"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="15" t="s">
-        <v>1605</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>1606</v>
       </c>
       <c r="C54" s="33"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
-        <v>46</v>
+        <v>1605</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="C55" s="33"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>1608</v>
+        <v>46</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="C56" s="33"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C57" s="33"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B58" s="17" t="s">
         <v>1610</v>
       </c>
-      <c r="C57" s="33"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="15"/>
-      <c r="B58" s="17"/>
       <c r="C58" s="33"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="15"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="33"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="34"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="15" t="s">
+      <c r="B60" s="16"/>
+      <c r="C60" s="34"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="15" t="s">
         <v>1611</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="33">
+      <c r="B61" s="17"/>
+      <c r="C61" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O152&lt;&gt;"")*(COUNTIF('2. Rates'!O6:O152,'2. Rates'!O6:O152)&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="15" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="15" t="s">
         <v>1612</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="33">
+      <c r="B62" s="17"/>
+      <c r="C62" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O152&lt;&gt;"")*(COUNTIF('4. Scope rules'!A91:A229,'2. Rates'!O6:O152)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="15" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="15" t="s">
         <v>1613</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="33">
+      <c r="B63" s="17"/>
+      <c r="C63" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A91:A229&lt;&gt;"")*(COUNTIF('2. Rates'!O6:O152,'4. Scope rules'!A91:A229)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
         <v>1614</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="33">
+      <c r="B64" s="17"/>
+      <c r="C64" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A91:A229&lt;&gt;"")*(COUNTIF('4. Scope rules'!A6:A87,'4. Scope rules'!B91:B229)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="15" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="15" t="s">
         <v>1615</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="33">
+      <c r="B65" s="17"/>
+      <c r="C65" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O152&lt;&gt;"")*('2. Rates'!M6:M152=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="15" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
         <v>1616</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="33">
+      <c r="B66" s="17"/>
+      <c r="C66" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*(ROUND('4. Scope rules'!M6:M87+'4. Scope rules'!O6:O87,4)&lt;&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="15" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="33">
+      <c r="B67" s="17"/>
+      <c r="C67" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*(COUNTIFS('4. Scope rules'!B91:B229,'4. Scope rules'!A6:A87,'4. Scope rules'!E91:E229,"Yes")=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="15" t="s">
         <v>1617</v>
       </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="33">
+      <c r="B68" s="17"/>
+      <c r="C68" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*('4. Scope rules'!F6:F87="One")*(COUNTIFS('4. Scope rules'!B91:B229,'4. Scope rules'!A6:A87,'4. Scope rules'!E91:E229,"Yes")&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="15" t="s">
         <v>1618</v>
       </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="33">
+      <c r="B69" s="17"/>
+      <c r="C69" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*('4. Scope rules'!G6:G87=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="33">
+      <c r="B70" s="17"/>
+      <c r="C70" s="33">
         <f>SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!H6:H87,"NB",""),"EX",""),"RF",""),"FO",""),"EW",""),"DM",""),"OM",""),"—","")))&gt;0))+SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!I6:I87,"NB",""),"EX",""),"RF",""),"FO",""),"EW",""),"DM",""),"OM",""),"—","")))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="33">
+      <c r="B71" s="17"/>
+      <c r="C71" s="33">
         <f>SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!J6:J87,"RES",""),"STU",""),"OFF",""),"EDU",""),"HEA",""),"RET",""),"IND",""),"HOS",""),"MIX",""),"OTH",""),"ALL","")))&gt;0))+SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('2. Rates'!D6:D152,"RES",""),"STU",""),"OFF",""),"EDU",""),"HEA",""),"RET",""),"IND",""),"HOS",""),"MIX",""),"OTH",""),"ALL","")))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="15" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="33">
+      <c r="B72" s="17"/>
+      <c r="C72" s="33">
         <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*(COUNTIFS('3. Settings'!A96:A123,'3. Settings'!A96:A123,'3. Settings'!B96:B123,"ALL")=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="15" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="33">
+      <c r="B73" s="17"/>
+      <c r="C73" s="33">
         <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*('3. Settings'!C96:C123=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="15"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="33"/>
-    </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="15"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="33"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B74" s="16"/>
-      <c r="C74" s="34"/>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="15" t="s">
+      <c r="B75" s="16"/>
+      <c r="C75" s="34"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="33">
+      <c r="B76" s="17"/>
+      <c r="C76" s="33">
         <f>COUNTA('4. Scope rules'!A6:A87)</f>
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="15" t="s">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="15" t="s">
         <v>1619</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="33">
+      <c r="B77" s="17"/>
+      <c r="C77" s="33">
         <f>COUNTA('2. Rates'!O6:O152)</f>
         <v>139</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="15"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="33"/>
-    </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="15"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="33"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="16"/>
-      <c r="C78" s="34"/>
-    </row>
-    <row r="79" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="17" t="s">
+      <c r="B79" s="16"/>
+      <c r="C79" s="34"/>
+    </row>
+    <row r="80" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="17" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>1779</v>
+      </c>
+      <c r="C80" s="60"/>
+    </row>
+    <row r="81" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B81" s="17" t="s">
         <v>1749</v>
-      </c>
-      <c r="C79" s="60"/>
-    </row>
-    <row r="80" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A80" s="17" t="s">
-        <v>1722</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C80" s="60"/>
-    </row>
-    <row r="81" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A81" s="17" t="s">
-        <v>1711</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>1712</v>
       </c>
       <c r="C81" s="60"/>
     </row>
     <row r="82" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A82" s="17" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C82" s="60"/>
+    </row>
+    <row r="83" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C83" s="60"/>
+    </row>
+    <row r="84" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A84" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B84" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C82" s="60"/>
-    </row>
-    <row r="83" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A83" s="15" t="s">
+      <c r="C84" s="60"/>
+    </row>
+    <row r="85" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A85" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C83" s="33"/>
-    </row>
-    <row r="84" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A84" s="15" t="s">
+      <c r="C85" s="33"/>
+    </row>
+    <row r="86" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A86" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>1061</v>
-      </c>
-      <c r="C84" s="33"/>
-    </row>
-    <row r="85" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C85" s="33"/>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B86" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="C86" s="33"/>
     </row>
     <row r="87" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A87" s="15" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B87" s="17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C87" s="33"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" s="33"/>
+    </row>
+    <row r="89" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A89" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C87" s="33"/>
-    </row>
-    <row r="88" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
+      <c r="C89" s="33"/>
+    </row>
+    <row r="90" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A90" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B90" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C88" s="33"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
+      <c r="C90" s="33"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C89" s="33"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
+      <c r="C91" s="33"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C90" s="33"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="15"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="33"/>
+      <c r="C92" s="33"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="15"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6705,7 +6813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61613224-FE41-4C03-8B46-4109509C3076}">
-  <dimension ref="A1:R152"/>
+  <dimension ref="A1:S152"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="8" customWidth="1"/>
@@ -6723,7 +6831,8 @@
     <col min="16" max="16" width="25.85546875" style="8" customWidth="1"/>
     <col min="17" max="17" width="44.7109375" style="8" customWidth="1"/>
     <col min="18" max="18" width="16.7109375" style="8" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="8"/>
+    <col min="19" max="19" width="16.7109375" style="8" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.25">
@@ -6741,7 +6850,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>756</v>
       </c>
@@ -6791,10 +6900,13 @@
         <v>1623</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>1738</v>
+        <v>1752</v>
       </c>
       <c r="R5" s="12" t="s">
         <v>1739</v>
+      </c>
+      <c r="S5" s="12" t="s">
+        <v>1753</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -6906,7 +7018,7 @@
         <v>91.4</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>96</v>
       </c>
@@ -6945,7 +7057,10 @@
         <v>83</v>
       </c>
       <c r="Q9" s="22" t="s">
-        <v>1665</v>
+        <v>1754</v>
+      </c>
+      <c r="S9" s="22">
+        <v>51.4</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
@@ -7536,7 +7651,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:19" ht="218.75" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>1669</v>
       </c>
@@ -7583,7 +7698,10 @@
         <v>182</v>
       </c>
       <c r="Q25" s="22" t="s">
-        <v>1713</v>
+        <v>1755</v>
+      </c>
+      <c r="S25" s="22">
+        <v>516.9</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
@@ -7815,7 +7933,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:19" ht="155.0" x14ac:dyDescent="0.2">
       <c r="A31" s="21" t="s">
         <v>1146</v>
       </c>
@@ -7858,7 +7976,10 @@
         <v>209</v>
       </c>
       <c r="Q31" s="22" t="s">
-        <v>1677</v>
+        <v>1756</v>
+      </c>
+      <c r="S31" s="22">
+        <v>95.8</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
@@ -7880,7 +8001,7 @@
       <c r="N32" s="26"/>
       <c r="O32" s="27"/>
     </row>
-    <row r="33" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>221</v>
       </c>
@@ -7925,7 +8046,10 @@
         <v>216</v>
       </c>
       <c r="Q33" s="22" t="s">
-        <v>1678</v>
+        <v>1757</v>
+      </c>
+      <c r="S33" s="22">
+        <v>99.3</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
@@ -8025,7 +8149,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A36" s="23" t="s">
         <v>1655</v>
       </c>
@@ -8071,7 +8195,10 @@
       </c>
       <c r="P36"/>
       <c r="Q36" s="22" t="s">
-        <v>1658</v>
+        <v>1758</v>
+      </c>
+      <c r="S36" s="22">
+        <v>38.4</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
@@ -8122,7 +8249,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19" ht="104.0" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>1650</v>
       </c>
@@ -8166,7 +8293,10 @@
       </c>
       <c r="P38"/>
       <c r="Q38" s="22" t="s">
-        <v>1654</v>
+        <v>1759</v>
+      </c>
+      <c r="S38" s="22">
+        <v>70.4</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
@@ -8324,7 +8454,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19" ht="104.0" x14ac:dyDescent="0.2">
       <c r="A43" s="48" t="s">
         <v>1175</v>
       </c>
@@ -8370,8 +8500,11 @@
       <c r="O43" s="52" t="s">
         <v>257</v>
       </c>
-      <c r="Q43" s="49" t="s">
-        <v>1666</v>
+      <c r="Q43" s="22" t="s">
+        <v>1760</v>
+      </c>
+      <c r="S43" s="22">
+        <v>3869</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
@@ -8563,7 +8696,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A48" s="21" t="s">
         <v>292</v>
       </c>
@@ -8606,6 +8739,12 @@
       </c>
       <c r="O48" s="24" t="s">
         <v>281</v>
+      </c>
+      <c r="Q48" s="22" t="s">
+        <v>1761</v>
+      </c>
+      <c r="S48" s="22">
+        <v>63.7</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
@@ -9938,7 +10077,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:19" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A78" s="23" t="s">
         <v>1299</v>
       </c>
@@ -9983,6 +10122,12 @@
       </c>
       <c r="O78" s="24" t="s">
         <v>415</v>
+      </c>
+      <c r="Q78" s="22" t="s">
+        <v>1762</v>
+      </c>
+      <c r="S78" s="22">
+        <v>38.9</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
@@ -10038,7 +10183,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:19" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
         <v>1672</v>
       </c>
@@ -10085,10 +10230,10 @@
         <v>424</v>
       </c>
       <c r="Q80" s="22" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>1644</v>
       </c>
@@ -10132,7 +10277,10 @@
       </c>
       <c r="P81"/>
       <c r="Q81" s="22" t="s">
-        <v>1649</v>
+        <v>1764</v>
+      </c>
+      <c r="S81" s="22">
+        <v>28.2</v>
       </c>
     </row>
     <row r="82" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -10180,7 +10328,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="83" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:19" ht="40.25" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
         <v>373</v>
       </c>
@@ -10224,6 +10372,12 @@
       <c r="O83" s="24" t="s">
         <v>433</v>
       </c>
+      <c r="Q83" s="22" t="s">
+        <v>1765</v>
+      </c>
+      <c r="S83" s="22">
+        <v>4.3</v>
+      </c>
     </row>
     <row r="84" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="55" t="s">
@@ -10393,7 +10547,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" ht="116.75" x14ac:dyDescent="0.2">
       <c r="A88" s="23" t="s">
         <v>1332</v>
       </c>
@@ -10440,7 +10594,10 @@
         <v>455</v>
       </c>
       <c r="Q88" s="22" t="s">
-        <v>1668</v>
+        <v>1766</v>
+      </c>
+      <c r="S88" s="22">
+        <v>157.7</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -10486,7 +10643,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A90" s="23" t="s">
         <v>1338</v>
       </c>
@@ -10533,7 +10690,10 @@
         <v>461</v>
       </c>
       <c r="Q90" s="22" t="s">
-        <v>1683</v>
+        <v>1767</v>
+      </c>
+      <c r="S90" s="22">
+        <v>113.2</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -10868,7 +11028,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
         <v>507</v>
       </c>
@@ -10913,7 +11073,10 @@
         <v>496</v>
       </c>
       <c r="Q99" s="22" t="s">
-        <v>1685</v>
+        <v>1768</v>
+      </c>
+      <c r="S99" s="22">
+        <v>64.7</v>
       </c>
     </row>
     <row r="100" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -11050,7 +11213,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" ht="53.0" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
         <v>1640</v>
       </c>
@@ -11094,10 +11257,13 @@
       </c>
       <c r="P103"/>
       <c r="Q103" s="22" t="s">
-        <v>1643</v>
-      </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+        <v>1769</v>
+      </c>
+      <c r="S103" s="22">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2" ht="53.0" customHeight="1">
       <c r="A104" s="21" t="s">
         <v>563</v>
       </c>
@@ -11142,10 +11308,13 @@
         <v>524</v>
       </c>
       <c r="Q104" s="22" t="s">
-        <v>1687</v>
-      </c>
-    </row>
-    <row r="105" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+        <v>1770</v>
+      </c>
+      <c r="S104" s="22">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" ht="53.0" x14ac:dyDescent="0.2">
       <c r="A105" s="23" t="s">
         <v>1381</v>
       </c>
@@ -11190,6 +11359,12 @@
       </c>
       <c r="O105" s="24" t="s">
         <v>529</v>
+      </c>
+      <c r="Q105" s="22" t="s">
+        <v>1771</v>
+      </c>
+      <c r="S105" s="22">
+        <v>112847</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -11929,7 +12104,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:19" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A124" s="21" t="s">
         <v>1635</v>
       </c>
@@ -11971,7 +12146,10 @@
       </c>
       <c r="P124"/>
       <c r="Q124" s="22" t="s">
-        <v>1639</v>
+        <v>1772</v>
+      </c>
+      <c r="S124" s="22">
+        <v>11.0</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
@@ -12091,7 +12269,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A128" s="23" t="s">
         <v>1443</v>
       </c>
@@ -12139,6 +12317,9 @@
       <c r="N128" s="22"/>
       <c r="O128" s="24" t="s">
         <v>625</v>
+      </c>
+      <c r="Q128" s="22" t="s">
+        <v>1773</v>
       </c>
     </row>
     <row r="129" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
@@ -13220,7 +13401,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>1750</v>
+        <v>1780</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -13231,7 +13412,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1751</v>
+        <v>1781</v>
       </c>
       <c r="C7" s="2"/>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="1752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4226" uniqueCount="1758">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5287,6 +5287,24 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £8.1 on the contract (Total Reclaims, £28,050 to the asbestos BoQ) over 3,740 m² GIA (17 blocks × about 220 m², owner's figures). Five bids on the same BoQ: £8.1–£42.5, median £12.7. Mace's pre-tender allowance was £85,000 (£24.5). The R&amp;D survey (£9,400) was a fee.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £73 per m² demolished on the contract, 3,740 m² GIA (17 blocks × about 220 m², owner's figures): soft strip, demolish, slabs and foundations £34; disconnecting and cutting back drainage, water, gas, electrical and telecoms, plus Trinity / Honeywell fire alarm, security and metering removal, £39. Core demolition across five bids £34–£70 (median £46). About £15k per block. Excludes the water-main replacement (0.7) and the contractor's own £15k provisional sums for the Trinity / Honeywell work, which those quotes replace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £36 per m² footprint on the contract (17 × about 130 m² = 2,210 m² footprint): replacing 254 m of ductile iron water main across the site in MDPE, with temporary water, trenching, stone surround and tarmac reinstatement (£74k; about £315/m of main). £44 with the changes pending at FS 16, Jul 2026 (trial pits on the district heating and water mains, out-of-hours water works: £16.7k).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WF: £2.1 per m² over the 8,000 m² site (contract £15.4k): topsoil and grass seed to the UoW Grounds specification only — no planting or maintenance. Five bids £2.1–£11.2, median £3.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column R on '2. Rates': the Whitefields demolition contract figure for that row (Total Reclaims, £525,676; AFC £532,445 at FS 16, Jul 2026), in the row's unit and on this workbook's basis — line items without the contractor's prelims and OH&amp;P, ÷ 0.94 West Midlands factor, × 1.014 to Q3 2026. Quantities from the owner: 17 blocks, 3,740 m² GIA (about 220 m² each over ground and first floors), 2,210 m² footprint (about 130 m² each), 8,000 m² site. Evidence only: the app does not read this column and no rate changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. New column R 'Whitefields rate' on '2. Rates' and WF lines in Tender check, from the Whitefields demolition contract (Total Reclaims £525,676; AFC £532,445 at FS 16, Jul 2026; 3,740 m² GIA, 2,210 m² footprint, 8,000 m² site): 0.1 asbestos £8.1/m² GIFA; 0.2 demolition incl. disconnections £73/m² demolished; 0.7 service diversions £36/m² footprint (254 m water-main replacement); 8.10 topsoil and seed £2.1/m². Not on '2. Rates': the contractor's prelims incl. hoarding were 16.8% of works and OH&amp;P 15%; professional fees 28% of construction (asbestos surveys £43k, ecology £33k), UoW Estates fees 4%, contingency 7%; construction 15–16 weeks on site.</t>
   </si>
 </sst>
 </file>
@@ -6094,7 +6112,7 @@
         <v>1746</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1747</v>
+        <v>1756</v>
       </c>
       <c r="C22" s="33"/>
     </row>
@@ -6590,7 +6608,7 @@
         <v>1748</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>1749</v>
+        <v>1757</v>
       </c>
       <c r="C79" s="60"/>
     </row>
@@ -6855,10 +6873,10 @@
         <v>58</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>1740</v>
+        <v>1752</v>
       </c>
       <c r="R7" s="22">
-        <v>10.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="38.25" x14ac:dyDescent="0.2">
@@ -6900,10 +6918,10 @@
         <v>73</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>1741</v>
+        <v>1753</v>
       </c>
       <c r="R8" s="22">
-        <v>91.4</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
@@ -7100,10 +7118,10 @@
         <v>113</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>1742</v>
+        <v>1754</v>
       </c>
       <c r="R13" s="22">
-        <v>40.2</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -12838,10 +12856,10 @@
         <v>697</v>
       </c>
       <c r="Q145" s="22" t="s">
-        <v>1743</v>
+        <v>1755</v>
       </c>
       <c r="R145" s="22">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="146" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1790">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5395,6 +5395,12 @@
   </si>
   <si>
     <t xml:space="preserve">WF: £2.1 per m² over the 8,000 m² site (contract £15.4k): topsoil and grass seed to the UoW Grounds specification only — no planting or maintenance. Five bids £2.1–£11.2, median £3.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.11 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-04</t>
   </si>
 </sst>
 </file>
@@ -6015,7 +6021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -6026,7 +6032,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1774</v>
+        <v>1788</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -6216,613 +6222,637 @@
       <c r="C23" s="33"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Project rate columns (T–Z)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Columns T–Y on '2. Rates' hold the other real projects' figures in the row's unit and on this workbook's basis, beside Whitefields (R) and Claycroft (S): T Lakeside S&amp;F (tender Sep 2026, median of 4 bids); U Computer Science decarbonisation (tender Mar 2024, mean of 2 bids); V Scarman Public Toilets Phase 2 (HIGH spec, tender Apr 2026, median of 6 bids; per m² over the 71 m² toilet area); W Co-op grocery store fit-out (Kingfisher contract Aug 2025, 885 m²); X IBRB café servery (Senevo winning bid 2025, 72 m² café, 28 m² servery); Y Riley Court Psychology full refurbishment (Maris signed contract £9.15m, GMP Nov 2024, GIFA 3,850 m²). Each excludes the contractor's prelims, OH&amp;P and design, rebased to Q3 2026 and ÷ 0.94 West Midlands. Column Z is the average of R–Y for the row. Projects differ in scope and specification, so expect spread. Not on '2. Rates': scaffold for envelope works £42 (CS) and £33 (Claycroft) per m² GIFA; retail refrigeration £379 and retailer equipment £373 per m² (Co-op); preliminaries Lakeside ~9%, Whitefields 16.8%, Claycroft 11.3%, Scarman 14%, Co-op 7.2%, IBRB 17.7%, Riley Court 5.5% (+4% contractor PM and design). Evidence only: the app does not read these columns and no rate changed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="13" t="s">
         <v>1568</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="34"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="15" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C25" s="33"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="34"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>1098</v>
+        <v>1076</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="C26" s="33"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>1118</v>
+        <v>1098</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="C27" s="33"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
-        <v>1179</v>
+        <v>1118</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="C28" s="33"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
-        <v>1174</v>
+        <v>1179</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="C29" s="33"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>1573</v>
+      </c>
+      <c r="C30" s="33"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
         <v>1637</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B31" s="17" t="s">
         <v>1710</v>
       </c>
-      <c r="C30" s="33"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="15"/>
-      <c r="B31" s="17"/>
       <c r="C31" s="33"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="15"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="33"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="34"/>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="15" t="s">
-        <v>1574</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>1575</v>
-      </c>
-      <c r="C33" s="33"/>
+      <c r="B33" s="16"/>
+      <c r="C33" s="34"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>8</v>
+        <v>1574</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="C34" s="33"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
-        <v>1577</v>
+        <v>8</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="C35" s="33"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
-        <v>1579</v>
-      </c>
-      <c r="B36" s="32" t="s">
-        <v>1580</v>
+        <v>1577</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>1578</v>
       </c>
       <c r="C36" s="33"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="C37" s="33"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>1583</v>
+        <v>1581</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>1582</v>
       </c>
       <c r="C38" s="33"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>1583</v>
+      </c>
+      <c r="C39" s="33"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B40" s="17" t="s">
         <v>1584</v>
       </c>
-      <c r="C39" s="33"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="15"/>
-      <c r="B40" s="17"/>
       <c r="C40" s="33"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="15"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="33"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="13" t="s">
         <v>1585</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="34"/>
-    </row>
-    <row r="42" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A42" s="15" t="s">
-        <v>1586</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>1587</v>
-      </c>
-      <c r="C42" s="33"/>
+      <c r="B42" s="16"/>
+      <c r="C42" s="34"/>
     </row>
     <row r="43" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>1587</v>
+      </c>
+      <c r="C43" s="33"/>
+    </row>
+    <row r="44" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A44" s="15" t="s">
         <v>1588</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B44" s="17" t="s">
         <v>3</v>
-      </c>
-      <c r="C43" s="33"/>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="15" t="s">
-        <v>1589</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>1590</v>
       </c>
       <c r="C44" s="33"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="C45" s="33"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C46" s="33"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="B46" s="17" t="s">
+      <c r="B47" s="17" t="s">
         <v>1593</v>
       </c>
-      <c r="C46" s="33"/>
-    </row>
-    <row r="47" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+      <c r="C47" s="33"/>
+    </row>
+    <row r="48" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A48" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B48" s="17" t="s">
         <v>1633</v>
       </c>
-      <c r="C47" s="33"/>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
+      <c r="C48" s="33"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B49" s="17" t="s">
         <v>1594</v>
-      </c>
-      <c r="C48" s="33"/>
-    </row>
-    <row r="49" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
-        <v>1595</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>1596</v>
       </c>
       <c r="C49" s="33"/>
     </row>
     <row r="50" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>1596</v>
+      </c>
+      <c r="C50" s="33"/>
+    </row>
+    <row r="51" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A51" s="15" t="s">
         <v>1597</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B51" s="17" t="s">
         <v>1598</v>
-      </c>
-      <c r="C50" s="33"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="15" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>1600</v>
       </c>
       <c r="C51" s="33"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C52" s="33"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C53" s="33"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B54" s="17" t="s">
         <v>1603</v>
       </c>
-      <c r="C53" s="33"/>
-    </row>
-    <row r="54" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A54" s="15" t="s">
+      <c r="C54" s="33"/>
+    </row>
+    <row r="55" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B55" s="17" t="s">
         <v>1604</v>
-      </c>
-      <c r="C54" s="33"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="15" t="s">
-        <v>1605</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>1606</v>
       </c>
       <c r="C55" s="33"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>46</v>
+        <v>1605</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="C56" s="33"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
-        <v>1608</v>
+        <v>46</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="C57" s="33"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>1609</v>
+      </c>
+      <c r="C58" s="33"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B59" s="17" t="s">
         <v>1610</v>
       </c>
-      <c r="C58" s="33"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="15"/>
-      <c r="B59" s="17"/>
       <c r="C59" s="33"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="15"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="33"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="34"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="15" t="s">
+      <c r="B61" s="16"/>
+      <c r="C61" s="34"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="15" t="s">
         <v>1611</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="33">
+      <c r="B62" s="17"/>
+      <c r="C62" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O152&lt;&gt;"")*(COUNTIF('2. Rates'!O6:O152,'2. Rates'!O6:O152)&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="15" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="15" t="s">
         <v>1612</v>
       </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="33">
+      <c r="B63" s="17"/>
+      <c r="C63" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O152&lt;&gt;"")*(COUNTIF('4. Scope rules'!A91:A229,'2. Rates'!O6:O152)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="15" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="15" t="s">
         <v>1613</v>
       </c>
-      <c r="B63" s="17"/>
-      <c r="C63" s="33">
+      <c r="B64" s="17"/>
+      <c r="C64" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A91:A229&lt;&gt;"")*(COUNTIF('2. Rates'!O6:O152,'4. Scope rules'!A91:A229)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="15" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="15" t="s">
         <v>1614</v>
       </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="33">
+      <c r="B65" s="17"/>
+      <c r="C65" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A91:A229&lt;&gt;"")*(COUNTIF('4. Scope rules'!A6:A87,'4. Scope rules'!B91:B229)=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="15" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="15" t="s">
         <v>1615</v>
       </c>
-      <c r="B65" s="17"/>
-      <c r="C65" s="33">
+      <c r="B66" s="17"/>
+      <c r="C66" s="33">
         <f>SUMPRODUCT(('2. Rates'!O6:O152&lt;&gt;"")*('2. Rates'!M6:M152=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="15" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="15" t="s">
         <v>1616</v>
       </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="33">
+      <c r="B67" s="17"/>
+      <c r="C67" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*(ROUND('4. Scope rules'!M6:M87+'4. Scope rules'!O6:O87,4)&lt;&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="15" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B67" s="17"/>
-      <c r="C67" s="33">
+      <c r="B68" s="17"/>
+      <c r="C68" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*(COUNTIFS('4. Scope rules'!B91:B229,'4. Scope rules'!A6:A87,'4. Scope rules'!E91:E229,"Yes")=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="15" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="15" t="s">
         <v>1617</v>
       </c>
-      <c r="B68" s="17"/>
-      <c r="C68" s="33">
+      <c r="B69" s="17"/>
+      <c r="C69" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*('4. Scope rules'!F6:F87="One")*(COUNTIFS('4. Scope rules'!B91:B229,'4. Scope rules'!A6:A87,'4. Scope rules'!E91:E229,"Yes")&gt;1))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="15" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="15" t="s">
         <v>1618</v>
       </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="33">
+      <c r="B70" s="17"/>
+      <c r="C70" s="33">
         <f>SUMPRODUCT(('4. Scope rules'!A6:A87&lt;&gt;"")*('4. Scope rules'!G6:G87=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="15" t="s">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B70" s="17"/>
-      <c r="C70" s="33">
+      <c r="B71" s="17"/>
+      <c r="C71" s="33">
         <f>SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!H6:H87,"NB",""),"EX",""),"RF",""),"FO",""),"EW",""),"DM",""),"OM",""),"—","")))&gt;0))+SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!I6:I87,"NB",""),"EX",""),"RF",""),"FO",""),"EW",""),"DM",""),"OM",""),"—","")))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="15" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B71" s="17"/>
-      <c r="C71" s="33">
+      <c r="B72" s="17"/>
+      <c r="C72" s="33">
         <f>SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('4. Scope rules'!J6:J87,"RES",""),"STU",""),"OFF",""),"EDU",""),"HEA",""),"RET",""),"IND",""),"HOS",""),"MIX",""),"OTH",""),"ALL","")))&gt;0))+SUMPRODUCT(--(LEN(TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE('2. Rates'!D6:D152,"RES",""),"STU",""),"OFF",""),"EDU",""),"HEA",""),"RET",""),"IND",""),"HOS",""),"MIX",""),"OTH",""),"ALL","")))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="15" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B72" s="17"/>
-      <c r="C72" s="33">
+      <c r="B73" s="17"/>
+      <c r="C73" s="33">
         <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*(COUNTIFS('3. Settings'!A96:A123,'3. Settings'!A96:A123,'3. Settings'!B96:B123,"ALL")=0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="15" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B73" s="17"/>
-      <c r="C73" s="33">
+      <c r="B74" s="17"/>
+      <c r="C74" s="33">
         <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*('3. Settings'!C96:C123=""))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="15"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="33"/>
-    </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="15"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="33"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B75" s="16"/>
-      <c r="C75" s="34"/>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="15" t="s">
+      <c r="B76" s="16"/>
+      <c r="C76" s="34"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B76" s="17"/>
-      <c r="C76" s="33">
+      <c r="B77" s="17"/>
+      <c r="C77" s="33">
         <f>COUNTA('4. Scope rules'!A6:A87)</f>
         <v>82</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="15" t="s">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="15" t="s">
         <v>1619</v>
       </c>
-      <c r="B77" s="17"/>
-      <c r="C77" s="33">
+      <c r="B78" s="17"/>
+      <c r="C78" s="33">
         <f>COUNTA('2. Rates'!O6:O152)</f>
         <v>139</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="15"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="33"/>
-    </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="15"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="33"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B79" s="16"/>
-      <c r="C79" s="34"/>
-    </row>
-    <row r="80" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="17" t="s">
+      <c r="B80" s="16"/>
+      <c r="C80" s="34"/>
+    </row>
+    <row r="81" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>v5.11 — 4 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="17" t="s">
         <v>1778</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B82" s="17" t="s">
         <v>1779</v>
       </c>
-      <c r="C80" s="60"/>
-    </row>
-    <row r="81" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="17" t="s">
+      <c r="C82" s="60"/>
+    </row>
+    <row r="83" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B83" s="17" t="s">
         <v>1783</v>
-      </c>
-      <c r="C81" s="60"/>
-    </row>
-    <row r="82" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="17" t="s">
-        <v>1722</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>1737</v>
-      </c>
-      <c r="C82" s="60"/>
-    </row>
-    <row r="83" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A83" s="17" t="s">
-        <v>1711</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>1712</v>
       </c>
       <c r="C83" s="60"/>
     </row>
     <row r="84" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A84" s="17" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>1737</v>
+      </c>
+      <c r="C84" s="60"/>
+    </row>
+    <row r="85" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A85" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C85" s="60"/>
+    </row>
+    <row r="86" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C84" s="60"/>
-    </row>
-    <row r="85" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A85" s="15" t="s">
+      <c r="C86" s="60"/>
+    </row>
+    <row r="87" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A87" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B87" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C85" s="33"/>
-    </row>
-    <row r="86" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="15" t="s">
+      <c r="C87" s="33"/>
+    </row>
+    <row r="88" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A88" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B88" s="17" t="s">
         <v>1061</v>
-      </c>
-      <c r="C86" s="33"/>
-    </row>
-    <row r="87" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C87" s="33"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="C88" s="33"/>
     </row>
     <row r="89" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C89" s="33"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" s="33"/>
+    </row>
+    <row r="91" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A91" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C89" s="33"/>
-    </row>
-    <row r="90" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
+      <c r="C91" s="33"/>
+    </row>
+    <row r="92" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A92" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C90" s="33"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
+      <c r="C92" s="33"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B93" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C91" s="33"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="15" t="s">
+      <c r="C93" s="33"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B94" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C92" s="33"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="15"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="33"/>
+      <c r="C94" s="33"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="15"/>
+      <c r="B95" s="17"/>
+      <c r="C95" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6831,7 +6861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61613224-FE41-4C03-8B46-4109509C3076}">
-  <dimension ref="A1:S152"/>
+  <dimension ref="A1:Z152"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="8" customWidth="1"/>
@@ -6850,7 +6880,9 @@
     <col min="17" max="17" width="44.7109375" style="8" customWidth="1"/>
     <col min="18" max="18" width="16.7109375" style="8" customWidth="1"/>
     <col min="19" max="19" width="16.7109375" style="8" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="8"/>
+    <col min="20" max="25" width="16.7109375" style="8" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="8" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.25">
@@ -6868,7 +6900,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>756</v>
       </c>
@@ -6925,6 +6957,41 @@
       </c>
       <c r="S5" s="12" t="s">
         <v>1753</v>
+      </c>
+      <c r="T5" s="12" t="inlineStr">
+        <is>
+          <t>Lakeside rate (£ per this row's unit, this workbook's basis: Lakeside Staff &amp; Family Flats refurbishment, tender Sep 2026, median of 4 bids ÷ 0.94. Evidence only — the app does not read it)</t>
+        </is>
+      </c>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>Computer Science rate (£ per this row's unit, this workbook's basis: CS Building decarbonisation, tender Mar 2024, mean of 2 bids × 1.07 ÷ 0.94; roof per m² footprint; 5.1b is the whole M&amp;E package. Evidence only)</t>
+        </is>
+      </c>
+      <c r="V5" s="12" t="inlineStr">
+        <is>
+          <t>Scarman rate (£ per this row's unit, this workbook's basis: Scarman Public Toilets Phase 2, HIGH specification, tender Apr 2026, median of 6 bids × 1.007 ÷ 0.94; per m² figures over the 71 m² toilet area only. Evidence only)</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>Co-op rate (£ per this row's unit, this workbook's basis: Co-op grocery store fit-out, Kingfisher CSA, contract Aug 2025 × 1.03 ÷ 0.94, over 885 m². Evidence only)</t>
+        </is>
+      </c>
+      <c r="X5" s="12" t="inlineStr">
+        <is>
+          <t>IBRB café rate (£ per this row's unit, this workbook's basis: IBRB café servery fit-out, Senevo winning bid 2025 × 1.035 ÷ 0.94, over 72 m² (catering kitchen per 28 m² servery). Evidence only)</t>
+        </is>
+      </c>
+      <c r="Y5" s="12" t="inlineStr">
+        <is>
+          <t>Riley Court rate (£ per this row's unit, this workbook's basis: Psychology building full refurbishment, Maris signed contract CSA £9.15m, GMP Nov 2024 × 1.05 ÷ 0.94, GIFA 3,850 m². Evidence only)</t>
+        </is>
+      </c>
+      <c r="Z5" s="12" t="inlineStr">
+        <is>
+          <t>Average of project rates (mean of columns R–Y that hold a figure for this row. Projects differ in scope and specification, so read it with the column notes. Evidence only — the app does not read it)</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -6946,7 +7013,7 @@
       <c r="N6" s="19"/>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:18" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>72</v>
       </c>
@@ -6990,8 +7057,12 @@
       <c r="R7" s="22" t="n">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="40">
+        <f>AVERAGE(R7:Y7)</f>
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>82</v>
       </c>
@@ -7035,8 +7106,12 @@
       <c r="R8" s="22" t="n">
         <v>73.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" ht="78.5" x14ac:dyDescent="0.2">
+      <c r="Z8" s="40">
+        <f>AVERAGE(R8:Y8)</f>
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>96</v>
       </c>
@@ -7080,6 +7155,25 @@
       <c r="S9" s="22">
         <v>51.4</v>
       </c>
+      <c r="T9" s="22">
+        <v>54</v>
+      </c>
+      <c r="V9" s="22">
+        <v>217</v>
+      </c>
+      <c r="W9" s="22">
+        <v>48.8</v>
+      </c>
+      <c r="X9" s="22">
+        <v>11.5</v>
+      </c>
+      <c r="Y9" s="22">
+        <v>54.9</v>
+      </c>
+      <c r="Z9" s="40">
+        <f>AVERAGE(R9:Y9)</f>
+        <v>72.933333</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
@@ -7196,7 +7290,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>119</v>
       </c>
@@ -7236,6 +7330,10 @@
         <v>1786</v>
       </c>
       <c r="R13" s="22" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="Z13" s="40">
+        <f>AVERAGE(R13:Y13)</f>
         <v>36.3</v>
       </c>
     </row>
@@ -7669,7 +7767,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="218.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:26" ht="218.75" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>1669</v>
       </c>
@@ -7721,8 +7819,15 @@
       <c r="S25" s="22">
         <v>516.9</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="U25" s="22">
+        <v>182</v>
+      </c>
+      <c r="Z25" s="40">
+        <f>AVERAGE(R25:Y25)</f>
+        <v>349.45</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
         <v>1659</v>
       </c>
@@ -7764,8 +7869,15 @@
       <c r="Q26" s="22" t="s">
         <v>1664</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="T26" s="22">
+        <v>32</v>
+      </c>
+      <c r="Z26" s="40">
+        <f>AVERAGE(R26:Y26)</f>
+        <v>32.0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
         <v>197</v>
       </c>
@@ -7812,8 +7924,18 @@
       <c r="Q27" s="22" t="s">
         <v>1730</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" ht="165.75" x14ac:dyDescent="0.2">
+      <c r="U27" s="22">
+        <v>48</v>
+      </c>
+      <c r="Y27" s="22">
+        <v>170.5</v>
+      </c>
+      <c r="Z27" s="40">
+        <f>AVERAGE(R27:Y27)</f>
+        <v>109.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>203</v>
       </c>
@@ -7860,8 +7982,21 @@
       <c r="Q28" s="22" t="s">
         <v>1731</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="U28" s="22">
+        <v>210</v>
+      </c>
+      <c r="W28" s="22">
+        <v>24.4</v>
+      </c>
+      <c r="Y28" s="22">
+        <v>146.7</v>
+      </c>
+      <c r="Z28" s="40">
+        <f>AVERAGE(R28:Y28)</f>
+        <v>127.033333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="21" t="s">
         <v>208</v>
       </c>
@@ -7905,8 +8040,18 @@
       <c r="O29" s="24" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="W29" s="22">
+        <v>26.4</v>
+      </c>
+      <c r="Y29" s="22">
+        <v>246.9</v>
+      </c>
+      <c r="Z29" s="40">
+        <f>AVERAGE(R29:Y29)</f>
+        <v>136.65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="21" t="s">
         <v>1142</v>
       </c>
@@ -7950,8 +8095,21 @@
       <c r="O30" s="24" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" ht="155.0" x14ac:dyDescent="0.2">
+      <c r="V30" s="22">
+        <v>99</v>
+      </c>
+      <c r="W30" s="22">
+        <v>9.1</v>
+      </c>
+      <c r="Y30" s="22">
+        <v>163.7</v>
+      </c>
+      <c r="Z30" s="40">
+        <f>AVERAGE(R30:Y30)</f>
+        <v>90.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" ht="155.0" x14ac:dyDescent="0.2">
       <c r="A31" s="21" t="s">
         <v>1146</v>
       </c>
@@ -7998,6 +8156,22 @@
       </c>
       <c r="S31" s="22">
         <v>95.8</v>
+      </c>
+      <c r="T31" s="22">
+        <v>13.5</v>
+      </c>
+      <c r="V31" s="22">
+        <v>24</v>
+      </c>
+      <c r="W31" s="22">
+        <v>3.4</v>
+      </c>
+      <c r="Y31" s="22">
+        <v>15.6</v>
+      </c>
+      <c r="Z31" s="40">
+        <f>AVERAGE(R31:Y31)</f>
+        <v>30.46</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
@@ -8019,7 +8193,7 @@
       <c r="N32" s="26"/>
       <c r="O32" s="27"/>
     </row>
-    <row r="33" spans="1:19" ht="91.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:26" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>221</v>
       </c>
@@ -8069,8 +8243,27 @@
       <c r="S33" s="22">
         <v>99.3</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T33" s="22">
+        <v>72</v>
+      </c>
+      <c r="V33" s="22">
+        <v>304</v>
+      </c>
+      <c r="W33" s="22">
+        <v>26.6</v>
+      </c>
+      <c r="X33" s="22">
+        <v>49</v>
+      </c>
+      <c r="Y33" s="22">
+        <v>39.4</v>
+      </c>
+      <c r="Z33" s="40">
+        <f>AVERAGE(R33:Y33)</f>
+        <v>98.383333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
         <v>1153</v>
       </c>
@@ -8118,6 +8311,19 @@
       </c>
       <c r="Q34" s="22" t="s">
         <v>1679</v>
+      </c>
+      <c r="V34" s="22">
+        <v>177</v>
+      </c>
+      <c r="W34" s="22">
+        <v>21.5</v>
+      </c>
+      <c r="Y34" s="22">
+        <v>95.3</v>
+      </c>
+      <c r="Z34" s="40">
+        <f>AVERAGE(R34:Y34)</f>
+        <v>97.933333</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
@@ -8167,7 +8373,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A36" s="23" t="s">
         <v>1655</v>
       </c>
@@ -8218,8 +8424,15 @@
       <c r="S36" s="22">
         <v>38.4</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T36" s="22">
+        <v>51</v>
+      </c>
+      <c r="Z36" s="40">
+        <f>AVERAGE(R36:Y36)</f>
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A37" s="21" t="s">
         <v>1671</v>
       </c>
@@ -8266,8 +8479,21 @@
       <c r="Q37" s="22" t="s">
         <v>1680</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" ht="104.0" x14ac:dyDescent="0.2">
+      <c r="V37" s="22">
+        <v>129</v>
+      </c>
+      <c r="W37" s="22">
+        <v>21.0</v>
+      </c>
+      <c r="Y37" s="22">
+        <v>109.6</v>
+      </c>
+      <c r="Z37" s="40">
+        <f>AVERAGE(R37:Y37)</f>
+        <v>86.533333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" ht="104.0" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>1650</v>
       </c>
@@ -8315,6 +8541,13 @@
       </c>
       <c r="S38" s="22">
         <v>70.4</v>
+      </c>
+      <c r="T38" s="22">
+        <v>30</v>
+      </c>
+      <c r="Z38" s="40">
+        <f>AVERAGE(R38:Y38)</f>
+        <v>50.2</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
@@ -8336,7 +8569,7 @@
       <c r="N39" s="26"/>
       <c r="O39" s="27"/>
     </row>
-    <row r="40" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A40" s="48" t="s">
         <v>1164</v>
       </c>
@@ -8383,8 +8616,18 @@
         <v>238</v>
       </c>
       <c r="P40" s="54"/>
-    </row>
-    <row r="41" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="V40" s="22">
+        <v>7653</v>
+      </c>
+      <c r="Y40" s="22">
+        <v>14573</v>
+      </c>
+      <c r="Z40" s="40">
+        <f>AVERAGE(R40:Y40)</f>
+        <v>11113.0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A41" s="48" t="s">
         <v>1169</v>
       </c>
@@ -8428,6 +8671,13 @@
       <c r="O41" s="52" t="s">
         <v>251</v>
       </c>
+      <c r="Y41" s="22">
+        <v>16025</v>
+      </c>
+      <c r="Z41" s="40">
+        <f>AVERAGE(R41:Y41)</f>
+        <v>16025.0</v>
+      </c>
     </row>
     <row r="42" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="43" t="s">
@@ -8472,7 +8722,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="104.0" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:26" ht="104.0" x14ac:dyDescent="0.2">
       <c r="A43" s="48" t="s">
         <v>1175</v>
       </c>
@@ -8523,6 +8773,13 @@
       </c>
       <c r="S43" s="22">
         <v>3869</v>
+      </c>
+      <c r="T43" s="22">
+        <v>2563</v>
+      </c>
+      <c r="Z43" s="40">
+        <f>AVERAGE(R43:Y43)</f>
+        <v>3216.0</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
@@ -8617,7 +8874,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="48" t="s">
         <v>1188</v>
       </c>
@@ -8666,8 +8923,15 @@
       <c r="Q46" s="49" t="s">
         <v>1667</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="T46" s="22">
+        <v>5296</v>
+      </c>
+      <c r="Z46" s="40">
+        <f>AVERAGE(R46:Y46)</f>
+        <v>5296.0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A47" s="48" t="s">
         <v>1194</v>
       </c>
@@ -8713,8 +8977,15 @@
       <c r="O47" s="52" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="48" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
+      <c r="Y47" s="22">
+        <v>10276</v>
+      </c>
+      <c r="Z47" s="40">
+        <f>AVERAGE(R47:Y47)</f>
+        <v>10276.0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A48" s="21" t="s">
         <v>292</v>
       </c>
@@ -8764,8 +9035,18 @@
       <c r="S48" s="22">
         <v>63.7</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="W48" s="22">
+        <v>7.0</v>
+      </c>
+      <c r="Y48" s="22">
+        <v>41.8</v>
+      </c>
+      <c r="Z48" s="40">
+        <f>AVERAGE(R48:Y48)</f>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="21" t="s">
         <v>1199</v>
       </c>
@@ -8809,6 +9090,16 @@
       <c r="O49" s="24" t="s">
         <v>287</v>
       </c>
+      <c r="W49" s="22">
+        <v>16.4</v>
+      </c>
+      <c r="Y49" s="22">
+        <v>12.2</v>
+      </c>
+      <c r="Z49" s="40">
+        <f>AVERAGE(R49:Y49)</f>
+        <v>14.3</v>
+      </c>
     </row>
     <row r="50" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A50" s="21" t="s">
@@ -9035,7 +9326,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A55" s="21" t="s">
         <v>1216</v>
       </c>
@@ -9076,6 +9367,13 @@
       <c r="N55" s="22"/>
       <c r="O55" s="24" t="s">
         <v>312</v>
+      </c>
+      <c r="X55" s="22">
+        <v>1438</v>
+      </c>
+      <c r="Z55" s="40">
+        <f>AVERAGE(R55:Y55)</f>
+        <v>1438.0</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -9392,7 +9690,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:26" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A64" s="55" t="s">
         <v>1027</v>
       </c>
@@ -9444,6 +9742,13 @@
       <c r="Q64" s="22" t="s">
         <v>1732</v>
       </c>
+      <c r="U64" s="22">
+        <v>224</v>
+      </c>
+      <c r="Z64" s="40">
+        <f>AVERAGE(R64:Y64)</f>
+        <v>224.0</v>
+      </c>
     </row>
     <row r="65" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A65" s="55" t="s">
@@ -9495,7 +9800,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A66" s="55" t="s">
         <v>1252</v>
       </c>
@@ -9544,6 +9849,13 @@
       <c r="O66" s="59" t="s">
         <v>383</v>
       </c>
+      <c r="Y66" s="22">
+        <v>134.7</v>
+      </c>
+      <c r="Z66" s="40">
+        <f>AVERAGE(R66:Y66)</f>
+        <v>134.7</v>
+      </c>
     </row>
     <row r="67" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A67" s="55" t="s">
@@ -10095,7 +10407,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="91.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:26" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A78" s="23" t="s">
         <v>1299</v>
       </c>
@@ -10147,8 +10459,24 @@
       <c r="S78" s="22">
         <v>38.9</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="V78" s="22">
+        <v>209</v>
+      </c>
+      <c r="W78" s="22">
+        <v>18.2</v>
+      </c>
+      <c r="X78" s="22">
+        <v>124</v>
+      </c>
+      <c r="Y78" s="22">
+        <v>104.5</v>
+      </c>
+      <c r="Z78" s="40">
+        <f>AVERAGE(R78:Y78)</f>
+        <v>98.92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A79" s="23" t="s">
         <v>1304</v>
       </c>
@@ -10200,8 +10528,15 @@
       <c r="Q79" s="22" t="s">
         <v>1681</v>
       </c>
-    </row>
-    <row r="80" spans="1:19" ht="78.5" x14ac:dyDescent="0.2">
+      <c r="T79" s="22">
+        <v>20</v>
+      </c>
+      <c r="Z79" s="40">
+        <f>AVERAGE(R79:Y79)</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
         <v>1672</v>
       </c>
@@ -10250,8 +10585,18 @@
       <c r="Q80" s="22" t="s">
         <v>1763</v>
       </c>
-    </row>
-    <row r="81" spans="1:19" ht="91.25" x14ac:dyDescent="0.2">
+      <c r="W80" s="22">
+        <v>73.1</v>
+      </c>
+      <c r="Y80" s="22">
+        <v>172.4</v>
+      </c>
+      <c r="Z80" s="40">
+        <f>AVERAGE(R80:Y80)</f>
+        <v>122.75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:26" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>1644</v>
       </c>
@@ -10300,8 +10645,18 @@
       <c r="S81" s="22">
         <v>28.2</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="T81" s="22">
+        <v>18.5</v>
+      </c>
+      <c r="V81" s="22">
+        <v>62</v>
+      </c>
+      <c r="Z81" s="40">
+        <f>AVERAGE(R81:Y81)</f>
+        <v>36.233333</v>
+      </c>
+    </row>
+    <row r="82" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
         <v>420</v>
       </c>
@@ -10345,8 +10700,18 @@
       <c r="O82" s="24" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="83" spans="1:19" ht="40.25" x14ac:dyDescent="0.2">
+      <c r="W82" s="22">
+        <v>39.5</v>
+      </c>
+      <c r="Y82" s="22">
+        <v>34.1</v>
+      </c>
+      <c r="Z82" s="40">
+        <f>AVERAGE(R82:Y82)</f>
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:26" ht="40.25" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
         <v>373</v>
       </c>
@@ -10396,6 +10761,16 @@
       <c r="S83" s="22">
         <v>4.3</v>
       </c>
+      <c r="W83" s="22">
+        <v>11.5</v>
+      </c>
+      <c r="Y83" s="22">
+        <v>59.1</v>
+      </c>
+      <c r="Z83" s="40">
+        <f>AVERAGE(R83:Y83)</f>
+        <v>24.966667</v>
+      </c>
     </row>
     <row r="84" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="55" t="s">
@@ -10518,7 +10893,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="87" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A87" s="23" t="s">
         <v>1328</v>
       </c>
@@ -10564,8 +10939,24 @@
       <c r="O87" s="24" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="88" spans="1:19" ht="116.75" x14ac:dyDescent="0.2">
+      <c r="V87" s="22">
+        <v>97</v>
+      </c>
+      <c r="W87" s="22">
+        <v>88.5</v>
+      </c>
+      <c r="X87" s="22">
+        <v>218</v>
+      </c>
+      <c r="Y87" s="22">
+        <v>130.6</v>
+      </c>
+      <c r="Z87" s="40">
+        <f>AVERAGE(R87:Y87)</f>
+        <v>133.525</v>
+      </c>
+    </row>
+    <row r="88" spans="1:26" ht="116.75" x14ac:dyDescent="0.2">
       <c r="A88" s="23" t="s">
         <v>1332</v>
       </c>
@@ -10616,6 +11007,13 @@
       </c>
       <c r="S88" s="22">
         <v>157.7</v>
+      </c>
+      <c r="T88" s="22">
+        <v>153</v>
+      </c>
+      <c r="Z88" s="40">
+        <f>AVERAGE(R88:Y88)</f>
+        <v>155.35</v>
       </c>
     </row>
     <row r="89" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -10661,7 +11059,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A90" s="23" t="s">
         <v>1338</v>
       </c>
@@ -10712,6 +11110,22 @@
       </c>
       <c r="S90" s="22">
         <v>113.2</v>
+      </c>
+      <c r="V90" s="22">
+        <v>84</v>
+      </c>
+      <c r="W90" s="22">
+        <v>80.6</v>
+      </c>
+      <c r="X90" s="22">
+        <v>51</v>
+      </c>
+      <c r="Y90" s="22">
+        <v>198.0</v>
+      </c>
+      <c r="Z90" s="40">
+        <f>AVERAGE(R90:Y90)</f>
+        <v>105.36</v>
       </c>
     </row>
     <row r="91" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -11046,7 +11460,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="65.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
         <v>507</v>
       </c>
@@ -11096,6 +11510,22 @@
       <c r="S99" s="22">
         <v>64.7</v>
       </c>
+      <c r="T99" s="22">
+        <v>18.6</v>
+      </c>
+      <c r="V99" s="22">
+        <v>77</v>
+      </c>
+      <c r="W99" s="22">
+        <v>28.4</v>
+      </c>
+      <c r="Y99" s="22">
+        <v>43.5</v>
+      </c>
+      <c r="Z99" s="40">
+        <f>AVERAGE(R99:Y99)</f>
+        <v>46.44</v>
+      </c>
     </row>
     <row r="100" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A100" s="21" t="s">
@@ -11183,7 +11613,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A102" s="21" t="s">
         <v>1674</v>
       </c>
@@ -11230,8 +11660,21 @@
       <c r="Q102" s="22" t="s">
         <v>1686</v>
       </c>
-    </row>
-    <row r="103" spans="1:19" ht="53.0" x14ac:dyDescent="0.2">
+      <c r="T102" s="22">
+        <v>19.4</v>
+      </c>
+      <c r="X102" s="22">
+        <v>5.3</v>
+      </c>
+      <c r="Y102" s="22">
+        <v>33.6</v>
+      </c>
+      <c r="Z102" s="40">
+        <f>AVERAGE(R102:Y102)</f>
+        <v>19.433333</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" ht="53.0" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
         <v>1640</v>
       </c>
@@ -11280,8 +11723,15 @@
       <c r="S103" s="22">
         <v>19.3</v>
       </c>
-    </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.2" ht="53.0" customHeight="1">
+      <c r="T103" s="22">
+        <v>24.5</v>
+      </c>
+      <c r="Z103" s="40">
+        <f>AVERAGE(R103:Y103)</f>
+        <v>21.9</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.2" ht="53.0" customHeight="1">
       <c r="A104" s="21" t="s">
         <v>563</v>
       </c>
@@ -11331,8 +11781,18 @@
       <c r="S104" s="22">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="105" spans="1:19" ht="53.0" x14ac:dyDescent="0.2">
+      <c r="W104" s="22">
+        <v>57.8</v>
+      </c>
+      <c r="Y104" s="22">
+        <v>22.0</v>
+      </c>
+      <c r="Z104" s="40">
+        <f>AVERAGE(R104:Y104)</f>
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" ht="53.0" x14ac:dyDescent="0.2">
       <c r="A105" s="23" t="s">
         <v>1381</v>
       </c>
@@ -11383,6 +11843,10 @@
       </c>
       <c r="S105" s="22">
         <v>112847</v>
+      </c>
+      <c r="Z105" s="40">
+        <f>AVERAGE(R105:Y105)</f>
+        <v>112847.0</v>
       </c>
     </row>
     <row r="106" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -12076,7 +12540,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="123" spans="1:17" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="21" t="s">
         <v>1675</v>
       </c>
@@ -12121,8 +12585,18 @@
       <c r="Q123" s="22" t="s">
         <v>1733</v>
       </c>
-    </row>
-    <row r="124" spans="1:19" ht="78.5" x14ac:dyDescent="0.2">
+      <c r="U123" s="22">
+        <v>8</v>
+      </c>
+      <c r="W123" s="22">
+        <v>3.1</v>
+      </c>
+      <c r="Z123" s="40">
+        <f>AVERAGE(R123:Y123)</f>
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="124" spans="1:26" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A124" s="21" t="s">
         <v>1635</v>
       </c>
@@ -12168,6 +12642,13 @@
       </c>
       <c r="S124" s="22">
         <v>11.0</v>
+      </c>
+      <c r="T124" s="22">
+        <v>27</v>
+      </c>
+      <c r="Z124" s="40">
+        <f>AVERAGE(R124:Y124)</f>
+        <v>19.0</v>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
@@ -12189,7 +12670,7 @@
       <c r="N125" s="26"/>
       <c r="O125" s="27"/>
     </row>
-    <row r="126" spans="1:17" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A126" s="23" t="s">
         <v>1435</v>
       </c>
@@ -12236,6 +12717,13 @@
       <c r="Q126" s="22" t="s">
         <v>1734</v>
       </c>
+      <c r="U126" s="22">
+        <v>48</v>
+      </c>
+      <c r="Z126" s="40">
+        <f>AVERAGE(R126:Y126)</f>
+        <v>48.0</v>
+      </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="23" t="s">
@@ -12340,7 +12828,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A129" s="21" t="s">
         <v>1447</v>
       </c>
@@ -12383,6 +12871,13 @@
       </c>
       <c r="O129" s="24" t="s">
         <v>628</v>
+      </c>
+      <c r="Y129" s="22">
+        <v>53.7</v>
+      </c>
+      <c r="Z129" s="40">
+        <f>AVERAGE(R129:Y129)</f>
+        <v>53.7</v>
       </c>
     </row>
     <row r="130" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -12537,7 +13032,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A134" s="21" t="s">
         <v>691</v>
       </c>
@@ -12581,8 +13076,15 @@
       <c r="O134" s="24" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="Y134" s="22">
+        <v>35.4</v>
+      </c>
+      <c r="Z134" s="40">
+        <f>AVERAGE(R134:Y134)</f>
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A135" s="21" t="s">
         <v>656</v>
       </c>
@@ -12626,6 +13128,13 @@
       <c r="O135" s="24" t="s">
         <v>662</v>
       </c>
+      <c r="Y135" s="22">
+        <v>67.6</v>
+      </c>
+      <c r="Z135" s="40">
+        <f>AVERAGE(R135:Y135)</f>
+        <v>67.6</v>
+      </c>
     </row>
     <row r="136" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A136" s="23" t="s">
@@ -12992,7 +13501,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A145" s="21" t="s">
         <v>696</v>
       </c>
@@ -13040,6 +13549,10 @@
         <v>1787</v>
       </c>
       <c r="R145" s="22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z145" s="40">
+        <f>AVERAGE(R145:Y145)</f>
         <v>2.1</v>
       </c>
     </row>
@@ -13419,7 +13932,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>1780</v>
+        <v>507</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -13430,7 +13943,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1781</v>
+        <v>1789</v>
       </c>
       <c r="C7" s="2"/>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -6229,7 +6229,7 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>Columns T–Y on '2. Rates' hold the other real projects' figures in the row's unit and on this workbook's basis, beside Whitefields (R) and Claycroft (S): T Lakeside S&amp;F (tender Sep 2026, median of 4 bids); U Computer Science decarbonisation (tender Mar 2024, mean of 2 bids); V Scarman Public Toilets Phase 2 (HIGH spec, tender Apr 2026, median of 6 bids; per m² over the 71 m² toilet area); W Co-op grocery store fit-out (Kingfisher contract Aug 2025, 885 m²); X IBRB café servery (Senevo winning bid 2025, 72 m² café, 28 m² servery); Y Riley Court Psychology full refurbishment (Maris signed contract £9.15m, GMP Nov 2024, GIFA 3,850 m²). Each excludes the contractor's prelims, OH&amp;P and design, rebased to Q3 2026 and ÷ 0.94 West Midlands. Column Z is the average of R–Y for the row. Projects differ in scope and specification, so expect spread. Not on '2. Rates': scaffold for envelope works £42 (CS) and £33 (Claycroft) per m² GIFA; retail refrigeration £379 and retailer equipment £373 per m² (Co-op); preliminaries Lakeside ~9%, Whitefields 16.8%, Claycroft 11.3%, Scarman 14%, Co-op 7.2%, IBRB 17.7%, Riley Court 5.5% (+4% contractor PM and design). Evidence only: the app does not read these columns and no rate changed.</t>
+          <t>Columns T–Y on '2. Rates' hold the other real projects' figures in the row's unit and on this workbook's basis, beside Whitefields (R) and Claycroft (S): T Lakeside S&amp;F (tender Sep 2026, median of 4 bids); U Computer Science decarbonisation (tender Mar 2024, mean of 2 bids); V Scarman Public Toilets Phase 2 (HIGH spec, tender Apr 2026, median of 6 bids; per m² over the 71 m² toilet area); W Co-op grocery store fit-out (Kingfisher contract Aug 2025, 885 m²); X IBRB café servery (Senevo winning bid 2025, 72 m² café, 28 m² servery); Y Riley Court Psychology full refurbishment (Maris signed contract £9.15m, GMP Nov 2024, GIFA 3,850 m²). Each excludes the contractor's prelims, OH&amp;P and design, rebased to Q3 2026 and ÷ 0.94 West Midlands. Column Z is the average of R–Y for the row. Projects differ in scope and specification, so expect spread. Not on '2. Rates': scaffold for envelope works £42 (CS) and £33 (Claycroft) per m² GIFA; retail refrigeration £379 and retailer equipment £373 per m² (Co-op); preliminaries Lakeside ~9%, Whitefields 16.8%, Claycroft 11.3%, Scarman 14%, Co-op 7.2%, IBRB 17.7%, Riley Court 5.5% (+4% contractor PM and design). Evidence only: the app does not read these columns and no rate changed. Column AA is Claude's suggested Refurb &amp; Fit-out Standard rate for each row with evidence, and AB the reason (Raise / Lower / Keep). They are suggestions for the owner only: the app does not read them, and a rate changes only when the owner edits the rate columns.</t>
         </is>
       </c>
     </row>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %).</t>
+          <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %). Columns AA–AB: Claude's suggested Refurb &amp; Fit-out Std rate and the reason, on all 47 rows (25 raise, 2 lower, 20 keep).</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61613224-FE41-4C03-8B46-4109509C3076}">
-  <dimension ref="A1:Z152"/>
+  <dimension ref="A1:AB152"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="8" customWidth="1"/>
@@ -6882,7 +6882,9 @@
     <col min="19" max="19" width="16.7109375" style="8" customWidth="1"/>
     <col min="20" max="25" width="16.7109375" style="8" customWidth="1"/>
     <col min="26" max="26" width="14.7109375" style="8" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="8"/>
+    <col min="27" max="27" width="14.7109375" style="8" customWidth="1"/>
+    <col min="28" max="28" width="60.7109375" style="8" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.25">
@@ -6900,7 +6902,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>756</v>
       </c>
@@ -6991,6 +6993,16 @@
       <c r="Z5" s="12" t="inlineStr">
         <is>
           <t>Average of project rates (mean of columns R–Y that hold a figure for this row. Projects differ in scope and specification, so read it with the column notes. Evidence only — the app does not read it)</t>
+        </is>
+      </c>
+      <c r="AA5" s="12" t="inlineStr">
+        <is>
+          <t>Suggested Refurb &amp; Fit-out Std rate (Claude's suggestion from the project columns R–Y, 4 Oct 2026, for the owner to accept, change or ignore. Evidence only — the app does not read it)</t>
+        </is>
+      </c>
+      <c r="AB5" s="12" t="inlineStr">
+        <is>
+          <t>Reason for the suggestion</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7025,7 @@
       <c r="N6" s="19"/>
       <c r="O6" s="20"/>
     </row>
-    <row r="7" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" ht="51" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>72</v>
       </c>
@@ -7061,8 +7073,16 @@
         <f>AVERAGE(R7:Y7)</f>
         <v>8.1</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="AA7" s="40">
+        <v>25</v>
+      </c>
+      <c r="AB7" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Matches Mace pre-tender allowance (£24.5); one low tender (£8) is not enough to cut it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A8" s="21" t="s">
         <v>82</v>
       </c>
@@ -7110,8 +7130,16 @@
         <f>AVERAGE(R8:Y8)</f>
         <v>73.3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" ht="78.5" x14ac:dyDescent="0.2">
+      <c r="AA8" s="40">
+        <v>100</v>
+      </c>
+      <c r="AB8" s="22" t="inlineStr">
+        <is>
+          <t>Lower. Whitefields £73 on simple 2-storey masonry; £100 leaves room for framed or taller buildings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>96</v>
       </c>
@@ -7174,6 +7202,14 @@
         <f>AVERAGE(R9:Y9)</f>
         <v>72.933333</v>
       </c>
+      <c r="AA9" s="40">
+        <v>55</v>
+      </c>
+      <c r="AB9" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside, Claycroft, Co-op and Riley Court all £49–55. Scarman and IBRB are tiny jobs.</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
@@ -7290,7 +7326,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>119</v>
       </c>
@@ -7335,6 +7371,14 @@
       <c r="Z13" s="40">
         <f>AVERAGE(R13:Y13)</f>
         <v>36.3</v>
+      </c>
+      <c r="AA13" s="40">
+        <v>100</v>
+      </c>
+      <c r="AB13" s="22" t="inlineStr">
+        <is>
+          <t>Keep. One water-main job (£36); diversions are too site-specific to move the rate.</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -7767,7 +7811,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="218.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:28" ht="218.75" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>1669</v>
       </c>
@@ -7826,8 +7870,16 @@
         <f>AVERAGE(R25:Y25)</f>
         <v>349.45</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="AA25" s="40">
+        <v>190</v>
+      </c>
+      <c r="AB25" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Computer Science £182 per m² footprint. Claycroft metal over-roof £517 is a High case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A26" s="21" t="s">
         <v>1659</v>
       </c>
@@ -7876,8 +7928,16 @@
         <f>AVERAGE(R26:Y26)</f>
         <v>32.0</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="AA26" s="40">
+        <v>32</v>
+      </c>
+      <c r="AB26" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside tender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" spans="1:28" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
         <v>197</v>
       </c>
@@ -7934,8 +7994,16 @@
         <f>AVERAGE(R27:Y27)</f>
         <v>109.25</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" ht="165.75" x14ac:dyDescent="0.2">
+      <c r="AA27" s="40">
+        <v>100</v>
+      </c>
+      <c r="AB27" s="22" t="inlineStr">
+        <is>
+          <t>Raise. CS part render £48; Riley Court full envelope upgrade £171 (cladding, insulated linings).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="165.75" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>203</v>
       </c>
@@ -7995,8 +8063,16 @@
         <f>AVERAGE(R28:Y28)</f>
         <v>127.033333</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA28" s="40">
+        <v>140</v>
+      </c>
+      <c r="AB28" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court new windows £147; CS triple glazing £210 (High). Co-op was refinish only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A29" s="21" t="s">
         <v>208</v>
       </c>
@@ -8050,8 +8126,16 @@
         <f>AVERAGE(R29:Y29)</f>
         <v>136.65</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA29" s="40">
+        <v>150</v>
+      </c>
+      <c r="AB29" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £247 (acoustic academic partitions); Co-op £26 was a light shop fit-out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A30" s="21" t="s">
         <v>1142</v>
       </c>
@@ -8108,8 +8192,16 @@
         <f>AVERAGE(R30:Y30)</f>
         <v>90.6</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" ht="155.0" x14ac:dyDescent="0.2">
+      <c r="AA30" s="40">
+        <v>100</v>
+      </c>
+      <c r="AB30" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £164, Scarman £99; Co-op £9 reused most doors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" spans="1:28" ht="155.0" x14ac:dyDescent="0.2">
       <c r="A31" s="21" t="s">
         <v>1146</v>
       </c>
@@ -8172,6 +8264,14 @@
       <c r="Z31" s="40">
         <f>AVERAGE(R31:Y31)</f>
         <v>30.46</v>
+      </c>
+      <c r="AA31" s="40">
+        <v>30</v>
+      </c>
+      <c r="AB31" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Most projects £3–24; Claycroft £96 out-turn (surveyed occupied residential) is a High case.</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
@@ -8193,7 +8293,7 @@
       <c r="N32" s="26"/>
       <c r="O32" s="27"/>
     </row>
-    <row r="33" spans="1:26" ht="91.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:28" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>221</v>
       </c>
@@ -8262,8 +8362,16 @@
         <f>AVERAGE(R33:Y33)</f>
         <v>98.383333</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA33" s="40">
+        <v>75</v>
+      </c>
+      <c r="AB33" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £72, Claycroft £99, Riley Court £39 (decoration only). Scarman is toilet-area only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
         <v>1153</v>
       </c>
@@ -8325,6 +8433,14 @@
         <f>AVERAGE(R34:Y34)</f>
         <v>97.933333</v>
       </c>
+      <c r="AA34" s="40">
+        <v>85</v>
+      </c>
+      <c r="AB34" s="22" t="inlineStr">
+        <is>
+          <t>Raise slightly. Riley Court £95 full replacement; Co-op £22 kept its floor. Scarman is toilet-area only.</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A35" s="23" t="s">
@@ -8373,7 +8489,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:28" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A36" s="23" t="s">
         <v>1655</v>
       </c>
@@ -8431,8 +8547,16 @@
         <f>AVERAGE(R36:Y36)</f>
         <v>44.7</v>
       </c>
-    </row>
-    <row r="37" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA36" s="40">
+        <v>50</v>
+      </c>
+      <c r="AB36" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £51, Claycroft £38.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A37" s="21" t="s">
         <v>1671</v>
       </c>
@@ -8492,8 +8616,16 @@
         <f>AVERAGE(R37:Y37)</f>
         <v>86.533333</v>
       </c>
-    </row>
-    <row r="38" spans="1:26" ht="104.0" x14ac:dyDescent="0.2">
+      <c r="AA37" s="40">
+        <v>80</v>
+      </c>
+      <c r="AB37" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £110 new suspended ceilings; Co-op £21 painted soffits only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" spans="1:28" ht="104.0" x14ac:dyDescent="0.2">
       <c r="A38" s="21" t="s">
         <v>1650</v>
       </c>
@@ -8548,6 +8680,14 @@
       <c r="Z38" s="40">
         <f>AVERAGE(R38:Y38)</f>
         <v>50.2</v>
+      </c>
+      <c r="AA38" s="40">
+        <v>30</v>
+      </c>
+      <c r="AB38" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £30; Claycroft £70 was full replacement (High case).</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
@@ -8569,7 +8709,7 @@
       <c r="N39" s="26"/>
       <c r="O39" s="27"/>
     </row>
-    <row r="40" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A40" s="48" t="s">
         <v>1164</v>
       </c>
@@ -8626,8 +8766,16 @@
         <f>AVERAGE(R40:Y40)</f>
         <v>11113.0</v>
       </c>
-    </row>
-    <row r="41" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="AA40" s="40">
+        <v>7000</v>
+      </c>
+      <c r="AB40" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Scarman £7,650 (high spec) and Riley Court £14,600 incl. tiling both far above £3,950.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A41" s="48" t="s">
         <v>1169</v>
       </c>
@@ -8678,6 +8826,14 @@
         <f>AVERAGE(R41:Y41)</f>
         <v>16025.0</v>
       </c>
+      <c r="AA41" s="40">
+        <v>9000</v>
+      </c>
+      <c r="AB41" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £16,000 per accessible WC incl. tiling and shower; £5,500 too low.</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A42" s="43" t="s">
@@ -8722,7 +8878,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="104.0" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:28" ht="104.0" x14ac:dyDescent="0.2">
       <c r="A43" s="48" t="s">
         <v>1175</v>
       </c>
@@ -8781,6 +8937,14 @@
         <f>AVERAGE(R43:Y43)</f>
         <v>3216.0</v>
       </c>
+      <c r="AA43" s="40">
+        <v>2500</v>
+      </c>
+      <c r="AB43" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £2,563; Claycroft £3,869 sits between Std and High.</t>
+        </is>
+      </c>
     </row>
     <row r="44" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A44" s="48" t="s">
@@ -8874,7 +9038,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A46" s="48" t="s">
         <v>1188</v>
       </c>
@@ -8930,8 +9094,16 @@
         <f>AVERAGE(R46:Y46)</f>
         <v>5296.0</v>
       </c>
-    </row>
-    <row r="47" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="AA46" s="40">
+        <v>5300</v>
+      </c>
+      <c r="AB46" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside tender £5,296.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A47" s="48" t="s">
         <v>1194</v>
       </c>
@@ -8984,8 +9156,16 @@
         <f>AVERAGE(R47:Y47)</f>
         <v>10276.0</v>
       </c>
-    </row>
-    <row r="48" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
+      <c r="AA47" s="40">
+        <v>6000</v>
+      </c>
+      <c r="AB47" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court about £10,300 per tea point (8 assumed); your own review said £5,500.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" spans="1:28" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A48" s="21" t="s">
         <v>292</v>
       </c>
@@ -9045,8 +9225,16 @@
         <f>AVERAGE(R48:Y48)</f>
         <v>37.5</v>
       </c>
-    </row>
-    <row r="49" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA48" s="40">
+        <v>45</v>
+      </c>
+      <c r="AB48" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Riley Court £42, Claycroft £64, Co-op £7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A49" s="21" t="s">
         <v>1199</v>
       </c>
@@ -9100,6 +9288,14 @@
         <f>AVERAGE(R49:Y49)</f>
         <v>14.3</v>
       </c>
+      <c r="AA49" s="40">
+        <v>12</v>
+      </c>
+      <c r="AB49" s="22" t="inlineStr">
+        <is>
+          <t>Raise slightly. Riley Court £12, Co-op £16 (incl. graphics).</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:16" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A50" s="21" t="s">
@@ -9326,7 +9522,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="55" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A55" s="21" t="s">
         <v>1216</v>
       </c>
@@ -9374,6 +9570,14 @@
       <c r="Z55" s="40">
         <f>AVERAGE(R55:Y55)</f>
         <v>1438.0</v>
+      </c>
+      <c r="AA55" s="40">
+        <v>1000</v>
+      </c>
+      <c r="AB55" s="22" t="inlineStr">
+        <is>
+          <t>Raise. IBRB café servery £1,438 (bespoke stainless) = High; your own review said Std £1,000.</t>
+        </is>
       </c>
     </row>
     <row r="56" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -9690,7 +9894,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="140.25" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:28" ht="140.25" x14ac:dyDescent="0.2">
       <c r="A64" s="55" t="s">
         <v>1027</v>
       </c>
@@ -9749,6 +9953,14 @@
         <f>AVERAGE(R64:Y64)</f>
         <v>224.0</v>
       </c>
+      <c r="AA64" s="40">
+        <v>190</v>
+      </c>
+      <c r="AB64" s="22" t="inlineStr">
+        <is>
+          <t>Raise. CS whole heat pump M&amp;E package £224; enter as a figure, not = 5.1a × factor.</t>
+        </is>
+      </c>
     </row>
     <row r="65" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A65" s="55" t="s">
@@ -9800,7 +10012,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="66" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A66" s="55" t="s">
         <v>1252</v>
       </c>
@@ -9856,6 +10068,14 @@
         <f>AVERAGE(R66:Y66)</f>
         <v>134.7</v>
       </c>
+      <c r="AA66" s="40">
+        <v>120</v>
+      </c>
+      <c r="AB66" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £135 incl. new LTHW pipework, radiators and pumps off district heating.</t>
+        </is>
+      </c>
     </row>
     <row r="67" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A67" s="55" t="s">
@@ -10407,7 +10627,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="91.25" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:28" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A78" s="23" t="s">
         <v>1299</v>
       </c>
@@ -10475,8 +10695,16 @@
         <f>AVERAGE(R78:Y78)</f>
         <v>98.92</v>
       </c>
-    </row>
-    <row r="79" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA78" s="40">
+        <v>80</v>
+      </c>
+      <c r="AB78" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £105, IBRB £124 (small café); Claycroft £39 and Co-op £18 were partial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A79" s="23" t="s">
         <v>1304</v>
       </c>
@@ -10535,8 +10763,16 @@
         <f>AVERAGE(R79:Y79)</f>
         <v>20.0</v>
       </c>
-    </row>
-    <row r="80" spans="1:26" ht="78.5" x14ac:dyDescent="0.2">
+      <c r="AA79" s="40">
+        <v>19.5</v>
+      </c>
+      <c r="AB79" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" spans="1:28" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A80" s="21" t="s">
         <v>1672</v>
       </c>
@@ -10595,8 +10831,16 @@
         <f>AVERAGE(R80:Y80)</f>
         <v>122.75</v>
       </c>
-    </row>
-    <row r="81" spans="1:26" ht="91.25" x14ac:dyDescent="0.2">
+      <c r="AA80" s="40">
+        <v>100</v>
+      </c>
+      <c r="AB80" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court MVHR £172, Co-op £73, Claycroft out-turn £92.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" spans="1:28" ht="91.25" x14ac:dyDescent="0.2">
       <c r="A81" s="21" t="s">
         <v>1644</v>
       </c>
@@ -10655,8 +10899,16 @@
         <f>AVERAGE(R81:Y81)</f>
         <v>36.233333</v>
       </c>
-    </row>
-    <row r="82" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA81" s="40">
+        <v>22</v>
+      </c>
+      <c r="AB81" s="22" t="inlineStr">
+        <is>
+          <t>Raise slightly. Lakeside £18.5, Claycroft £28; Scarman £62 is toilet-area only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A82" s="21" t="s">
         <v>420</v>
       </c>
@@ -10710,8 +10962,16 @@
         <f>AVERAGE(R82:Y82)</f>
         <v>36.8</v>
       </c>
-    </row>
-    <row r="83" spans="1:26" ht="40.25" x14ac:dyDescent="0.2">
+      <c r="AA82" s="40">
+        <v>75</v>
+      </c>
+      <c r="AB82" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Riley Court £34 and Co-op £40 cooled only some rooms; no whole-building evidence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:28" ht="40.25" x14ac:dyDescent="0.2">
       <c r="A83" s="21" t="s">
         <v>373</v>
       </c>
@@ -10771,6 +11031,14 @@
         <f>AVERAGE(R83:Y83)</f>
         <v>24.966667</v>
       </c>
+      <c r="AA83" s="40">
+        <v>25</v>
+      </c>
+      <c r="AB83" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £59 (full BMS budget); Co-op £11.5; Claycroft £4 interfaces only.</t>
+        </is>
+      </c>
     </row>
     <row r="84" spans="1:15" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="55" t="s">
@@ -10893,7 +11161,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="87" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A87" s="23" t="s">
         <v>1328</v>
       </c>
@@ -10955,8 +11223,16 @@
         <f>AVERAGE(R87:Y87)</f>
         <v>133.525</v>
       </c>
-    </row>
-    <row r="88" spans="1:26" ht="116.75" x14ac:dyDescent="0.2">
+      <c r="AA87" s="40">
+        <v>126</v>
+      </c>
+      <c r="AB87" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Riley Court £131, Scarman £97, Co-op £89. IBRB £218 is one supply on a small room.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:28" ht="116.75" x14ac:dyDescent="0.2">
       <c r="A88" s="23" t="s">
         <v>1332</v>
       </c>
@@ -11015,6 +11291,14 @@
         <f>AVERAGE(R88:Y88)</f>
         <v>155.35</v>
       </c>
+      <c r="AA88" s="40">
+        <v>150</v>
+      </c>
+      <c r="AB88" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £153, Claycroft £158.</t>
+        </is>
+      </c>
     </row>
     <row r="89" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A89" s="23" t="s">
@@ -11059,7 +11343,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="90" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:28" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A90" s="23" t="s">
         <v>1338</v>
       </c>
@@ -11127,6 +11411,14 @@
         <f>AVERAGE(R90:Y90)</f>
         <v>105.36</v>
       </c>
+      <c r="AA90" s="40">
+        <v>80</v>
+      </c>
+      <c r="AB90" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Five projects £51–198 (median £84); £33 is far too low.</t>
+        </is>
+      </c>
     </row>
     <row r="91" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A91" s="23" t="s">
@@ -11460,7 +11752,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="65.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:28" ht="65.75" x14ac:dyDescent="0.2">
       <c r="A99" s="21" t="s">
         <v>507</v>
       </c>
@@ -11526,6 +11818,14 @@
         <f>AVERAGE(R99:Y99)</f>
         <v>46.44</v>
       </c>
+      <c r="AA99" s="40">
+        <v>35</v>
+      </c>
+      <c r="AB99" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £44, Claycroft £65, Scarman £77 for new systems; Lakeside £19 was partial.</t>
+        </is>
+      </c>
     </row>
     <row r="100" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A100" s="21" t="s">
@@ -11613,7 +11913,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="102" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A102" s="21" t="s">
         <v>1674</v>
       </c>
@@ -11673,8 +11973,16 @@
         <f>AVERAGE(R102:Y102)</f>
         <v>19.433333</v>
       </c>
-    </row>
-    <row r="103" spans="1:26" ht="53.0" x14ac:dyDescent="0.2">
+      <c r="AA102" s="40">
+        <v>20</v>
+      </c>
+      <c r="AB102" s="22" t="inlineStr">
+        <is>
+          <t>Raise slightly. Lakeside £19, Riley Court £34, IBRB £5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" spans="1:28" ht="53.0" x14ac:dyDescent="0.2">
       <c r="A103" s="21" t="s">
         <v>1640</v>
       </c>
@@ -11730,8 +12038,16 @@
         <f>AVERAGE(R103:Y103)</f>
         <v>21.9</v>
       </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.2" ht="53.0" customHeight="1">
+      <c r="AA103" s="40">
+        <v>25</v>
+      </c>
+      <c r="AB103" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £24.5, Claycroft £19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" spans="1:28" x14ac:dyDescent="0.2" ht="53.0" customHeight="1">
       <c r="A104" s="21" t="s">
         <v>563</v>
       </c>
@@ -11791,8 +12107,16 @@
         <f>AVERAGE(R104:Y104)</f>
         <v>28.1</v>
       </c>
-    </row>
-    <row r="105" spans="1:26" ht="53.0" x14ac:dyDescent="0.2">
+      <c r="AA104" s="40">
+        <v>20</v>
+      </c>
+      <c r="AB104" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £22, Co-op £58 (retail CCTV and alarm); Claycroft £4.5 minimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" spans="1:28" ht="53.0" x14ac:dyDescent="0.2">
       <c r="A105" s="23" t="s">
         <v>1381</v>
       </c>
@@ -11848,6 +12172,14 @@
         <f>AVERAGE(R105:Y105)</f>
         <v>112847.0</v>
       </c>
+      <c r="AA105" s="40">
+        <v>100000</v>
+      </c>
+      <c r="AB105" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Claycroft £112,850 for a replacement passenger lift; £40,000 is a third of that.</t>
+        </is>
+      </c>
     </row>
     <row r="106" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A106" s="23" t="s">
@@ -12540,7 +12872,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="123" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:28" ht="51" x14ac:dyDescent="0.2">
       <c r="A123" s="21" t="s">
         <v>1675</v>
       </c>
@@ -12595,8 +12927,16 @@
         <f>AVERAGE(R123:Y123)</f>
         <v>5.55</v>
       </c>
-    </row>
-    <row r="124" spans="1:26" ht="78.5" x14ac:dyDescent="0.2">
+      <c r="AA123" s="40">
+        <v>12</v>
+      </c>
+      <c r="AB123" s="22" t="inlineStr">
+        <is>
+          <t>Lower. CS £8, Co-op £3; most builder's work sits inside the M&amp;E prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" spans="1:28" ht="78.5" x14ac:dyDescent="0.2">
       <c r="A124" s="21" t="s">
         <v>1635</v>
       </c>
@@ -12649,6 +12989,14 @@
       <c r="Z124" s="40">
         <f>AVERAGE(R124:Y124)</f>
         <v>19.0</v>
+      </c>
+      <c r="AA124" s="40">
+        <v>27</v>
+      </c>
+      <c r="AB124" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Lakeside £27 (rewire of occupied flats); Claycroft £11.</t>
+        </is>
       </c>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.2">
@@ -12670,7 +13018,7 @@
       <c r="N125" s="26"/>
       <c r="O125" s="27"/>
     </row>
-    <row r="126" spans="1:26" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:28" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A126" s="23" t="s">
         <v>1435</v>
       </c>
@@ -12724,6 +13072,14 @@
         <f>AVERAGE(R126:Y126)</f>
         <v>48.0</v>
       </c>
+      <c r="AA126" s="40">
+        <v>45</v>
+      </c>
+      <c r="AB126" s="22" t="inlineStr">
+        <is>
+          <t>Keep. CS brick remedials £48.</t>
+        </is>
+      </c>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A127" s="23" t="s">
@@ -12828,7 +13184,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="129" spans="1:26" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A129" s="21" t="s">
         <v>1447</v>
       </c>
@@ -12878,6 +13234,14 @@
       <c r="Z129" s="40">
         <f>AVERAGE(R129:Y129)</f>
         <v>53.7</v>
+      </c>
+      <c r="AA129" s="40">
+        <v>60</v>
+      </c>
+      <c r="AB129" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Riley Court £54.</t>
+        </is>
       </c>
     </row>
     <row r="130" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">
@@ -13032,7 +13396,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="134" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A134" s="21" t="s">
         <v>691</v>
       </c>
@@ -13083,8 +13447,16 @@
         <f>AVERAGE(R134:Y134)</f>
         <v>35.4</v>
       </c>
-    </row>
-    <row r="135" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="AA134" s="40">
+        <v>15</v>
+      </c>
+      <c r="AB134" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £35 for new internal below-ground drainage (one project).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A135" s="21" t="s">
         <v>656</v>
       </c>
@@ -13135,6 +13507,14 @@
         <f>AVERAGE(R135:Y135)</f>
         <v>67.6</v>
       </c>
+      <c r="AA135" s="40">
+        <v>25</v>
+      </c>
+      <c r="AB135" s="22" t="inlineStr">
+        <is>
+          <t>Raise. Riley Court £68 for new district heating and water mains (one project; site-specific).</t>
+        </is>
+      </c>
     </row>
     <row r="136" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A136" s="23" t="s">
@@ -13501,7 +13881,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="145" spans="1:26" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A145" s="21" t="s">
         <v>696</v>
       </c>
@@ -13554,6 +13934,14 @@
       <c r="Z145" s="40">
         <f>AVERAGE(R145:Y145)</f>
         <v>2.1</v>
+      </c>
+      <c r="AA145" s="40">
+        <v>30</v>
+      </c>
+      <c r="AB145" s="22" t="inlineStr">
+        <is>
+          <t>Keep. Whitefields £2 was topsoil and seed only, not planting.</t>
+        </is>
       </c>
     </row>
     <row r="146" spans="1:15" ht="25.5" x14ac:dyDescent="0.2">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1791">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5401,6 +5401,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.12 (October 2026)</t>
   </si>
 </sst>
 </file>
@@ -6021,7 +6024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -6032,7 +6035,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -6723,136 +6726,148 @@
     <row r="81" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="inlineStr">
         <is>
+          <t>v5.12 — 4 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Lakeside tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
           <t>v5.11 — 4 Oct 2026</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
+      <c r="B82" s="17" t="inlineStr">
         <is>
           <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %). Columns AA–AB: Claude's suggested Refurb &amp; Fit-out Std rate and the reason, on all 47 rows (25 raise, 2 lower, 20 keep).</t>
         </is>
       </c>
     </row>
-    <row r="82" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="17" t="s">
+    <row r="83" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="s">
         <v>1778</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B83" s="17" t="s">
         <v>1779</v>
       </c>
-      <c r="C82" s="60"/>
-    </row>
-    <row r="83" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="17" t="s">
+      <c r="C83" s="60"/>
+    </row>
+    <row r="84" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B84" s="17" t="s">
         <v>1783</v>
-      </c>
-      <c r="C83" s="60"/>
-    </row>
-    <row r="84" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
-        <v>1722</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>1737</v>
       </c>
       <c r="C84" s="60"/>
     </row>
     <row r="85" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A85" s="17" t="s">
-        <v>1711</v>
+        <v>1722</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>1712</v>
+        <v>1737</v>
       </c>
       <c r="C85" s="60"/>
     </row>
     <row r="86" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A86" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C86" s="60"/>
+    </row>
+    <row r="87" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A87" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B87" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C86" s="60"/>
-    </row>
-    <row r="87" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A87" s="15" t="s">
+      <c r="C87" s="60"/>
+    </row>
+    <row r="88" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A88" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B88" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C87" s="33"/>
-    </row>
-    <row r="88" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
+      <c r="C88" s="33"/>
+    </row>
+    <row r="89" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A89" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C88" s="33"/>
-    </row>
-    <row r="89" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
+      <c r="C89" s="33"/>
+    </row>
+    <row r="90" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A90" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B90" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C89" s="33"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
+      <c r="C90" s="33"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C90" s="33"/>
-    </row>
-    <row r="91" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
+      <c r="C91" s="33"/>
+    </row>
+    <row r="92" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A92" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C91" s="33"/>
-    </row>
-    <row r="92" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A92" s="15" t="s">
+      <c r="C92" s="33"/>
+    </row>
+    <row r="93" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A93" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B93" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C92" s="33"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C93" s="33"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A94" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B94" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" s="33"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B95" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C94" s="33"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="15"/>
-      <c r="B95" s="17"/>
       <c r="C95" s="33"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="15"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7104,15 +7119,17 @@
       </c>
       <c r="H8" s="39"/>
       <c r="I8" s="40">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="J8" s="39"/>
       <c r="K8" s="40">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L8" s="39"/>
-      <c r="M8" s="22" t="s">
-        <v>1076</v>
+      <c r="M8" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N8" s="22" t="s">
         <v>1080</v>
@@ -7834,22 +7851,24 @@
         <v>705</v>
       </c>
       <c r="H25" s="39">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="I25" s="40">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="J25" s="39">
-        <v>200</v>
+        <v>345</v>
       </c>
       <c r="K25" s="40">
-        <v>220</v>
+        <v>380</v>
       </c>
       <c r="L25" s="39">
-        <v>300</v>
-      </c>
-      <c r="M25" s="22" t="s">
-        <v>1098</v>
+        <v>518</v>
+      </c>
+      <c r="M25" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N25" s="22" t="s">
         <v>1132</v>
@@ -7958,22 +7977,24 @@
         <v>1075</v>
       </c>
       <c r="H27" s="39">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I27" s="40">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J27" s="39">
-        <v>110</v>
+        <v>183</v>
       </c>
       <c r="K27" s="40">
-        <v>220</v>
+        <v>367</v>
       </c>
       <c r="L27" s="39">
-        <v>340</v>
-      </c>
-      <c r="M27" s="22" t="s">
-        <v>1098</v>
+        <v>567</v>
+      </c>
+      <c r="M27" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N27" s="22" t="s">
         <v>1135</v>
@@ -8024,22 +8045,24 @@
         <v>1075</v>
       </c>
       <c r="H28" s="39">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I28" s="40">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="J28" s="39">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="K28" s="40">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="L28" s="39">
-        <v>260</v>
-      </c>
-      <c r="M28" s="22" t="s">
-        <v>1098</v>
+        <v>303</v>
+      </c>
+      <c r="M28" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N28" s="22" t="s">
         <v>1138</v>
@@ -8093,22 +8116,24 @@
         <v>1075</v>
       </c>
       <c r="H29" s="39">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="I29" s="40">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="J29" s="39">
-        <v>160</v>
+        <v>218</v>
       </c>
       <c r="K29" s="40">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="L29" s="39">
-        <v>160</v>
-      </c>
-      <c r="M29" s="22" t="s">
-        <v>1098</v>
+        <v>218</v>
+      </c>
+      <c r="M29" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N29" s="22" t="s">
         <v>1141</v>
@@ -8156,22 +8181,24 @@
         <v>1075</v>
       </c>
       <c r="H30" s="39">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="I30" s="40">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J30" s="39">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="K30" s="40">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L30" s="39">
-        <v>120</v>
-      </c>
-      <c r="M30" s="22" t="s">
-        <v>1098</v>
+        <v>200</v>
+      </c>
+      <c r="M30" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N30" s="22" t="s">
         <v>1145</v>
@@ -8394,22 +8421,24 @@
         <v>1075</v>
       </c>
       <c r="H34" s="39">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I34" s="40">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J34" s="39">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="K34" s="40">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="L34" s="39">
-        <v>200</v>
-      </c>
-      <c r="M34" s="22" t="s">
-        <v>1118</v>
+        <v>227</v>
+      </c>
+      <c r="M34" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N34" s="22" t="s">
         <v>1156</v>
@@ -8577,22 +8606,24 @@
         <v>1075</v>
       </c>
       <c r="H37" s="39">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I37" s="40">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="J37" s="39">
-        <v>140</v>
+        <v>224</v>
       </c>
       <c r="K37" s="40">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="L37" s="39">
-        <v>140</v>
-      </c>
-      <c r="M37" s="22" t="s">
-        <v>1098</v>
+        <v>224</v>
+      </c>
+      <c r="M37" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N37" s="22" t="s">
         <v>1162</v>
@@ -8771,7 +8802,7 @@
       </c>
       <c r="AB40" s="22" t="inlineStr">
         <is>
-          <t>Raise. Scarman £7,650 (high spec) and Riley Court £14,600 incl. tiling both far above £3,950.</t>
+          <t>Keep as is (owner, 4 Oct 2026).</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8862,7 @@
       </c>
       <c r="AB41" s="22" t="inlineStr">
         <is>
-          <t>Raise. Riley Court £16,000 per accessible WC incl. tiling and shower; £5,500 too low.</t>
+          <t>Keep as is (owner, 4 Oct 2026).</t>
         </is>
       </c>
     </row>
@@ -9126,22 +9157,24 @@
         <v>1626</v>
       </c>
       <c r="H47" s="50">
-        <v>2500</v>
+        <v>3750</v>
       </c>
       <c r="I47" s="51">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="J47" s="50">
-        <v>7000</v>
+        <v>10500</v>
       </c>
       <c r="K47" s="51">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="L47" s="50">
-        <v>7000</v>
-      </c>
-      <c r="M47" s="49" t="s">
-        <v>1174</v>
+        <v>10500</v>
+      </c>
+      <c r="M47" s="49" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N47" s="49" t="s">
         <v>1195</v>
@@ -9255,22 +9288,24 @@
         <v>1075</v>
       </c>
       <c r="H49" s="39">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" s="40">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J49" s="39">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K49" s="40">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L49" s="39">
-        <v>15</v>
-      </c>
-      <c r="M49" s="22" t="s">
-        <v>1179</v>
+        <v>18</v>
+      </c>
+      <c r="M49" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N49" s="22" t="s">
         <v>1202</v>
@@ -9543,22 +9578,24 @@
         <v>1219</v>
       </c>
       <c r="H55" s="39">
-        <v>373</v>
+        <v>541</v>
       </c>
       <c r="I55" s="40">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="J55" s="39">
-        <v>1455</v>
+        <v>2100</v>
       </c>
       <c r="K55" s="40">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="L55" s="39">
-        <v>1455</v>
-      </c>
-      <c r="M55" s="22" t="s">
-        <v>1179</v>
+        <v>2100</v>
+      </c>
+      <c r="M55" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N55" s="22"/>
       <c r="O55" s="24" t="s">
@@ -9917,27 +9954,24 @@
         <v>1075</v>
       </c>
       <c r="H64" s="57">
-        <f>H63*1.3</f>
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="I64" s="58">
-        <f>I63*1.3</f>
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="J64" s="57">
-        <f>J63*1.3</f>
-        <v>175.5</v>
+        <v>427</v>
       </c>
       <c r="K64" s="58">
-        <f>K63*1.3</f>
-        <v>78</v>
+        <v>190</v>
       </c>
       <c r="L64" s="57">
-        <f>L63*1.3</f>
-        <v>136.5</v>
-      </c>
-      <c r="M64" s="56" t="s">
-        <v>1247</v>
+        <v>332</v>
+      </c>
+      <c r="M64" s="56" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N64" s="56"/>
       <c r="O64" s="59" t="s">
@@ -10035,27 +10069,24 @@
         <v>1075</v>
       </c>
       <c r="H66" s="57">
-        <f>H63*0.9</f>
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="I66" s="58">
-        <f>I63*0.9</f>
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="J66" s="57">
-        <f>J63*0.9</f>
-        <v>121.5</v>
+        <v>270</v>
       </c>
       <c r="K66" s="58">
-        <f>K63*0.9</f>
-        <v>54</v>
+        <v>120</v>
       </c>
       <c r="L66" s="57">
-        <f>L63*0.9</f>
-        <v>94.5</v>
-      </c>
-      <c r="M66" s="56" t="s">
-        <v>1255</v>
+        <v>210</v>
+      </c>
+      <c r="M66" s="56" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N66" s="56"/>
       <c r="O66" s="59" t="s">
@@ -10251,23 +10282,23 @@
       </c>
       <c r="H70" s="57">
         <f>H64*0.45</f>
-        <v>17.55</v>
+        <v>42.75</v>
       </c>
       <c r="I70" s="58">
         <f>I64*0.45</f>
-        <v>35.1</v>
+        <v>85.5</v>
       </c>
       <c r="J70" s="57">
         <f>J64*0.45</f>
-        <v>78.975000000000009</v>
+        <v>192.15</v>
       </c>
       <c r="K70" s="58">
         <f>K64*0.45</f>
-        <v>35.1</v>
+        <v>85.5</v>
       </c>
       <c r="L70" s="57">
         <f>L64*0.45</f>
-        <v>61.425000000000004</v>
+        <v>149.4</v>
       </c>
       <c r="M70" s="56" t="s">
         <v>1271</v>
@@ -10301,23 +10332,23 @@
       </c>
       <c r="H71" s="57">
         <f>H64*0.3</f>
-        <v>11.7</v>
+        <v>28.5</v>
       </c>
       <c r="I71" s="58">
         <f>I64*0.3</f>
-        <v>23.4</v>
+        <v>57</v>
       </c>
       <c r="J71" s="57">
         <f>J64*0.3</f>
-        <v>52.65</v>
+        <v>128.1</v>
       </c>
       <c r="K71" s="58">
         <f>K64*0.3</f>
-        <v>23.4</v>
+        <v>57</v>
       </c>
       <c r="L71" s="57">
         <f>L64*0.3</f>
-        <v>40.949999999999996</v>
+        <v>99.6</v>
       </c>
       <c r="M71" s="56" t="s">
         <v>1275</v>
@@ -10451,23 +10482,23 @@
       </c>
       <c r="H74" s="57">
         <f t="shared" si="0"/>
-        <v>8.1</v>
+        <v>18.0</v>
       </c>
       <c r="I74" s="58">
         <f t="shared" si="0"/>
-        <v>16.2</v>
+        <v>36.0</v>
       </c>
       <c r="J74" s="57">
         <f t="shared" si="0"/>
-        <v>36.449999999999996</v>
+        <v>81.0</v>
       </c>
       <c r="K74" s="58">
         <f t="shared" si="0"/>
-        <v>16.2</v>
+        <v>36.0</v>
       </c>
       <c r="L74" s="57">
         <f t="shared" si="0"/>
-        <v>28.349999999999998</v>
+        <v>63.0</v>
       </c>
       <c r="M74" s="56" t="s">
         <v>1287</v>
@@ -10501,23 +10532,23 @@
       </c>
       <c r="H75" s="57">
         <f>H66*0.3</f>
-        <v>8.1</v>
+        <v>18</v>
       </c>
       <c r="I75" s="58">
         <f>I66*0.3</f>
-        <v>16.2</v>
+        <v>36</v>
       </c>
       <c r="J75" s="57">
         <f>J66*0.3</f>
-        <v>36.449999999999996</v>
+        <v>81</v>
       </c>
       <c r="K75" s="58">
         <f>K66*0.3</f>
-        <v>16.2</v>
+        <v>36</v>
       </c>
       <c r="L75" s="57">
         <f>L66*0.3</f>
-        <v>28.349999999999998</v>
+        <v>63</v>
       </c>
       <c r="M75" s="56" t="s">
         <v>1287</v>
@@ -10650,22 +10681,24 @@
         <v>1075</v>
       </c>
       <c r="H78" s="39">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I78" s="40">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="J78" s="39">
-        <v>180</v>
+        <v>222</v>
       </c>
       <c r="K78" s="40">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L78" s="39">
-        <v>90</v>
-      </c>
-      <c r="M78" s="22" t="s">
-        <v>1179</v>
+        <v>111</v>
+      </c>
+      <c r="M78" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N78" s="22" t="s">
         <v>1303</v>
@@ -10727,27 +10760,24 @@
         <v>1075</v>
       </c>
       <c r="H79" s="39">
-        <f>H78*0.3</f>
         <v>9</v>
       </c>
       <c r="I79" s="40">
-        <f>I78*0.3</f>
         <v>19.5</v>
       </c>
       <c r="J79" s="39">
-        <f>J78*0.3</f>
         <v>54</v>
       </c>
       <c r="K79" s="40">
-        <f>K78*0.3</f>
         <v>9</v>
       </c>
       <c r="L79" s="39">
-        <f>L78*0.3</f>
         <v>27</v>
       </c>
-      <c r="M79" s="22" t="s">
-        <v>1307</v>
+      <c r="M79" s="22" t="inlineStr">
+        <is>
+          <t>Tender – Lakeside S&amp;F (Sep 2026)</t>
+        </is>
       </c>
       <c r="N79" s="22"/>
       <c r="O79" s="24" t="s">
@@ -10795,22 +10825,24 @@
         <v>1075</v>
       </c>
       <c r="H80" s="39">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="I80" s="40">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="J80" s="39">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="K80" s="40">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="L80" s="39">
-        <v>70</v>
-      </c>
-      <c r="M80" s="22" t="s">
-        <v>1179</v>
+        <v>117</v>
+      </c>
+      <c r="M80" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N80" s="22" t="s">
         <v>1310</v>
@@ -10832,7 +10864,7 @@
         <v>122.75</v>
       </c>
       <c r="AA80" s="40">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AB80" s="22" t="inlineStr">
         <is>
@@ -10863,20 +10895,22 @@
         <v>1075</v>
       </c>
       <c r="H81" s="39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I81" s="40">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J81" s="39">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K81" s="40">
         <v>0</v>
       </c>
       <c r="L81" s="39"/>
-      <c r="M81" s="22" t="s">
-        <v>1637</v>
+      <c r="M81" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N81" s="22"/>
       <c r="O81" s="24" t="s">
@@ -10992,22 +11026,24 @@
         <v>1075</v>
       </c>
       <c r="H83" s="39">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I83" s="40">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J83" s="39">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K83" s="40">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="L83" s="39">
-        <v>22</v>
-      </c>
-      <c r="M83" s="22" t="s">
-        <v>1179</v>
+        <v>37</v>
+      </c>
+      <c r="M83" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N83" s="22" t="s">
         <v>1316</v>
@@ -11366,22 +11402,24 @@
         <v>1075</v>
       </c>
       <c r="H90" s="39">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="I90" s="40">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="J90" s="39">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="K90" s="40">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="L90" s="39">
-        <v>52</v>
-      </c>
-      <c r="M90" s="22" t="s">
-        <v>1179</v>
+        <v>126</v>
+      </c>
+      <c r="M90" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N90" s="22" t="s">
         <v>1341</v>
@@ -11444,23 +11482,23 @@
       </c>
       <c r="H91" s="39">
         <f>H90*0.75</f>
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I91" s="40">
         <f>I90*0.75</f>
-        <v>24.75</v>
+        <v>60</v>
       </c>
       <c r="J91" s="39">
         <f>J90*0.75</f>
-        <v>39</v>
+        <v>94.5</v>
       </c>
       <c r="K91" s="40">
         <f>K90*0.75</f>
-        <v>24.75</v>
+        <v>60</v>
       </c>
       <c r="L91" s="39">
         <f>L90*0.75</f>
-        <v>39</v>
+        <v>94.5</v>
       </c>
       <c r="M91" s="22" t="s">
         <v>1345</v>
@@ -11773,22 +11811,24 @@
         <v>1075</v>
       </c>
       <c r="H99" s="39">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I99" s="40">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J99" s="39">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="K99" s="40">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L99" s="39">
-        <v>25</v>
-      </c>
-      <c r="M99" s="22" t="s">
-        <v>1179</v>
+        <v>49</v>
+      </c>
+      <c r="M99" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N99" s="22" t="s">
         <v>1371</v>
@@ -11934,22 +11974,24 @@
         <v>1075</v>
       </c>
       <c r="H102" s="39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I102" s="40">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J102" s="39">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K102" s="40">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L102" s="39">
-        <v>30</v>
-      </c>
-      <c r="M102" s="22" t="s">
-        <v>1179</v>
+        <v>33</v>
+      </c>
+      <c r="M102" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N102" s="22" t="s">
         <v>1379</v>
@@ -12068,22 +12110,24 @@
         <v>1075</v>
       </c>
       <c r="H104" s="39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I104" s="40">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J104" s="39">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K104" s="40">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L104" s="39">
-        <v>20</v>
-      </c>
-      <c r="M104" s="22" t="s">
-        <v>1179</v>
+        <v>27</v>
+      </c>
+      <c r="M104" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N104" s="22" t="s">
         <v>1316</v>
@@ -12139,22 +12183,24 @@
         <v>1385</v>
       </c>
       <c r="H105" s="39">
-        <v>25000</v>
+        <v>37500</v>
       </c>
       <c r="I105" s="40">
-        <v>40000</v>
+        <v>60000</v>
       </c>
       <c r="J105" s="39">
+        <v>90000</v>
+      </c>
+      <c r="K105" s="40">
         <v>60000</v>
       </c>
-      <c r="K105" s="40">
-        <v>40000</v>
-      </c>
       <c r="L105" s="39">
-        <v>60000</v>
-      </c>
-      <c r="M105" s="22" t="s">
-        <v>1179</v>
+        <v>90000</v>
+      </c>
+      <c r="M105" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N105" s="22" t="s">
         <v>1386</v>
@@ -12173,7 +12219,7 @@
         <v>112847.0</v>
       </c>
       <c r="AA105" s="40">
-        <v>100000</v>
+        <v>60000</v>
       </c>
       <c r="AB105" s="22" t="inlineStr">
         <is>
@@ -12891,22 +12937,24 @@
         <v>1075</v>
       </c>
       <c r="H123" s="39">
+        <v>5</v>
+      </c>
+      <c r="I123" s="40">
+        <v>12</v>
+      </c>
+      <c r="J123" s="39">
+        <v>20</v>
+      </c>
+      <c r="K123" s="40">
         <v>8</v>
       </c>
-      <c r="I123" s="40">
-        <v>18</v>
-      </c>
-      <c r="J123" s="39">
-        <v>30</v>
-      </c>
-      <c r="K123" s="40">
-        <v>12</v>
-      </c>
       <c r="L123" s="39">
-        <v>24</v>
-      </c>
-      <c r="M123" s="22" t="s">
-        <v>1179</v>
+        <v>16</v>
+      </c>
+      <c r="M123" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N123" s="22" t="s">
         <v>1433</v>
@@ -13417,22 +13465,24 @@
         <v>1075</v>
       </c>
       <c r="H134" s="39">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I134" s="40">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J134" s="39">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K134" s="40">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L134" s="39">
-        <v>15</v>
-      </c>
-      <c r="M134" s="22" t="s">
-        <v>1179</v>
+        <v>25</v>
+      </c>
+      <c r="M134" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N134" s="22" t="s">
         <v>1462</v>
@@ -13448,7 +13498,7 @@
         <v>35.4</v>
       </c>
       <c r="AA134" s="40">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AB134" s="22" t="inlineStr">
         <is>
@@ -13477,22 +13527,24 @@
         <v>1075</v>
       </c>
       <c r="H135" s="39">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="I135" s="40">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J135" s="39">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K135" s="40">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L135" s="39">
-        <v>20</v>
-      </c>
-      <c r="M135" s="22" t="s">
-        <v>1179</v>
+        <v>50</v>
+      </c>
+      <c r="M135" s="22" t="inlineStr">
+        <is>
+          <t>Your figure</t>
+        </is>
       </c>
       <c r="N135" s="22" t="s">
         <v>1465</v>
@@ -14320,7 +14372,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>507</v>
+        <v>298</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4236" uniqueCount="1791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1797">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5404,6 +5404,24 @@
   </si>
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.12 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGGEST: S-0020 Fire stopping · SUGGEST: S-0047 Emergency lighting · SUGGEST: S-0001 Asbestos removal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGGEST: S-0041 Ventilation · SUGGEST: S-0019 Internal doors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGGEST: S-0041 Ventilation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUGGEST: S-0020 Fire stopping · SUGGEST: S-0047 Emergency lighting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.13 (October 2026)</t>
   </si>
 </sst>
 </file>
@@ -6035,7 +6053,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1790</v>
+        <v>1796</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -14372,7 +14390,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>298</v>
+        <v>365</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -14383,7 +14401,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1789</v>
+        <v>1795</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -21229,7 +21247,9 @@
       <c r="J93" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K93" s="15"/>
+      <c r="K93" s="15" t="s">
+        <v>1791</v>
+      </c>
       <c r="L93" s="15" t="s">
         <v>1701</v>
       </c>
@@ -22319,7 +22339,9 @@
       <c r="J123" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K123" s="15"/>
+      <c r="K123" s="15" t="s">
+        <v>1792</v>
+      </c>
       <c r="L123" s="15" t="s">
         <v>1702</v>
       </c>
@@ -22353,7 +22375,9 @@
       <c r="J124" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K124" s="15"/>
+      <c r="K124" s="15" t="s">
+        <v>1792</v>
+      </c>
       <c r="L124" s="15" t="s">
         <v>265</v>
       </c>
@@ -22425,7 +22449,9 @@
       <c r="J126" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K126" s="15"/>
+      <c r="K126" s="15" t="s">
+        <v>1792</v>
+      </c>
       <c r="L126" s="15" t="s">
         <v>1703</v>
       </c>
@@ -22461,7 +22487,9 @@
       <c r="J127" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K127" s="15"/>
+      <c r="K127" s="15" t="s">
+        <v>1793</v>
+      </c>
       <c r="L127" s="15" t="s">
         <v>280</v>
       </c>
@@ -23853,7 +23881,9 @@
       <c r="J166" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K166" s="15"/>
+      <c r="K166" s="15" t="s">
+        <v>1794</v>
+      </c>
       <c r="L166" s="15" t="s">
         <v>452</v>
       </c>
@@ -23889,7 +23919,9 @@
       <c r="J167" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="K167" s="15"/>
+      <c r="K167" s="15" t="s">
+        <v>1794</v>
+      </c>
       <c r="L167" s="15" t="s">
         <v>1704</v>
       </c>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1799">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5422,6 +5422,12 @@
   </si>
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.13 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.14 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
   </si>
 </sst>
 </file>
@@ -6053,7 +6059,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -14339,7 +14345,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G203"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14390,7 +14396,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>365</v>
+        <v>437</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -14401,7 +14407,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -16170,14 +16176,16 @@
       <c r="C131" s="2" t="s">
         <v>944</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>945</v>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Base 7% — vacant, no restrictions, relaxed programme</t>
+        </is>
       </c>
       <c r="E131" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F131" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -16197,7 +16205,7 @@
         <v>2</v>
       </c>
       <c r="F132" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -16237,7 +16245,7 @@
         <v>0.5</v>
       </c>
       <c r="F134" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -16257,7 +16265,7 @@
         <v>0.5</v>
       </c>
       <c r="F135" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -16277,172 +16285,196 @@
         <v>0.5</v>
       </c>
       <c r="F136" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>955</v>
+        <v>946</v>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Q2.3 has ≥4 M&amp;E items (complex services)</t>
+        </is>
       </c>
       <c r="E137" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F137" s="2">
         <v>11</v>
       </c>
-      <c r="F137" s="2"/>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>956</v>
+        <v>946</v>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Q1.4 = Pre-1900 OR Q3.4 includes Listed Building Consent (heritage complexity)</t>
+        </is>
       </c>
       <c r="E138" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="F138" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="F138" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>952</v>
+        <v>942</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>954</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>957</v>
+        <v>946</v>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Q4.1 = Hard deadline (condensed programme)</t>
+        </is>
       </c>
       <c r="E139" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="F139" s="2"/>
+        <v>1.5</v>
+      </c>
+      <c r="F139" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>960</v>
+        <v>946</v>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Q4.4 top priority = Speed (condensed programme)</t>
+        </is>
       </c>
       <c r="E140" s="2">
-        <v>13.5</v>
-      </c>
-      <c r="F140" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="F140" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>961</v>
+        <v>946</v>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Region = Outer London</t>
+        </is>
       </c>
       <c r="E141" s="2">
-        <v>11.5</v>
-      </c>
-      <c r="F141" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="F141" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>962</v>
+        <v>946</v>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Region = Inner London</t>
+        </is>
       </c>
       <c r="E142" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="F142" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="F142" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>944</v>
+        <v>954</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="E143" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F143" s="2"/>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1046</v>
+        <v>956</v>
       </c>
       <c r="E144" s="2">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F144" s="2"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="E145" s="2">
-        <v>1</v>
+        <v>8.5</v>
       </c>
       <c r="F145" s="2"/>
     </row>
-    <row r="146" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>958</v>
       </c>
@@ -16450,121 +16482,121 @@
         <v>959</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="E146" s="2">
-        <v>2</v>
+        <v>13.5</v>
       </c>
       <c r="F146" s="2"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>944</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="E147" s="2">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="F147" s="2"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>944</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="E148" s="2">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="F148" s="2"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>944</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>970</v>
+        <v>963</v>
       </c>
       <c r="E149" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F149" s="2"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>971</v>
+        <v>1046</v>
       </c>
       <c r="E150" s="2">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F150" s="2"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>966</v>
+        <v>958</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>967</v>
+        <v>959</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
       <c r="E151" s="2">
+        <v>1</v>
+      </c>
+      <c r="F151" s="2"/>
+    </row>
+    <row r="152" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E152" s="2">
         <v>2</v>
-      </c>
-      <c r="F151" s="2"/>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" s="2" t="s">
-        <v>966</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>944</v>
-      </c>
-      <c r="D152" s="2" t="s">
-        <v>973</v>
-      </c>
-      <c r="E152" s="2">
-        <v>3</v>
       </c>
       <c r="F152" s="2"/>
     </row>
@@ -16576,17 +16608,17 @@
         <v>967</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="E153" s="2">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="F153" s="2"/>
     </row>
-    <row r="154" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>966</v>
       </c>
@@ -16597,7 +16629,7 @@
         <v>944</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="E154" s="2">
         <v>4</v>
@@ -16606,123 +16638,111 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>944</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="E155" s="2">
-        <v>5</v>
-      </c>
-      <c r="F155" s="2">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F155" s="2"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>979</v>
+        <v>971</v>
       </c>
       <c r="E156" s="2">
-        <v>2</v>
-      </c>
-      <c r="F156" s="2">
-        <v>10</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F156" s="2"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="E157" s="2">
         <v>2</v>
       </c>
-      <c r="F157" s="2">
-        <v>10</v>
-      </c>
+      <c r="F157" s="2"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>981</v>
+        <v>973</v>
       </c>
       <c r="E158" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F158" s="2">
-        <v>10</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F158" s="2"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>946</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>982</v>
+        <v>974</v>
       </c>
       <c r="E159" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F159" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="F159" s="2"/>
+    </row>
+    <row r="160" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>983</v>
+        <v>975</v>
       </c>
       <c r="E160" s="2">
-        <v>1</v>
-      </c>
-      <c r="F160" s="2">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F160" s="2"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
@@ -16732,13 +16752,13 @@
         <v>977</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="E161" s="2">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="F161" s="2">
         <v>10</v>
@@ -16755,10 +16775,10 @@
         <v>946</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="E162" s="2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F162" s="2">
         <v>10</v>
@@ -16775,10 +16795,10 @@
         <v>946</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="E163" s="2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F163" s="2">
         <v>10</v>
@@ -16795,10 +16815,10 @@
         <v>946</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="E164" s="2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F164" s="2">
         <v>10</v>
@@ -16815,10 +16835,10 @@
         <v>946</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="E165" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F165" s="2">
         <v>10</v>
@@ -16835,153 +16855,153 @@
         <v>946</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>947</v>
+        <v>983</v>
       </c>
       <c r="E166" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F166" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>989</v>
+        <v>976</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>990</v>
+        <v>977</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>991</v>
+        <v>946</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>992</v>
+        <v>984</v>
       </c>
       <c r="E167" s="2">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="F167" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>995</v>
+        <v>946</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="E168" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F168" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>995</v>
+        <v>946</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="E169" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F169" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>995</v>
+        <v>946</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>998</v>
+        <v>987</v>
       </c>
       <c r="E170" s="2">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="F170" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>994</v>
+        <v>977</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>995</v>
+        <v>946</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="E171" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F171" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>993</v>
+        <v>976</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>1000</v>
+        <v>977</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>995</v>
+        <v>946</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>1001</v>
+        <v>947</v>
       </c>
       <c r="E172" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F172" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
       <c r="E173" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F173" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -16989,16 +17009,16 @@
         <v>993</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>995</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="E174" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F174" s="2">
         <v>12</v>
@@ -17009,16 +17029,16 @@
         <v>993</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>995</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>1004</v>
+        <v>997</v>
       </c>
       <c r="E175" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F175" s="2">
         <v>12</v>
@@ -17029,185 +17049,203 @@
         <v>993</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>995</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>1005</v>
+        <v>998</v>
       </c>
       <c r="E176" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F176" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="E177" s="2">
+        <v>6</v>
+      </c>
+      <c r="F177" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E178" s="2">
+        <v>1</v>
+      </c>
+      <c r="F178" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E179" s="2">
+        <v>2</v>
+      </c>
+      <c r="F179" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E180" s="2">
+        <v>3</v>
+      </c>
+      <c r="F180" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E181" s="2">
+        <v>4</v>
+      </c>
+      <c r="F181" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E182" s="2">
+        <v>5</v>
+      </c>
+      <c r="F182" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
         <v>1006</v>
       </c>
-      <c r="B177" s="2" t="s">
+      <c r="B183" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="C177" s="2" t="s">
+      <c r="C183" s="2" t="s">
         <v>991</v>
       </c>
-      <c r="D177" s="2" t="s">
+      <c r="D183" s="2" t="s">
         <v>1008</v>
       </c>
-      <c r="E177" s="2">
+      <c r="E183" s="2">
         <v>20</v>
       </c>
-      <c r="F177" s="2">
+      <c r="F183" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A179" s="3" t="s">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B185" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="6" t="s">
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="6" t="s">
         <v>1011</v>
       </c>
-      <c r="B180" s="6" t="s">
+      <c r="B186" s="6" t="s">
         <v>1012</v>
       </c>
-      <c r="C180" s="6" t="s">
+      <c r="C186" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="D180" s="6" t="s">
+      <c r="D186" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="E180" s="6" t="s">
+      <c r="E186" s="6" t="s">
         <v>751</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A182" s="2" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>1019</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E182" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E184" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>1033</v>
+        <v>291</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>1034</v>
+        <v>1015</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>1016</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1035</v>
+        <v>1017</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>752</v>
@@ -17215,126 +17253,228 @@
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>1036</v>
+        <v>1018</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>1016</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>1039</v>
+        <v>1021</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>1016</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A190" s="30" t="s">
-        <v>735</v>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>1024</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>734</v>
+        <v>1025</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>1016</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A196" s="30" t="s">
+        <v>735</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D196" s="2" t="s">
         <v>1630</v>
       </c>
-      <c r="E190" s="30" t="s">
+      <c r="E196" s="30" t="s">
         <v>1629</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="3" t="s">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="3" t="s">
         <v>1047</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B198" s="3" t="s">
         <v>1048</v>
       </c>
-      <c r="C192" s="4"/>
-      <c r="D192" s="4"/>
-      <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="6" t="s">
+      <c r="C198" s="4"/>
+      <c r="D198" s="4"/>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+      <c r="G198" s="4"/>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A199" s="6" t="s">
         <v>1049</v>
       </c>
-      <c r="B193" s="6" t="s">
+      <c r="B199" s="6" t="s">
         <v>819</v>
       </c>
-      <c r="C193" s="6" t="s">
+      <c r="C199" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="D193" s="6" t="s">
+      <c r="D199" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="194" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
+    <row r="200" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
         <v>942</v>
       </c>
-      <c r="B194" s="2">
+      <c r="B200" s="2">
         <v>0.9</v>
       </c>
-      <c r="C194" s="2">
+      <c r="C200" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D194" s="2" t="s">
+      <c r="D200" s="2" t="s">
         <v>1050</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
         <v>952</v>
       </c>
-      <c r="B195" s="2">
+      <c r="B201" s="2">
         <v>0.85</v>
       </c>
-      <c r="C195" s="2">
+      <c r="C201" s="2">
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
         <v>958</v>
       </c>
-      <c r="B196" s="2">
+      <c r="B202" s="2">
         <v>0.8</v>
       </c>
-      <c r="C196" s="2">
+      <c r="C202" s="2">
         <v>1.25</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
         <v>966</v>
       </c>
-      <c r="B197" s="2">
+      <c r="B203" s="2">
         <v>0.75</v>
       </c>
-      <c r="C197" s="2">
+      <c r="C203" s="2">
         <v>1.3</v>
       </c>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1800">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5428,6 +5428,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additions A–H, applied in the NRM1 order the app uses: A Prelims = % × Works; B OH&amp;P = % × (Works + A); Construction = Works + A + B; C Fees and D Developer costs = % × Construction; Base = Construction + C + D; E Risk and H Contingency = % × Base; F Inflation = % × (Base + E + H). A Prelims: 7% base (relaxed, vacant, no restrictions) plus the ADD rows that apply, capped at 11% outside London; London rows add 2 (Outer) or 3 (Inner) points with a 14% cap. The cap used is the highest cap among the rows that apply. Every figure here is read by the app — change it here, not in the code.</t>
   </si>
 </sst>
 </file>
@@ -16138,7 +16141,7 @@
         <v>935</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>936</v>
+        <v>1799</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1802">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5431,6 +5431,12 @@
   </si>
   <si>
     <t xml:space="preserve">Additions A–H, applied in the NRM1 order the app uses: A Prelims = % × Works; B OH&amp;P = % × (Works + A); Construction = Works + A + B; C Fees and D Developer costs = % × Construction; Base = Construction + C + D; E Risk and H Contingency = % × Base; F Inflation = % × (Base + E + H). A Prelims: 7% base (relaxed, vacant, no restrictions) plus the ADD rows that apply, capped at 11% outside London; London rows add 2 (Outer) or 3 (Inner) points with a 14% cap. The cap used is the highest cap among the rows that apply. Every figure here is read by the app — change it here, not in the code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.15 (October 2026)</t>
   </si>
 </sst>
 </file>
@@ -6062,7 +6068,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1797</v>
+        <v>1801</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -14348,7 +14354,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G203"/>
+  <dimension ref="A1:G228"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14399,7 +14405,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>437</v>
+        <v>563</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -14410,7 +14416,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -17442,7 +17448,7 @@
         <v>0.9</v>
       </c>
       <c r="C200" s="2">
-        <v>1.1000000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>1050</v>
@@ -17453,10 +17459,10 @@
         <v>952</v>
       </c>
       <c r="B201" s="2">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="C201" s="2">
-        <v>1.1499999999999999</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
@@ -17464,7 +17470,7 @@
         <v>958</v>
       </c>
       <c r="B202" s="2">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="C202" s="2">
         <v>1.25</v>
@@ -17475,11 +17481,441 @@
         <v>966</v>
       </c>
       <c r="B203" s="2">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="C203" s="2">
-        <v>1.3</v>
-      </c>
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>▶ confidence</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>Confidence grade: points per factor that applies, grade thresholds, and grade caps. The app adds up the points of every factor that applies, takes the grade from the GRADE rows, then applies the lowest cap of any factor that applies. Keys are read by the app — do not rename them.</t>
+        </is>
+      </c>
+      <c r="C205" s="4"/>
+      <c r="D205" s="4"/>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4"/>
+      <c r="G205" s="4"/>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>Factor (as printed)</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="D206" s="6" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>Caps grade at</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>GRADE_A</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Grade A when the total points are at most</t>
+        </is>
+      </c>
+      <c r="C207" s="2">
+        <v>1</v>
+      </c>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>GRADE_B</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Grade B when the total points are at most</t>
+        </is>
+      </c>
+      <c r="C208" s="2">
+        <v>3</v>
+      </c>
+      <c r="D208" s="2"/>
+      <c r="E208" s="2"/>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>GRADE_C</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Grade C when the total points are at most (above this: D)</t>
+        </is>
+      </c>
+      <c r="C209" s="2">
+        <v>6</v>
+      </c>
+      <c r="D209" s="2"/>
+      <c r="E209" s="2"/>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>STAGE_0_1</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>design at Stage 0–1</t>
+        </is>
+      </c>
+      <c r="C210" s="2">
+        <v>1</v>
+      </c>
+      <c r="D210" s="2"/>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>NO_SURVEYS</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>no surveys in the last 5 years</t>
+        </is>
+      </c>
+      <c r="C211" s="2">
+        <v>2</v>
+      </c>
+      <c r="D211" s="2"/>
+      <c r="E211" s="2"/>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>NO_CONDITION_SURVEY</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>no condition survey</t>
+        </is>
+      </c>
+      <c r="C212" s="2">
+        <v>1</v>
+      </c>
+      <c r="D212" s="2"/>
+      <c r="E212" s="2"/>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>NO_RD_SURVEY</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>no asbestos R&amp;D survey (pre-2000 building)</t>
+        </is>
+      </c>
+      <c r="C213" s="2">
+        <v>1</v>
+      </c>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2"/>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>NO_CONDITION_OR_RD</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>neither a condition nor an asbestos R&amp;D survey</t>
+        </is>
+      </c>
+      <c r="C214" s="2">
+        <v>0</v>
+      </c>
+      <c r="D214" s="2"/>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>CONDITION_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>building condition unknown</t>
+        </is>
+      </c>
+      <c r="C215" s="2">
+        <v>1</v>
+      </c>
+      <c r="D215" s="2"/>
+      <c r="E215" s="2"/>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>PLANNING_UNSURE</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>planning route not established</t>
+        </is>
+      </c>
+      <c r="C216" s="2">
+        <v>1</v>
+      </c>
+      <c r="D216" s="2"/>
+      <c r="E216" s="2"/>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>EXISTING_BUILDING</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>existing building</t>
+        </is>
+      </c>
+      <c r="C217" s="2">
+        <v>1</v>
+      </c>
+      <c r="D217" s="2"/>
+      <c r="E217" s="2"/>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>AGE_PRE_1980</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>built before 1980</t>
+        </is>
+      </c>
+      <c r="C218" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>OCCUPIED_FULL</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>fully occupied during works</t>
+        </is>
+      </c>
+      <c r="C219" s="2">
+        <v>1</v>
+      </c>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>OCCUPIED_PARTIAL</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>partly occupied during works</t>
+        </is>
+      </c>
+      <c r="C220" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>HIGH_RISKS</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>risks rated High (Threshold = how many)</t>
+        </is>
+      </c>
+      <c r="C221" s="2">
+        <v>1</v>
+      </c>
+      <c r="D221" s="2">
+        <v>2</v>
+      </c>
+      <c r="E221" s="2"/>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>CLIENT_SHARE_LOW</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>few client-confirmed quantities (Threshold = share of works cost below which it applies)</t>
+        </is>
+      </c>
+      <c r="C222" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D222" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E222" s="2"/>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>SENSE_HIGH</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>high-severity sense-check warning</t>
+        </is>
+      </c>
+      <c r="C223" s="2">
+        <v>2</v>
+      </c>
+      <c r="D223" s="2"/>
+      <c r="E223" s="2"/>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>SENSE_MEDIUM</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>sense-check warnings</t>
+        </is>
+      </c>
+      <c r="C224" s="2">
+        <v>1</v>
+      </c>
+      <c r="D224" s="2"/>
+      <c r="E224" s="2"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>BENCHMARK_MISSING</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>no published cost benchmark to check against</t>
+        </is>
+      </c>
+      <c r="C225" s="2">
+        <v>1</v>
+      </c>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>EXCLUDED_ITEMS</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>scope items excluded pending quantities</t>
+        </is>
+      </c>
+      <c r="C226" s="2">
+        <v>1</v>
+      </c>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>RATIO_ESTIMATES</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>quantities estimated from typical ratios</t>
+        </is>
+      </c>
+      <c r="C227" s="2">
+        <v>1</v>
+      </c>
+      <c r="D227" s="2"/>
+      <c r="E227" s="2"/>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>SPECIALIST_UNPRICED</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>specialist scope not priced</t>
+        </is>
+      </c>
+      <c r="C228" s="2">
+        <v>1</v>
+      </c>
+      <c r="D228" s="2"/>
+      <c r="E228" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1802">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1805">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5437,6 +5437,15 @@
   </si>
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.15 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.16 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additions A–H, applied in the NRM1 order the app uses: A Prelims = % × Works; B OH&amp;P = % × (Works + A); Construction = Works + A + B; C Fees and D Developer costs = % × Construction; Base = Construction + C + D; E Risk and H Contingency = % × Base; F Inflation = % × (Base + E + H). A Prelims: 7% base (relaxed, vacant, no restrictions) plus the ADD rows that apply, capped at 11% outside London; London rows add 2 (Outer) or 3 (Inner) points with a 14% cap. The cap used is the highest cap among the rows that apply. Every figure here is read by the app — change it here, not in the code. Since v5.16 the E and H rows below are not used: risk is set by ▶ risk_allowance (four NRM1 categories, no separate contingency); they are kept only for older copies of the app.</t>
   </si>
 </sst>
 </file>
@@ -6068,7 +6077,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -14354,7 +14363,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G228"/>
+  <dimension ref="A1:G258"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14405,7 +14414,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>563</v>
+        <v>523</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -14416,7 +14425,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -16147,7 +16156,7 @@
         <v>935</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>1799</v>
+        <v>1804</v>
       </c>
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
@@ -17916,6 +17925,677 @@
       </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>▶ risk_allowance</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="inlineStr">
+        <is>
+          <t>Risk allowance in the four NRM1 categories, % of base cost (construction + fees). The app adds the rows that apply in each category and caps the total; it replaces the E and H rows of ▶ percentage_rules. Nothing already priced in the scope, prelims, fees or programme is charged again (occupation, deadlines and phasing are in prelims and programme; inflation is F). Keys are read by the app — do not rename them.</t>
+        </is>
+      </c>
+      <c r="C230" s="4"/>
+      <c r="D230" s="4"/>
+      <c r="E230" s="4"/>
+      <c r="F230" s="4"/>
+      <c r="G230" s="4"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B231" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>Applies when (as printed)</t>
+        </is>
+      </c>
+      <c r="D231" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>DD_STAGE_0_1</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>design at Stage 0–1</t>
+        </is>
+      </c>
+      <c r="D232" s="2">
+        <v>5</v>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Base: by design stage reached (Q4.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>DD_STAGE_2</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>design at Stage 2</t>
+        </is>
+      </c>
+      <c r="D233" s="2">
+        <v>3</v>
+      </c>
+      <c r="E233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>DD_STAGE_3</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>design at Stage 3</t>
+        </is>
+      </c>
+      <c r="D234" s="2">
+        <v>2</v>
+      </c>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>DD_STAGE_4</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>design at Stage 4</t>
+        </is>
+      </c>
+      <c r="D235" s="2">
+        <v>1</v>
+      </c>
+      <c r="E235" s="2"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>DD_NO_CONDITION_SURVEY</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>no condition survey</t>
+        </is>
+      </c>
+      <c r="D236" s="2">
+        <v>1</v>
+      </c>
+      <c r="E236" s="2"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>DD_AGEING_ME</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>ageing M&amp;E</t>
+        </is>
+      </c>
+      <c r="D237" s="2">
+        <v>1</v>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Not at full systems replacement</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>DD_AGEING_ME_REPLACED</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>ageing M&amp;E (being replaced)</t>
+        </is>
+      </c>
+      <c r="D238" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>At full systems replacement (the replacement is priced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>DD_HIGHER_RISK</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Design development</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>higher-risk building</t>
+        </is>
+      </c>
+      <c r="D239" s="2">
+        <v>1</v>
+      </c>
+      <c r="E239" s="2"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>CR_NEW</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>new build</t>
+        </is>
+      </c>
+      <c r="D240" s="2">
+        <v>2</v>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Base: new build, external works</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>CR_EXISTING</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>existing building</t>
+        </is>
+      </c>
+      <c r="D241" s="2">
+        <v>4</v>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Base: refurbishment, fit-out, extension, demolition, mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>CR_ASBESTOS</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>no asbestos R&amp;D survey, removal not priced</t>
+        </is>
+      </c>
+      <c r="D242" s="2">
+        <v>2</v>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Pre-2000 building or asbestos known</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>CR_ASBESTOS_PRICED</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>no asbestos R&amp;D survey, removal priced</t>
+        </is>
+      </c>
+      <c r="D243" s="2">
+        <v>1</v>
+      </c>
+      <c r="E243" s="2"/>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>CR_STRUCTURAL</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>structural concerns</t>
+        </is>
+      </c>
+      <c r="D244" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Not priced (no repairs or alterations item)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>CR_STRUCTURAL_PRICED</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>structural concerns (repairs priced)</t>
+        </is>
+      </c>
+      <c r="D245" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E245" s="2"/>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>CR_CONTAMINATED</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>contaminated land</t>
+        </is>
+      </c>
+      <c r="D246" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Not priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>CR_CONTAMINATED_PRICED</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>contaminated land (remediation priced)</t>
+        </is>
+      </c>
+      <c r="D247" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E247" s="2"/>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>CR_DAMP</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>damp</t>
+        </is>
+      </c>
+      <c r="D248" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>0 when damp treatment is priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>CR_FIRE</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>fire safety issues</t>
+        </is>
+      </c>
+      <c r="D249" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>0 when fire stopping is priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>CR_DRAINAGE</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>drainage issues</t>
+        </is>
+      </c>
+      <c r="D250" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>0 when drainage is priced</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>CR_PRE_1980</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>pre-1980 building</t>
+        </is>
+      </c>
+      <c r="D251" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Existing buildings only</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>EC_STAGE_0_1</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Employer change</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>design at Stage 0–1</t>
+        </is>
+      </c>
+      <c r="D252" s="2">
+        <v>3</v>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>EC_LATER</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Employer change</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>design past Stage 1</t>
+        </is>
+      </c>
+      <c r="D253" s="2">
+        <v>2</v>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>EO_BASE</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Employer other</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D254" s="2">
+        <v>1</v>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>EO_PLANNING_UNSURE</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Employer other</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>planning route unsure</t>
+        </is>
+      </c>
+      <c r="D255" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E255" s="2"/>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>EO_GRANT</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Employer other</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>grant funding</t>
+        </is>
+      </c>
+      <c r="D256" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E256" s="2"/>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>EO_HERITAGE</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Employer other</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>listed or conservation area</t>
+        </is>
+      </c>
+      <c r="D257" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E257" s="2"/>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>CAP</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>total risk allowance cap</t>
+        </is>
+      </c>
+      <c r="D258" s="2">
+        <v>25</v>
+      </c>
+      <c r="E258" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1806">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5446,6 +5446,9 @@
   </si>
   <si>
     <t xml:space="preserve">Additions A–H, applied in the NRM1 order the app uses: A Prelims = % × Works; B OH&amp;P = % × (Works + A); Construction = Works + A + B; C Fees and D Developer costs = % × Construction; Base = Construction + C + D; E Risk and H Contingency = % × Base; F Inflation = % × (Base + E + H). A Prelims: 7% base (relaxed, vacant, no restrictions) plus the ADD rows that apply, capped at 11% outside London; London rows add 2 (Outer) or 3 (Inner) points with a 14% cap. The cap used is the highest cap among the rows that apply. Every figure here is read by the app — change it here, not in the code. Since v5.16 the E and H rows below are not used: risk is set by ▶ risk_allowance (four NRM1 categories, no separate contingency); they are kept only for older copies of the app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.17 (October 2026)</t>
   </si>
 </sst>
 </file>
@@ -6077,7 +6080,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -14363,7 +14366,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G258"/>
+  <dimension ref="A1:G265"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14414,7 +14417,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>523</v>
+        <v>1395</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -18596,6 +18599,104 @@
         <v>25</v>
       </c>
       <c r="E258" s="2"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>▶ inflation</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>Inflation (F) from the rate base date to the mid-point of construction (the programme's own dates): % = (1 + annual rate) ^ years − 1, capped. Replaces the banded F rows of ▶ percentage_rules. Keys are read by the app — do not rename them.</t>
+        </is>
+      </c>
+      <c r="C260" s="4"/>
+      <c r="D260" s="4"/>
+      <c r="E260" s="4"/>
+      <c r="F260" s="4"/>
+      <c r="G260" s="4"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>RATE_BASE_DATE</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>The date every rate on '2. Rates' is priced at (Q3 2026, taken as mid-quarter). Text, YYYY-MM-DD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>RATE_BASE_LABEL</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>How the base date is printed in the report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>ANNUAL_PCT</t>
+        </is>
+      </c>
+      <c r="B264" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Construction price inflation, % a year (estimate from published tender price forecasts, 2026–28).</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>CAP_PCT</t>
+        </is>
+      </c>
+      <c r="B265" s="2">
+        <v>12</v>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Maximum inflation allowance, %.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1807">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5449,6 +5449,9 @@
   </si>
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.17 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.18 (October 2026)</t>
   </si>
 </sst>
 </file>
@@ -6080,7 +6083,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -14366,7 +14369,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G272"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14417,7 +14420,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>1395</v>
+        <v>528</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -18120,7 +18123,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>ageing M&amp;E (being replaced)</t>
+          <t>ageing M&amp;E, being replaced</t>
         </is>
       </c>
       <c r="D238" s="2">
@@ -18695,6 +18698,117 @@
       <c r="C265" s="2" t="inlineStr">
         <is>
           <t>Maximum inflation allowance, %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>▶ route_fees</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Professional fees by the preferred procurement route (from the Procurement Reference). The client-fee adjustment (points) is added to C; the contractor's design (% of construction) is its own row. Applies only while Stage 4 is not yet complete (Q4.5). Route names must match the Procurement Reference exactly.</t>
+        </is>
+      </c>
+      <c r="C267" s="4"/>
+      <c r="D267" s="4"/>
+      <c r="E267" s="4"/>
+      <c r="F267" s="4"/>
+      <c r="G267" s="4"/>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>Route</t>
+        </is>
+      </c>
+      <c r="B268" s="6" t="inlineStr">
+        <is>
+          <t>Client fee adjustment (points)</t>
+        </is>
+      </c>
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>Contractor's design %</t>
+        </is>
+      </c>
+      <c r="D268" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Traditional</t>
+        </is>
+      </c>
+      <c r="B269" s="2">
+        <v>0</v>
+      </c>
+      <c r="C269" s="2">
+        <v>0</v>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>The client's design team does every stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Design and build (single stage)</t>
+        </is>
+      </c>
+      <c r="B270" s="2">
+        <v>-3</v>
+      </c>
+      <c r="C270" s="2">
+        <v>2</v>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>The contractor's team does Stage 4. Contractor's design 2% (Claycroft, Morgan Sindall D&amp;B: 2.1%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Two-stage (PCSA)</t>
+        </is>
+      </c>
+      <c r="B271" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="C271" s="2">
+        <v>1</v>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Stage 4 is shared with the contractor during the pre-construction stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Construction management</t>
+        </is>
+      </c>
+      <c r="B272" s="2">
+        <v>0</v>
+      </c>
+      <c r="C272" s="2">
+        <v>0</v>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Unchanged: the CM fee replaces part of the contractor's OH&amp;P (not modelled).</t>
         </is>
       </c>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -6072,7 +6072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -6774,148 +6774,220 @@
     <row r="81" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="inlineStr">
         <is>
-          <t>v5.12 — 4 Oct 2026</t>
+          <t>v5.18 — 8 Oct 2026</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Lakeside tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
+          <t>Professional fees by procurement route: new ▶ route_fees on '3. Settings'. Design and build: client fees −3 points and contractor's design 2% of construction (Claycroft D&amp;B 2.1%); two-stage (PCSA): −1.5 and 1%; traditional and construction management unchanged. Only while Stage 4 is still to do. The preferred route comes from the Procurement Reference.</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="17" t="inlineStr">
         <is>
+          <t>v5.17 — 8 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>Inflation from the rate base date: new ▶ inflation on '3. Settings'. Rates are at Q3 2026 (15 Aug 2026); 3.5% a year compounded to the programme's construction mid-point, capped at 12%. Replaces the banded F rows of ▶ percentage_rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="inlineStr">
+        <is>
+          <t>v5.16 — 8 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B83" s="17" t="inlineStr">
+        <is>
+          <t>Risk allowance in the four NRM1 categories: new ▶ risk_allowance on '3. Settings' (design development by design stage, construction, employer change, employer other; cap 25%). Replaces E and the fixed 5% contingency H. Items already priced in the scope reduce or remove their risk row; occupation, deadline and phasing stay in prelims and programme only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>v5.15 — 7 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
+        <is>
+          <t>Confidence grade scored from the workbook: new ▶ confidence on '3. Settings' (points per factor, grade thresholds, caps: Stage 0–1 at B; existing building with neither a condition nor an R&amp;D survey at C). ▶ range_widths skewed upwards: A −10/+15, B −10/+20, C −15/+25, D −20/+35.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="17" t="inlineStr">
+        <is>
+          <t>v5.14 — 6 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B85" s="17" t="inlineStr">
+        <is>
+          <t>Preliminaries: 7% base (relaxed, vacant, no restrictions) plus occupation, restricted hours, shared access, programme over 18 months, 4+ M&amp;E items, heritage, hard deadline and speed-first, capped at 11%; Outer London +2 and Inner London +3 with a 14% cap. The ▶ percentage_rules header states the on-cost order the app uses (OH&amp;P on works + prelims; risk on base cost; inflation on the cost limit).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>v5.13 — 5 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B86" s="17" t="inlineStr">
+        <is>
+          <t>Scope dependencies ('When selected' SUGGEST on '4. Scope rules'): kitchens and bathrooms → ventilation (domestic also → internal doors); strip-out → fire stopping, emergency lighting, asbestos removal; full power installation → fire stopping, emergency lighting. The report flags any that are not ticked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>v5.12 — 4 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B87" s="17" t="inlineStr">
+        <is>
+          <t>Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Lakeside tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="17" t="inlineStr">
+        <is>
           <t>v5.11 — 4 Oct 2026</t>
         </is>
       </c>
-      <c r="B82" s="17" t="inlineStr">
+      <c r="B88" s="17" t="inlineStr">
         <is>
           <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %). Columns AA–AB: Claude's suggested Refurb &amp; Fit-out Std rate and the reason, on all 47 rows (25 raise, 2 lower, 20 keep).</t>
         </is>
       </c>
     </row>
-    <row r="83" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="17" t="s">
+    <row r="89" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="17" t="s">
         <v>1778</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>1779</v>
       </c>
-      <c r="C83" s="60"/>
-    </row>
-    <row r="84" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+      <c r="C89" s="60"/>
+    </row>
+    <row r="90" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B90" s="17" t="s">
         <v>1783</v>
       </c>
-      <c r="C84" s="60"/>
-    </row>
-    <row r="85" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A85" s="17" t="s">
+      <c r="C90" s="60"/>
+    </row>
+    <row r="91" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A91" s="17" t="s">
         <v>1722</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>1737</v>
       </c>
-      <c r="C85" s="60"/>
-    </row>
-    <row r="86" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A86" s="17" t="s">
+      <c r="C91" s="60"/>
+    </row>
+    <row r="92" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A92" s="17" t="s">
         <v>1711</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>1712</v>
       </c>
-      <c r="C86" s="60"/>
-    </row>
-    <row r="87" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A87" s="17" t="s">
+      <c r="C92" s="60"/>
+    </row>
+    <row r="93" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A93" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B93" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C87" s="60"/>
-    </row>
-    <row r="88" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A88" s="15" t="s">
+      <c r="C93" s="60"/>
+    </row>
+    <row r="94" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A94" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B94" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C88" s="33"/>
-    </row>
-    <row r="89" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A89" s="15" t="s">
+      <c r="C94" s="33"/>
+    </row>
+    <row r="95" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A95" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B95" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C89" s="33"/>
-    </row>
-    <row r="90" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A90" s="15" t="s">
+      <c r="C95" s="33"/>
+    </row>
+    <row r="96" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A96" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B96" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C90" s="33"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="15" t="s">
+      <c r="C96" s="33"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C91" s="33"/>
-    </row>
-    <row r="92" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A92" s="15" t="s">
+      <c r="C97" s="33"/>
+    </row>
+    <row r="98" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A98" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B98" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C92" s="33"/>
-    </row>
-    <row r="93" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A93" s="15" t="s">
+      <c r="C98" s="33"/>
+    </row>
+    <row r="99" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A99" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B99" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C93" s="33"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94" s="15" t="s">
+      <c r="C99" s="33"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B100" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C94" s="33"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="15" t="s">
+      <c r="C100" s="33"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B101" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C95" s="33"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" s="15"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="33"/>
+      <c r="C101" s="33"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="15"/>
+      <c r="B102" s="17"/>
+      <c r="C102" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1809">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5452,6 +5452,12 @@
   </si>
   <si>
     <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.18 (October 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRM1 COST ESTIMATE TOOL — v5.19 (October 2026)</t>
   </si>
 </sst>
 </file>
@@ -6072,7 +6078,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C103"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -6083,7 +6089,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -6774,220 +6780,232 @@
     <row r="81" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="inlineStr">
         <is>
-          <t>v5.18 — 8 Oct 2026</t>
+          <t>v5.19 — 9 Oct 2026</t>
         </is>
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>Professional fees by procurement route: new ▶ route_fees on '3. Settings'. Design and build: client fees −3 points and contractor's design 2% of construction (Claycroft D&amp;B 2.1%); two-stage (PCSA): −1.5 and 1%; traditional and construction management unchanged. Only while Stage 4 is still to do. The preferred route comes from the Procurement Reference.</t>
+          <t>Wording only, no figure changed: ▶ risk_allowance label 'ageing M&amp;E, being replaced' → 'ageing M&amp;E being replaced' (it read as two items in the report).</t>
         </is>
       </c>
     </row>
     <row r="82" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>v5.17 — 8 Oct 2026</t>
+          <t>v5.18 — 8 Oct 2026</t>
         </is>
       </c>
       <c r="B82" s="17" t="inlineStr">
         <is>
-          <t>Inflation from the rate base date: new ▶ inflation on '3. Settings'. Rates are at Q3 2026 (15 Aug 2026); 3.5% a year compounded to the programme's construction mid-point, capped at 12%. Replaces the banded F rows of ▶ percentage_rules.</t>
+          <t>Professional fees by procurement route: new ▶ route_fees on '3. Settings'. Design and build: client fees −3 points and contractor's design 2% of construction (Claycroft D&amp;B 2.1%); two-stage (PCSA): −1.5 and 1%; traditional and construction management unchanged. Only while Stage 4 is still to do. The preferred route comes from the Procurement Reference.</t>
         </is>
       </c>
     </row>
     <row r="83" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t>v5.16 — 8 Oct 2026</t>
+          <t>v5.17 — 8 Oct 2026</t>
         </is>
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>Risk allowance in the four NRM1 categories: new ▶ risk_allowance on '3. Settings' (design development by design stage, construction, employer change, employer other; cap 25%). Replaces E and the fixed 5% contingency H. Items already priced in the scope reduce or remove their risk row; occupation, deadline and phasing stay in prelims and programme only.</t>
+          <t>Inflation from the rate base date: new ▶ inflation on '3. Settings'. Rates are at Q3 2026 (15 Aug 2026); 3.5% a year compounded to the programme's construction mid-point, capped at 12%. Replaces the banded F rows of ▶ percentage_rules.</t>
         </is>
       </c>
     </row>
     <row r="84" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>v5.15 — 7 Oct 2026</t>
+          <t>v5.16 — 8 Oct 2026</t>
         </is>
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>Confidence grade scored from the workbook: new ▶ confidence on '3. Settings' (points per factor, grade thresholds, caps: Stage 0–1 at B; existing building with neither a condition nor an R&amp;D survey at C). ▶ range_widths skewed upwards: A −10/+15, B −10/+20, C −15/+25, D −20/+35.</t>
+          <t>Risk allowance in the four NRM1 categories: new ▶ risk_allowance on '3. Settings' (design development by design stage, construction, employer change, employer other; cap 25%). Replaces E and the fixed 5% contingency H. Items already priced in the scope reduce or remove their risk row; occupation, deadline and phasing stay in prelims and programme only.</t>
         </is>
       </c>
     </row>
     <row r="85" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="17" t="inlineStr">
         <is>
-          <t>v5.14 — 6 Oct 2026</t>
+          <t>v5.15 — 7 Oct 2026</t>
         </is>
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>Preliminaries: 7% base (relaxed, vacant, no restrictions) plus occupation, restricted hours, shared access, programme over 18 months, 4+ M&amp;E items, heritage, hard deadline and speed-first, capped at 11%; Outer London +2 and Inner London +3 with a 14% cap. The ▶ percentage_rules header states the on-cost order the app uses (OH&amp;P on works + prelims; risk on base cost; inflation on the cost limit).</t>
+          <t>Confidence grade scored from the workbook: new ▶ confidence on '3. Settings' (points per factor, grade thresholds, caps: Stage 0–1 at B; existing building with neither a condition nor an R&amp;D survey at C). ▶ range_widths skewed upwards: A −10/+15, B −10/+20, C −15/+25, D −20/+35.</t>
         </is>
       </c>
     </row>
     <row r="86" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>v5.13 — 5 Oct 2026</t>
+          <t>v5.14 — 6 Oct 2026</t>
         </is>
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>Scope dependencies ('When selected' SUGGEST on '4. Scope rules'): kitchens and bathrooms → ventilation (domestic also → internal doors); strip-out → fire stopping, emergency lighting, asbestos removal; full power installation → fire stopping, emergency lighting. The report flags any that are not ticked.</t>
+          <t>Preliminaries: 7% base (relaxed, vacant, no restrictions) plus occupation, restricted hours, shared access, programme over 18 months, 4+ M&amp;E items, heritage, hard deadline and speed-first, capped at 11%; Outer London +2 and Inner London +3 with a 14% cap. The ▶ percentage_rules header states the on-cost order the app uses (OH&amp;P on works + prelims; risk on base cost; inflation on the cost limit).</t>
         </is>
       </c>
     </row>
     <row r="87" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>v5.12 — 4 Oct 2026</t>
+          <t>v5.13 — 5 Oct 2026</t>
         </is>
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Lakeside tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
+          <t>Scope dependencies ('When selected' SUGGEST on '4. Scope rules'): kitchens and bathrooms → ventilation (domestic also → internal doors); strip-out → fire stopping, emergency lighting, asbestos removal; full power installation → fire stopping, emergency lighting. The report flags any that are not ticked.</t>
         </is>
       </c>
     </row>
     <row r="88" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A88" s="17" t="inlineStr">
         <is>
+          <t>v5.12 — 4 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B88" s="17" t="inlineStr">
+        <is>
+          <t>Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Lakeside tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" spans="1:3" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="17" t="inlineStr">
+        <is>
           <t>v5.11 — 4 Oct 2026</t>
         </is>
       </c>
-      <c r="B88" s="17" t="inlineStr">
+      <c r="B89" s="17" t="inlineStr">
         <is>
           <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %). Columns AA–AB: Claude's suggested Refurb &amp; Fit-out Std rate and the reason, on all 47 rows (25 raise, 2 lower, 20 keep).</t>
         </is>
       </c>
     </row>
-    <row r="89" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="17" t="s">
+    <row r="90" spans="1:3" s="54" customFormat="1" ht="104.0" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="17" t="s">
         <v>1778</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B90" s="17" t="s">
         <v>1779</v>
       </c>
-      <c r="C89" s="60"/>
-    </row>
-    <row r="90" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="17" t="s">
+      <c r="C90" s="60"/>
+    </row>
+    <row r="91" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>1783</v>
-      </c>
-      <c r="C90" s="60"/>
-    </row>
-    <row r="91" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
-        <v>1722</v>
-      </c>
-      <c r="B91" s="17" t="s">
-        <v>1737</v>
       </c>
       <c r="C91" s="60"/>
     </row>
     <row r="92" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A92" s="17" t="s">
-        <v>1711</v>
+        <v>1722</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>1712</v>
+        <v>1737</v>
       </c>
       <c r="C92" s="60"/>
     </row>
     <row r="93" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A93" s="17" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B93" s="17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C93" s="60"/>
+    </row>
+    <row r="94" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A94" s="17" t="s">
         <v>1632</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B94" s="17" t="s">
         <v>1634</v>
       </c>
-      <c r="C93" s="60"/>
-    </row>
-    <row r="94" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A94" s="15" t="s">
+      <c r="C94" s="60"/>
+    </row>
+    <row r="95" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A95" s="15" t="s">
         <v>1620</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B95" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C94" s="33"/>
-    </row>
-    <row r="95" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A95" s="15" t="s">
+      <c r="C95" s="33"/>
+    </row>
+    <row r="96" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A96" s="15" t="s">
         <v>1060</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B96" s="17" t="s">
         <v>1061</v>
       </c>
-      <c r="C95" s="33"/>
-    </row>
-    <row r="96" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A96" s="15" t="s">
+      <c r="C96" s="33"/>
+    </row>
+    <row r="97" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A97" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C96" s="33"/>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A97" s="15" t="s">
+      <c r="C97" s="33"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B98" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C97" s="33"/>
-    </row>
-    <row r="98" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A98" s="15" t="s">
+      <c r="C98" s="33"/>
+    </row>
+    <row r="99" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A99" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B99" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="33"/>
-    </row>
-    <row r="99" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A99" s="15" t="s">
+      <c r="C99" s="33"/>
+    </row>
+    <row r="100" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A100" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B100" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C99" s="33"/>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B100" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C100" s="33"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B101" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" s="33"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B102" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C101" s="33"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" s="15"/>
-      <c r="B102" s="17"/>
       <c r="C102" s="33"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="15"/>
+      <c r="B103" s="17"/>
+      <c r="C103" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14492,7 +14510,7 @@
         <v>749</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>750</v>
@@ -14503,7 +14521,7 @@
         <v>751</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>1802</v>
+        <v>1807</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -18195,7 +18213,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>ageing M&amp;E, being replaced</t>
+          <t>ageing M&amp;E being replaced</t>
         </is>
       </c>
       <c r="D238" s="2">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D261EF-C12F-4C5D-BD6E-400750A2F41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8CEDBA-193B-44AD-83E1-FA7C8520DD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2. Rates'!$A$5:$O$152</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1" calcId="191029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4548" uniqueCount="1973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="2013">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5217,9 +5217,6 @@
     <t>Additions A–H, applied in the NRM1 order the app uses: A Prelims = % × Works; B OH&amp;P = % × (Works + A); Construction = Works + A + B; C Fees and D Developer costs = % × Construction; Base = Construction + C + D; E Risk and H Contingency = % × Base; F Inflation = % × (Base + E + H). A Prelims: 7% base (relaxed, vacant, no restrictions) plus the ADD rows that apply, capped at 11% outside London; London rows add 2 (Outer) or 3 (Inner) points with a 14% cap. The cap used is the highest cap among the rows that apply. Every figure here is read by the app — change it here, not in the code. Since v5.16 the E and H rows below are not used: risk is set by ▶ risk_allowance (four NRM1 categories, no separate contingency); they are kept only for older copies of the app.</t>
   </si>
   <si>
-    <t>2026-10-09</t>
-  </si>
-  <si>
     <t>NRM1 COST ESTIMATE TOOL — v5.19 (October 2026)</t>
   </si>
   <si>
@@ -5949,7 +5946,130 @@
     <t>Pre-launch fixes from test batch 3. ▶ percentage_rules: Q3.5 reworded (shared access) and three new Prelims ADD rows of 0.5 (restricted deliveries, tight site, public road), same 11% cap. ▶ quantity_ratios: m2_per_car_space 25 (AI estimate); Roads, paths and paving now deducts the car parking and HGV yard the client entered. ▶ inputs DEMOLISHED: ENTER on New Build and Extension (it was the new floor area); Asbestos removal follows it on Extension too. ▶ location_factors Scotland mid 0.90 → 0.965 (it sat below its own low). Heating: gas boiler is the default; the air source heat pump options carry NETZERO, the default when Q2.5 includes Net zero (owner, 10 Oct 2026).</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-10</t>
+    <t>BENCHMARK_BREACH</t>
+  </si>
+  <si>
+    <t>estimate more than 30% outside the cost benchmark (Threshold = share outside the band)</t>
+  </si>
+  <si>
+    <t>DEFAULT</t>
+  </si>
+  <si>
+    <t>Used only in the first calculation passes, before the confidence grade is known. Every printed range uses A–D.</t>
+  </si>
+  <si>
+    <t>vat_partly_share</t>
+  </si>
+  <si>
+    <t>Budget check: share of VAT counted</t>
+  </si>
+  <si>
+    <t>Q4.3a = Partly</t>
+  </si>
+  <si>
+    <t>Owner decision (Oct 2026)</t>
+  </si>
+  <si>
+    <t>sens_me_works_pct</t>
+  </si>
+  <si>
+    <t>Cost drivers list: M&amp;E works pushed by this %</t>
+  </si>
+  <si>
+    <t>Every report (what-if only; never changes the estimate)</t>
+  </si>
+  <si>
+    <t>Presentation step</t>
+  </si>
+  <si>
+    <t>sens_works_pct</t>
+  </si>
+  <si>
+    <t>Cost drivers list: all works pushed by this %</t>
+  </si>
+  <si>
+    <t>Every report (what-if only)</t>
+  </si>
+  <si>
+    <t>sens_prelims_pp</t>
+  </si>
+  <si>
+    <t>Cost drivers list: Prelims (A) pushed by these points</t>
+  </si>
+  <si>
+    <t>sens_ohp_pp</t>
+  </si>
+  <si>
+    <t>Cost drivers list: OH&amp;P (B) pushed by these points</t>
+  </si>
+  <si>
+    <t>sens_fees_pp</t>
+  </si>
+  <si>
+    <t>Cost drivers list: Fees (C) pushed by these points</t>
+  </si>
+  <si>
+    <t>sens_risk_pp</t>
+  </si>
+  <si>
+    <t>Cost drivers list: Risk (E) pushed by these points</t>
+  </si>
+  <si>
+    <t>sens_contingency_pp</t>
+  </si>
+  <si>
+    <t>Cost drivers list: Contingency (H) pushed by these points</t>
+  </si>
+  <si>
+    <t>sens_inflation_pp</t>
+  </si>
+  <si>
+    <t>Cost drivers list: Inflation (F) pushed by these points</t>
+  </si>
+  <si>
+    <t>v5.21 — 10 Oct 2026</t>
+  </si>
+  <si>
+    <t>No figure the estimate uses changed. Numbers the app used to hold in its code now live here, so nothing is ever assumed: ▶ factors gains vat_partly_share (0.5 — half the VAT counted when Q4.3a = Partly) and the eight what-if steps of the cost-drivers list (sens_*); ▶ range_widths gains DEFAULT (0.89 / 1.11, used only before the grade is known); ▶ confidence gains BENCHMARK_BREACH (estimate more than 30% outside its ▶ benchmarks band caps the grade at D). The app now refuses a workbook missing any of these rows, a range-width grade, an F row without a cap, or a G row of 0.</t>
+  </si>
+  <si>
+    <t>IF(USE=IND, IF(PT=NB EX, OFFICES, GIFA), GIFA)</t>
+  </si>
+  <si>
+    <t>IF(USE=IND, IF(PT=NB EX, OFFICES + PRODUCTION, GIFA), GIFA)</t>
+  </si>
+  <si>
+    <t>office_share</t>
+  </si>
+  <si>
+    <t>Industrial / warehouse (New build, Extension): share of the floor priced as offices, welfare and staff areas, the suggestion shown at Q1.3a</t>
+  </si>
+  <si>
+    <t>OFFICES</t>
+  </si>
+  <si>
+    <t>Q1.3a share of the floor that is offices, welfare and staff areas (%) × GIFA</t>
+  </si>
+  <si>
+    <t>GIFA * r.office_share</t>
+  </si>
+  <si>
+    <t>Industrial / warehouse, New build and Extension (where Q1.3a is asked). Fit-out items are measured on it</t>
+  </si>
+  <si>
+    <t>PRODUCTION</t>
+  </si>
+  <si>
+    <t>Q1.3b: Factory / production → GIFA − OFFICES; Storage / warehouse → 0</t>
+  </si>
+  <si>
+    <t>Production floor that also gets the building services</t>
+  </si>
+  <si>
+    <t>v5.22 — 10 Oct 2026</t>
+  </si>
+  <si>
+    <t>No rate changed. Industrial / warehouse new build and extensions are split into offices and the main space (owner, 10 Oct 2026): new inputs OFFICES (Q1.3a share × GIFA; default GIFA × r.office_share) and PRODUCTION (Q1.3b Factory / production → the rest of the floor, Storage / warehouse → 0); new ratio office_share 0.10 (suggestion, AI estimate – verify). On those projects internal walls, internal doors, wall / floor / ceiling finishes, signage and data are measured on OFFICES, and heating, water, ventilation, power and builder's work on OFFICES + PRODUCTION. Every other building use and project type is measured on GIFA as before.</t>
   </si>
 </sst>
 </file>
@@ -6142,7 +6262,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6307,6 +6427,9 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6573,7 +6696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -6584,7 +6707,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" s="31" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B1" s="17"/>
       <c r="C1" s="33"/>
@@ -6775,10 +6898,10 @@
     </row>
     <row r="24" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>1730</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>1731</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -7210,7 +7333,7 @@
       </c>
       <c r="B73" s="17"/>
       <c r="C73" s="33">
-        <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*(COUNTIFS('3. Settings'!A96:A123,'3. Settings'!A96:A123,'3. Settings'!B96:B123,"ALL")=0))</f>
+        <f>SUMPRODUCT(('3. Settings'!A98:A125&lt;&gt;"")*(COUNTIFS('3. Settings'!A98:A125,'3. Settings'!A98:A125,'3. Settings'!B98:B125,"ALL")=0))</f>
         <v>0</v>
       </c>
     </row>
@@ -7220,7 +7343,7 @@
       </c>
       <c r="B74" s="17"/>
       <c r="C74" s="33">
-        <f>SUMPRODUCT(('3. Settings'!A96:A123&lt;&gt;"")*('3. Settings'!C96:C123=""))</f>
+        <f>SUMPRODUCT(('3. Settings'!A98:A125&lt;&gt;"")*('3. Settings'!C98:C125=""))</f>
         <v>0</v>
       </c>
     </row>
@@ -7270,205 +7393,221 @@
     </row>
     <row r="81" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="17" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B83" s="17" t="s">
         <v>1970</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A82" s="17" t="s">
-        <v>1732</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A83" s="17" t="s">
-        <v>1734</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="84" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A84" s="17" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="85" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A85" s="17" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A86" s="17" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="87" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A87" s="17" t="s">
-        <v>1742</v>
+        <v>1737</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>1743</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="88" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A88" s="17" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A89" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B89" s="17" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A90" s="17" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B90" s="17" t="s">
         <v>1744</v>
       </c>
-      <c r="B88" s="17" t="s">
+    </row>
+    <row r="91" spans="1:3" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="17" t="s">
         <v>1745</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>1746</v>
       </c>
-      <c r="B89" s="17" t="s">
+    </row>
+    <row r="92" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="17" t="s">
         <v>1747</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A90" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>1748</v>
       </c>
-      <c r="B90" s="17" t="s">
-        <v>1749</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
+    </row>
+    <row r="93" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="17" t="s">
         <v>1715</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B93" s="17" t="s">
         <v>1716</v>
       </c>
-      <c r="C91" s="60"/>
-    </row>
-    <row r="92" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+      <c r="C93" s="60"/>
+    </row>
+    <row r="94" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="17" t="s">
         <v>1689</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B94" s="17" t="s">
         <v>1718</v>
-      </c>
-      <c r="C92" s="60"/>
-    </row>
-    <row r="93" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A93" s="17" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C93" s="60"/>
-    </row>
-    <row r="94" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A94" s="17" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B94" s="17" t="s">
-        <v>1679</v>
       </c>
       <c r="C94" s="60"/>
     </row>
     <row r="95" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A95" s="17" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B95" s="17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="C95" s="60"/>
+    </row>
+    <row r="96" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A96" s="17" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B96" s="17" t="s">
+        <v>1679</v>
+      </c>
+      <c r="C96" s="60"/>
+    </row>
+    <row r="97" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A97" s="17" t="s">
         <v>1619</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C95" s="60"/>
-    </row>
-    <row r="96" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A96" s="15" t="s">
+      <c r="C97" s="60"/>
+    </row>
+    <row r="98" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A98" s="15" t="s">
         <v>1608</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B98" s="17" t="s">
         <v>1609</v>
       </c>
-      <c r="C96" s="33"/>
-    </row>
-    <row r="97" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A97" s="15" t="s">
+      <c r="C98" s="33"/>
+    </row>
+    <row r="99" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A99" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B99" s="17" t="s">
         <v>1052</v>
-      </c>
-      <c r="C97" s="33"/>
-    </row>
-    <row r="98" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A98" s="15" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B98" s="17" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C98" s="33"/>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A99" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>24</v>
       </c>
       <c r="C99" s="33"/>
     </row>
     <row r="100" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A100" s="15" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B100" s="17" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C100" s="33"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="33"/>
+    </row>
+    <row r="102" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A102" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B102" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C100" s="33"/>
-    </row>
-    <row r="101" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A101" s="15" t="s">
+      <c r="C102" s="33"/>
+    </row>
+    <row r="103" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B103" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="C101" s="33"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" s="15" t="s">
+      <c r="C103" s="33"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B104" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C102" s="33"/>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A103" s="15" t="s">
+      <c r="C104" s="33"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B105" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C103" s="33"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A104" s="15"/>
-      <c r="B104" s="17"/>
-      <c r="C104" s="33"/>
+      <c r="C105" s="33"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="15"/>
+      <c r="B106" s="17"/>
+      <c r="C106" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7574,31 +7713,31 @@
         <v>1691</v>
       </c>
       <c r="T5" s="12" t="s">
+        <v>1749</v>
+      </c>
+      <c r="U5" s="12" t="s">
         <v>1750</v>
       </c>
-      <c r="U5" s="12" t="s">
+      <c r="V5" s="12" t="s">
         <v>1751</v>
       </c>
-      <c r="V5" s="12" t="s">
+      <c r="W5" s="12" t="s">
         <v>1752</v>
       </c>
-      <c r="W5" s="12" t="s">
+      <c r="X5" s="12" t="s">
         <v>1753</v>
       </c>
-      <c r="X5" s="12" t="s">
+      <c r="Y5" s="12" t="s">
         <v>1754</v>
       </c>
-      <c r="Y5" s="12" t="s">
+      <c r="Z5" s="12" t="s">
         <v>1755</v>
       </c>
-      <c r="Z5" s="12" t="s">
+      <c r="AA5" s="12" t="s">
         <v>1756</v>
       </c>
-      <c r="AA5" s="12" t="s">
+      <c r="AB5" s="12" t="s">
         <v>1757</v>
-      </c>
-      <c r="AB5" s="12" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -7672,7 +7811,7 @@
         <v>25</v>
       </c>
       <c r="AB7" s="22" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="153" x14ac:dyDescent="0.2">
@@ -7727,7 +7866,7 @@
         <v>100</v>
       </c>
       <c r="AB8" s="22" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="63.75" x14ac:dyDescent="0.2">
@@ -7797,7 +7936,7 @@
         <v>55</v>
       </c>
       <c r="AB9" s="22" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
@@ -7965,7 +8104,7 @@
         <v>100</v>
       </c>
       <c r="AB13" s="22" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
@@ -8461,7 +8600,7 @@
         <v>190</v>
       </c>
       <c r="AB25" s="22" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="38.25" x14ac:dyDescent="0.25">
@@ -8517,7 +8656,7 @@
         <v>32</v>
       </c>
       <c r="AB26" s="22" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="51" x14ac:dyDescent="0.2">
@@ -8581,7 +8720,7 @@
         <v>100</v>
       </c>
       <c r="AB27" s="22" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="140.25" x14ac:dyDescent="0.2">
@@ -8648,7 +8787,7 @@
         <v>140</v>
       </c>
       <c r="AB28" s="22" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -8709,7 +8848,7 @@
         <v>150</v>
       </c>
       <c r="AB29" s="22" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -8773,7 +8912,7 @@
         <v>100</v>
       </c>
       <c r="AB30" s="22" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="140.25" x14ac:dyDescent="0.2">
@@ -8844,7 +8983,7 @@
         <v>30</v>
       </c>
       <c r="AB31" s="22" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="32" spans="1:28" x14ac:dyDescent="0.2">
@@ -8939,7 +9078,7 @@
         <v>75</v>
       </c>
       <c r="AB33" s="22" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="34" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -9008,7 +9147,7 @@
         <v>85</v>
       </c>
       <c r="AB34" s="22" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="35" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -9120,7 +9259,7 @@
         <v>50</v>
       </c>
       <c r="AB36" s="22" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="37" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -9187,7 +9326,7 @@
         <v>80</v>
       </c>
       <c r="AB37" s="22" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="38" spans="1:28" ht="89.25" x14ac:dyDescent="0.25">
@@ -9250,7 +9389,7 @@
         <v>30</v>
       </c>
       <c r="AB38" s="22" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="39" spans="1:28" x14ac:dyDescent="0.2">
@@ -9333,7 +9472,7 @@
         <v>7000</v>
       </c>
       <c r="AB40" s="22" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="41" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
@@ -9391,7 +9530,7 @@
         <v>9000</v>
       </c>
       <c r="AB41" s="22" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="42" spans="1:28" ht="51" x14ac:dyDescent="0.2">
@@ -9500,7 +9639,7 @@
         <v>2500</v>
       </c>
       <c r="AB43" s="22" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="44" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -9655,7 +9794,7 @@
         <v>5300</v>
       </c>
       <c r="AB46" s="22" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="47" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
@@ -9715,7 +9854,7 @@
         <v>6000</v>
       </c>
       <c r="AB47" s="22" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="48" spans="1:28" ht="63.75" x14ac:dyDescent="0.2">
@@ -9782,7 +9921,7 @@
         <v>45</v>
       </c>
       <c r="AB48" s="22" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="49" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -9843,7 +9982,7 @@
         <v>12</v>
       </c>
       <c r="AB49" s="22" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="50" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -10124,7 +10263,7 @@
         <v>1000</v>
       </c>
       <c r="AB55" s="22" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="56" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -10499,7 +10638,7 @@
         <v>190</v>
       </c>
       <c r="AB64" s="22" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="65" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -10607,7 +10746,7 @@
         <v>120</v>
       </c>
       <c r="AB66" s="22" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="67" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -11232,7 +11371,7 @@
         <v>80</v>
       </c>
       <c r="AB78" s="22" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="79" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -11293,7 +11432,7 @@
         <v>19.5</v>
       </c>
       <c r="AB79" s="22" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="80" spans="1:28" ht="76.5" x14ac:dyDescent="0.2">
@@ -11359,7 +11498,7 @@
         <v>75</v>
       </c>
       <c r="AB80" s="22" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="81" spans="1:28" ht="89.25" x14ac:dyDescent="0.25">
@@ -11425,7 +11564,7 @@
         <v>22</v>
       </c>
       <c r="AB81" s="22" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="82" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -11486,7 +11625,7 @@
         <v>75</v>
       </c>
       <c r="AB82" s="22" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="83" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
@@ -11553,7 +11692,7 @@
         <v>25</v>
       </c>
       <c r="AB83" s="22" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="84" spans="1:28" ht="51" x14ac:dyDescent="0.2">
@@ -11743,7 +11882,7 @@
         <v>126</v>
       </c>
       <c r="AB87" s="22" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="88" spans="1:28" ht="114.75" x14ac:dyDescent="0.2">
@@ -11809,7 +11948,7 @@
         <v>150</v>
       </c>
       <c r="AB88" s="22" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="89" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -11927,7 +12066,7 @@
         <v>80</v>
       </c>
       <c r="AB90" s="22" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="91" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -12332,7 +12471,7 @@
         <v>35</v>
       </c>
       <c r="AB99" s="22" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="100" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -12485,7 +12624,7 @@
         <v>20</v>
       </c>
       <c r="AB102" s="22" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="103" spans="1:28" ht="51" x14ac:dyDescent="0.25">
@@ -12548,7 +12687,7 @@
         <v>25</v>
       </c>
       <c r="AB103" s="22" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="104" spans="1:28" ht="53.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -12615,7 +12754,7 @@
         <v>20</v>
       </c>
       <c r="AB104" s="22" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="105" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
@@ -12678,7 +12817,7 @@
         <v>60000</v>
       </c>
       <c r="AB105" s="22" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="106" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -13431,7 +13570,7 @@
         <v>12</v>
       </c>
       <c r="AB123" s="22" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="124" spans="1:28" ht="76.5" x14ac:dyDescent="0.25">
@@ -13492,7 +13631,7 @@
         <v>27</v>
       </c>
       <c r="AB124" s="22" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="125" spans="1:28" x14ac:dyDescent="0.2">
@@ -13572,7 +13711,7 @@
         <v>45</v>
       </c>
       <c r="AB126" s="22" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="127" spans="1:28" x14ac:dyDescent="0.2">
@@ -13733,7 +13872,7 @@
         <v>60</v>
       </c>
       <c r="AB129" s="22" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="130" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -13943,7 +14082,7 @@
         <v>10</v>
       </c>
       <c r="AB134" s="22" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="135" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -14001,7 +14140,7 @@
         <v>25</v>
       </c>
       <c r="AB135" s="22" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="136" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
@@ -14427,7 +14566,7 @@
         <v>30</v>
       </c>
       <c r="AB145" s="22" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="146" spans="1:28" ht="25.5" x14ac:dyDescent="0.2">
@@ -14755,7 +14894,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G276"/>
+  <dimension ref="A1:G290"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14806,7 +14945,7 @@
         <v>743</v>
       </c>
       <c r="B6" s="61" t="s">
-        <v>736</v>
+        <v>1404</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>744</v>
@@ -14816,8 +14955,8 @@
       <c r="A7" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>1972</v>
+      <c r="B7" s="62">
+        <v>46305</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -15936,7 +16075,7 @@
         <v>858</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>859</v>
@@ -15990,68 +16129,62 @@
         <v>871</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
+    <row r="93" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="C94" s="2">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B96" s="3" t="s">
         <v>873</v>
       </c>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A95" s="6" t="s">
+      <c r="C96" s="4"/>
+      <c r="D96" s="4"/>
+      <c r="E96" s="4"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="4"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="B95" s="6" t="s">
+      <c r="B97" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="C97" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="D97" s="6" t="s">
         <v>875</v>
       </c>
-      <c r="E95" s="6" t="s">
+      <c r="E97" s="6" t="s">
         <v>876</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A96" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C96" s="2">
-        <v>10</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>878</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C97" s="2">
-        <v>5</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>879</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -16059,13 +16192,13 @@
         <v>877</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="C98" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>10</v>
@@ -16076,13 +16209,13 @@
         <v>877</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>340</v>
+        <v>757</v>
       </c>
       <c r="C99" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>10</v>
@@ -16093,13 +16226,13 @@
         <v>877</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>347</v>
+        <v>248</v>
       </c>
       <c r="C100" s="2">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>10</v>
@@ -16110,30 +16243,30 @@
         <v>877</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>247</v>
+        <v>340</v>
       </c>
       <c r="C101" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>884</v>
+        <v>877</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>65</v>
+        <v>347</v>
       </c>
       <c r="C102" s="2">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>10</v>
@@ -16141,41 +16274,41 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>65</v>
+        <v>247</v>
       </c>
       <c r="C103" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C104" s="2">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+        <v>885</v>
+      </c>
+      <c r="E104" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>65</v>
@@ -16184,44 +16317,44 @@
         <v>1</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>1675</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+        <v>887</v>
+      </c>
+      <c r="E105" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C106" s="2">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>889</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>304</v>
+        <v>65</v>
       </c>
       <c r="C107" s="2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="E107" s="7" t="s">
-        <v>10</v>
+        <v>891</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>1675</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -16229,13 +16362,13 @@
         <v>892</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="C108" s="2">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>10</v>
@@ -16243,16 +16376,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>65</v>
+        <v>304</v>
       </c>
       <c r="C109" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>10</v>
@@ -16260,16 +16393,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>65</v>
+        <v>248</v>
       </c>
       <c r="C110" s="2">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>10</v>
@@ -16277,16 +16410,16 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C111" s="2">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>10</v>
@@ -16294,75 +16427,75 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C112" s="2">
-        <v>0.03</v>
+        <v>6</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>247</v>
+        <v>65</v>
       </c>
       <c r="C113" s="2">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C114" s="2">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>757</v>
+        <v>247</v>
       </c>
       <c r="C115" s="2">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>65</v>
@@ -16371,469 +16504,433 @@
         <v>0.1</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>248</v>
+        <v>757</v>
       </c>
       <c r="C117" s="2">
-        <v>0.4</v>
+        <v>0.15</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C118" s="2">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>587</v>
+        <v>909</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>65</v>
+        <v>248</v>
       </c>
       <c r="C119" s="2">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C120" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>915</v>
+        <v>587</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C121" s="2">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C122" s="2">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C123" s="2">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>1964</v>
+        <v>918</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C124" s="2">
-        <v>25</v>
+        <v>0.4</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1965</v>
+        <v>919</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A126" s="3" t="s">
+    <row r="125" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C125" s="2">
+        <v>4</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="E125" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C126" s="2">
+        <v>25</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="E126" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C127" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E127" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="3" t="s">
         <v>922</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B129" s="3" t="s">
         <v>923</v>
       </c>
-      <c r="C126" s="4"/>
-      <c r="D126" s="4"/>
-      <c r="E126" s="4"/>
-      <c r="F126" s="4"/>
-      <c r="G126" s="4"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A127" s="6" t="s">
+      <c r="C129" s="4"/>
+      <c r="D129" s="4"/>
+      <c r="E129" s="4"/>
+      <c r="F129" s="4"/>
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="B127" s="6" t="s">
+      <c r="B130" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="C127" s="6" t="s">
+      <c r="C130" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="D127" s="6" t="s">
+      <c r="D130" s="6" t="s">
         <v>925</v>
       </c>
-      <c r="E127" s="6" t="s">
+      <c r="E130" s="6" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A128" s="2" t="s">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
         <v>926</v>
       </c>
-      <c r="B128" s="2">
+      <c r="B131" s="2">
         <v>1.05</v>
       </c>
-      <c r="C128" s="2" t="s">
+      <c r="C131" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="D128" s="2" t="s">
+      <c r="D131" s="2" t="s">
         <v>928</v>
       </c>
-      <c r="E128" s="7" t="s">
+      <c r="E131" s="7" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A130" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="B130" s="3" t="s">
-        <v>1727</v>
-      </c>
-      <c r="C130" s="4"/>
-      <c r="D130" s="4"/>
-      <c r="E130" s="4"/>
-      <c r="F130" s="4"/>
-      <c r="G130" s="4"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A131" s="6" t="s">
-        <v>750</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>930</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>931</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>933</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>936</v>
+        <v>1975</v>
+      </c>
+      <c r="B132" s="2">
+        <v>0.5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>937</v>
+        <v>1976</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1805</v>
-      </c>
-      <c r="E132" s="2">
-        <v>7</v>
-      </c>
-      <c r="F132" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1977</v>
+      </c>
+      <c r="E132" s="7" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>936</v>
+        <v>1979</v>
+      </c>
+      <c r="B133" s="2">
+        <v>20</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>938</v>
+        <v>1980</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="E133" s="2">
-        <v>2</v>
-      </c>
-      <c r="F133" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1981</v>
+      </c>
+      <c r="E133" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>936</v>
+        <v>1983</v>
+      </c>
+      <c r="B134" s="2">
+        <v>10</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>938</v>
+        <v>1984</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>940</v>
-      </c>
-      <c r="E134" s="2">
-        <v>1</v>
-      </c>
-      <c r="F134" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1985</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>936</v>
+        <v>1986</v>
+      </c>
+      <c r="B135" s="2">
+        <v>3</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>938</v>
+        <v>1987</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>941</v>
-      </c>
-      <c r="E135" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F135" s="2">
-        <v>11</v>
+        <v>1985</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>1982</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>936</v>
+        <v>1988</v>
+      </c>
+      <c r="B136" s="2">
+        <v>1</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>938</v>
+        <v>1989</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1960</v>
-      </c>
-      <c r="E136" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F136" s="2">
-        <v>11</v>
+        <v>1985</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>1982</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>936</v>
+        <v>1990</v>
+      </c>
+      <c r="B137" s="2">
+        <v>2</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>938</v>
+        <v>1991</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1961</v>
-      </c>
-      <c r="E137" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F137" s="2">
-        <v>11</v>
+        <v>1985</v>
+      </c>
+      <c r="E137" s="7" t="s">
+        <v>1982</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>936</v>
+        <v>1992</v>
+      </c>
+      <c r="B138" s="2">
+        <v>2</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>938</v>
+        <v>1993</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1962</v>
-      </c>
-      <c r="E138" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F138" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1985</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>936</v>
+        <v>1994</v>
+      </c>
+      <c r="B139" s="2">
+        <v>2</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>938</v>
+        <v>1995</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E139" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F139" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1985</v>
+      </c>
+      <c r="E139" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>936</v>
+        <v>1996</v>
+      </c>
+      <c r="B140" s="2">
+        <v>2</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>938</v>
+        <v>1997</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>942</v>
-      </c>
-      <c r="E140" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F140" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A141" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>1806</v>
-      </c>
-      <c r="E141" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F141" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A142" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>1807</v>
-      </c>
-      <c r="E142" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F142" s="2">
-        <v>11</v>
-      </c>
+        <v>1985</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>1808</v>
-      </c>
-      <c r="E143" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F143" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>935</v>
       </c>
@@ -16841,13 +16938,13 @@
         <v>936</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="E144" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F144" s="2">
         <v>11</v>
@@ -16864,13 +16961,13 @@
         <v>938</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>1810</v>
+        <v>939</v>
       </c>
       <c r="E145" s="2">
         <v>2</v>
       </c>
       <c r="F145" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -16884,1351 +16981,1430 @@
         <v>938</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>1811</v>
+        <v>940</v>
       </c>
       <c r="E146" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F146" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="E147" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F147" s="2">
         <v>11</v>
       </c>
-      <c r="F147" s="2"/>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>947</v>
+        <v>1959</v>
       </c>
       <c r="E148" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="F148" s="2"/>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="F148" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>948</v>
+        <v>1960</v>
       </c>
       <c r="E149" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="F149" s="2"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="F149" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>951</v>
+        <v>1961</v>
       </c>
       <c r="E150" s="2">
-        <v>13.5</v>
-      </c>
-      <c r="F150" s="2"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="F150" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>952</v>
+        <v>1962</v>
       </c>
       <c r="E151" s="2">
-        <v>11.5</v>
-      </c>
-      <c r="F151" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="F151" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>953</v>
+        <v>942</v>
       </c>
       <c r="E152" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="F152" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="F152" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>954</v>
+        <v>1805</v>
       </c>
       <c r="E153" s="2">
-        <v>6</v>
-      </c>
-      <c r="F153" s="2"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="F153" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1037</v>
+        <v>1806</v>
       </c>
       <c r="E154" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F154" s="2"/>
+        <v>0.5</v>
+      </c>
+      <c r="F154" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>955</v>
+        <v>1807</v>
       </c>
       <c r="E155" s="2">
-        <v>1</v>
-      </c>
-      <c r="F155" s="2"/>
-    </row>
-    <row r="156" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+      <c r="F155" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>956</v>
+        <v>1808</v>
       </c>
       <c r="E156" s="2">
-        <v>2</v>
-      </c>
-      <c r="F156" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="F156" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>957</v>
+        <v>935</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>959</v>
+        <v>1809</v>
       </c>
       <c r="E157" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="F157" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="F157" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>957</v>
+        <v>935</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>960</v>
+        <v>1810</v>
       </c>
       <c r="E158" s="2">
-        <v>4</v>
-      </c>
-      <c r="F158" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="F158" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>961</v>
+        <v>946</v>
       </c>
       <c r="E159" s="2">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F159" s="2"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>962</v>
+        <v>947</v>
       </c>
       <c r="E160" s="2">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="F160" s="2"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>963</v>
+        <v>948</v>
       </c>
       <c r="E161" s="2">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="F161" s="2"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>937</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>964</v>
+        <v>951</v>
       </c>
       <c r="E162" s="2">
-        <v>3</v>
+        <v>13.5</v>
       </c>
       <c r="F162" s="2"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>965</v>
+        <v>952</v>
       </c>
       <c r="E163" s="2">
-        <v>0.5</v>
+        <v>11.5</v>
       </c>
       <c r="F163" s="2"/>
     </row>
-    <row r="164" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>937</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>966</v>
+        <v>953</v>
       </c>
       <c r="E164" s="2">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="F164" s="2"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>937</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>969</v>
+        <v>954</v>
       </c>
       <c r="E165" s="2">
-        <v>5</v>
-      </c>
-      <c r="F165" s="2">
-        <v>10</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F165" s="2"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>970</v>
+        <v>1037</v>
       </c>
       <c r="E166" s="2">
-        <v>2</v>
-      </c>
-      <c r="F166" s="2">
-        <v>10</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F166" s="2"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>971</v>
+        <v>955</v>
       </c>
       <c r="E167" s="2">
-        <v>2</v>
-      </c>
-      <c r="F167" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="F167" s="2"/>
+    </row>
+    <row r="168" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>972</v>
+        <v>956</v>
       </c>
       <c r="E168" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F168" s="2">
-        <v>10</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F168" s="2"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
       <c r="E169" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="F169" s="2">
-        <v>10</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="F169" s="2"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
       <c r="E170" s="2">
-        <v>1</v>
-      </c>
-      <c r="F170" s="2">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F170" s="2"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="E171" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F171" s="2">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F171" s="2"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>976</v>
+        <v>962</v>
       </c>
       <c r="E172" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F172" s="2">
-        <v>10</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F172" s="2"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>977</v>
+        <v>963</v>
       </c>
       <c r="E173" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F173" s="2">
-        <v>10</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F173" s="2"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
       <c r="E174" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F174" s="2">
-        <v>10</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F174" s="2"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>938</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="E175" s="2">
-        <v>1</v>
-      </c>
-      <c r="F175" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="F175" s="2"/>
+    </row>
+    <row r="176" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>966</v>
+      </c>
+      <c r="E176" s="2">
+        <v>4</v>
+      </c>
+      <c r="F176" s="2"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
         <v>967</v>
       </c>
-      <c r="B176" s="2" t="s">
+      <c r="B177" s="2" t="s">
         <v>968</v>
       </c>
-      <c r="C176" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="E176" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="F176" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A177" s="2" t="s">
-        <v>980</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>981</v>
-      </c>
       <c r="C177" s="2" t="s">
-        <v>982</v>
+        <v>937</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="E177" s="2">
         <v>5</v>
       </c>
       <c r="F177" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>987</v>
+        <v>970</v>
       </c>
       <c r="E178" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F178" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>988</v>
+        <v>971</v>
       </c>
       <c r="E179" s="2">
         <v>2</v>
       </c>
       <c r="F179" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>989</v>
+        <v>972</v>
       </c>
       <c r="E180" s="2">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="F180" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>990</v>
+        <v>973</v>
       </c>
       <c r="E181" s="2">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="F181" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>991</v>
+        <v>968</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="E182" s="2">
         <v>1</v>
       </c>
       <c r="F182" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E183" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F183" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="E184" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F184" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="E185" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F185" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E186" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F186" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="E187" s="2">
+        <v>1</v>
+      </c>
+      <c r="F187" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="E188" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F188" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>983</v>
+      </c>
+      <c r="E189" s="2">
+        <v>5</v>
+      </c>
+      <c r="F189" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="E190" s="2">
+        <v>0</v>
+      </c>
+      <c r="F190" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A183" s="2" t="s">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="C183" s="2" t="s">
+      <c r="B191" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="D183" s="2" t="s">
-        <v>993</v>
-      </c>
-      <c r="E183" s="2">
+      <c r="D191" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="E191" s="2">
         <v>2</v>
       </c>
-      <c r="F183" s="2">
+      <c r="F191" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A184" s="2" t="s">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
         <v>984</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="C184" s="2" t="s">
+      <c r="B192" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>986</v>
       </c>
-      <c r="D184" s="2" t="s">
-        <v>994</v>
-      </c>
-      <c r="E184" s="2">
-        <v>3</v>
-      </c>
-      <c r="F184" s="2">
+      <c r="D192" s="2" t="s">
+        <v>989</v>
+      </c>
+      <c r="E192" s="2">
+        <v>4</v>
+      </c>
+      <c r="F192" s="2">
         <v>12</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>995</v>
-      </c>
-      <c r="E185" s="2">
-        <v>4</v>
-      </c>
-      <c r="F185" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A186" s="2" t="s">
-        <v>984</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>991</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>986</v>
-      </c>
-      <c r="D186" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="E186" s="2">
-        <v>5</v>
-      </c>
-      <c r="F186" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>997</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>999</v>
-      </c>
-      <c r="E187" s="2">
-        <v>20</v>
-      </c>
-      <c r="F187" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C189" s="4"/>
-      <c r="D189" s="4"/>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A190" s="6" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C190" s="6" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="E190" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>1012</v>
+        <v>984</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>1013</v>
+        <v>985</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>746</v>
+        <v>990</v>
+      </c>
+      <c r="E193" s="2">
+        <v>6</v>
+      </c>
+      <c r="F193" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>1015</v>
+        <v>984</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>1016</v>
+        <v>991</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>1017</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>746</v>
+        <v>992</v>
+      </c>
+      <c r="E194" s="2">
+        <v>1</v>
+      </c>
+      <c r="F194" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>1018</v>
+        <v>984</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>1019</v>
+        <v>991</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>746</v>
+        <v>993</v>
+      </c>
+      <c r="E195" s="2">
+        <v>2</v>
+      </c>
+      <c r="F195" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>1021</v>
+        <v>984</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>1022</v>
+        <v>991</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>746</v>
+        <v>994</v>
+      </c>
+      <c r="E196" s="2">
+        <v>3</v>
+      </c>
+      <c r="F196" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>1024</v>
+        <v>984</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1025</v>
+        <v>991</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>746</v>
+        <v>995</v>
+      </c>
+      <c r="E197" s="2">
+        <v>4</v>
+      </c>
+      <c r="F197" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>1027</v>
+        <v>984</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1028</v>
+        <v>991</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>1007</v>
+        <v>986</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>746</v>
+        <v>996</v>
+      </c>
+      <c r="E198" s="2">
+        <v>5</v>
+      </c>
+      <c r="F198" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>1030</v>
+        <v>997</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1031</v>
+        <v>998</v>
       </c>
       <c r="C199" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="E199" s="2">
+        <v>20</v>
+      </c>
+      <c r="F199" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B201" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="4"/>
+      <c r="G201" s="4"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D199" s="2" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E199" s="2" t="s">
+      <c r="D203" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A200" s="30" t="s">
-        <v>729</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="C200" s="2" t="s">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>1007</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="E200" s="30" t="s">
-        <v>1617</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A202" s="3" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B202" s="3" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C202" s="4"/>
-      <c r="D202" s="4"/>
-      <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="6" t="s">
-        <v>1040</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="C203" s="6" t="s">
-        <v>795</v>
-      </c>
-      <c r="D203" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B204" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="C204" s="2">
-        <v>1.1499999999999999</v>
-      </c>
       <c r="D204" s="2" t="s">
-        <v>1041</v>
+        <v>1011</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="B205" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="C205" s="2">
-        <v>1.2</v>
+        <v>1012</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>949</v>
-      </c>
-      <c r="B206" s="2">
-        <v>0.85</v>
-      </c>
-      <c r="C206" s="2">
-        <v>1.25</v>
+        <v>1015</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>957</v>
-      </c>
-      <c r="B207" s="2">
-        <v>0.8</v>
-      </c>
-      <c r="C207" s="2">
-        <v>1.35</v>
+        <v>1018</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A209" s="3" t="s">
-        <v>1812</v>
-      </c>
-      <c r="B209" s="3" t="s">
-        <v>1813</v>
-      </c>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
+      <c r="A209" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A210" s="6" t="s">
-        <v>874</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>1814</v>
-      </c>
-      <c r="C210" s="6" t="s">
-        <v>1815</v>
-      </c>
-      <c r="D210" s="6" t="s">
-        <v>1816</v>
-      </c>
-      <c r="E210" s="6" t="s">
-        <v>1817</v>
+      <c r="A210" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>1818</v>
+        <v>1030</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="C211" s="2">
-        <v>1</v>
-      </c>
-      <c r="D211" s="2"/>
-      <c r="E211" s="2"/>
+        <v>1031</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>746</v>
+      </c>
     </row>
     <row r="212" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A212" s="2" t="s">
-        <v>1820</v>
+      <c r="A212" s="30" t="s">
+        <v>729</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C212" s="2">
-        <v>3</v>
-      </c>
-      <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
-    </row>
-    <row r="213" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A213" s="2" t="s">
-        <v>1822</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C213" s="2">
-        <v>6</v>
-      </c>
-      <c r="D213" s="2"/>
-      <c r="E213" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="E212" s="30" t="s">
+        <v>1617</v>
+      </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A214" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="C214" s="2">
-        <v>1</v>
-      </c>
-      <c r="D214" s="2"/>
-      <c r="E214" s="2" t="s">
-        <v>943</v>
-      </c>
+      <c r="A214" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C214" s="4"/>
+      <c r="D214" s="4"/>
+      <c r="E214" s="4"/>
+      <c r="F214" s="4"/>
+      <c r="G214" s="4"/>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>1826</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C215" s="2">
-        <v>2</v>
-      </c>
-      <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
+      <c r="A215" s="6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>795</v>
+      </c>
+      <c r="D215" s="6" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="216" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>1828</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>1829</v>
+        <v>935</v>
+      </c>
+      <c r="B216" s="2">
+        <v>0.9</v>
       </c>
       <c r="C216" s="2">
-        <v>1</v>
-      </c>
-      <c r="D216" s="2"/>
-      <c r="E216" s="2"/>
-    </row>
-    <row r="217" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>1830</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>1831</v>
+        <v>943</v>
+      </c>
+      <c r="B217" s="2">
+        <v>0.9</v>
       </c>
       <c r="C217" s="2">
-        <v>1</v>
-      </c>
-      <c r="D217" s="2"/>
-      <c r="E217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>1832</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>1833</v>
+        <v>949</v>
+      </c>
+      <c r="B218" s="2">
+        <v>0.85</v>
       </c>
       <c r="C218" s="2">
-        <v>0</v>
-      </c>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2" t="s">
-        <v>949</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>1834</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>1835</v>
+        <v>957</v>
+      </c>
+      <c r="B219" s="2">
+        <v>0.8</v>
       </c>
       <c r="C219" s="2">
-        <v>1</v>
-      </c>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
+        <v>1.35</v>
+      </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>1836</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>1837</v>
+        <v>1973</v>
+      </c>
+      <c r="B220" s="2">
+        <v>0.89</v>
       </c>
       <c r="C220" s="2">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="3" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C222" s="4"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="4"/>
+      <c r="G222" s="4"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D223" s="6" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="C224" s="2">
         <v>1</v>
-      </c>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
-        <v>1838</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="C221" s="2">
-        <v>1</v>
-      </c>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
-        <v>1840</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>1841</v>
-      </c>
-      <c r="C222" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C223" s="2">
-        <v>1</v>
-      </c>
-      <c r="D223" s="2"/>
-      <c r="E223" s="2"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C224" s="2">
-        <v>0.5</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
     </row>
-    <row r="225" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>1846</v>
+        <v>1819</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>1847</v>
+        <v>1820</v>
       </c>
       <c r="C225" s="2">
+        <v>3</v>
+      </c>
+      <c r="D225" s="2"/>
+      <c r="E225" s="2"/>
+    </row>
+    <row r="226" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="C226" s="2">
+        <v>6</v>
+      </c>
+      <c r="D226" s="2"/>
+      <c r="E226" s="2"/>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C227" s="2">
         <v>1</v>
       </c>
-      <c r="D225" s="2">
+      <c r="D227" s="2"/>
+      <c r="E227" s="2" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C228" s="2">
         <v>2</v>
-      </c>
-      <c r="E225" s="2"/>
-    </row>
-    <row r="226" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
-        <v>1848</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>1849</v>
-      </c>
-      <c r="C226" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="D226" s="2">
-        <v>0.25</v>
-      </c>
-      <c r="E226" s="2"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>1851</v>
-      </c>
-      <c r="C227" s="2">
-        <v>2</v>
-      </c>
-      <c r="D227" s="2"/>
-      <c r="E227" s="2"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>1853</v>
-      </c>
-      <c r="C228" s="2">
-        <v>1</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
     </row>
-    <row r="229" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>1854</v>
+        <v>1827</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>1855</v>
+        <v>1828</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
@@ -18236,12 +18412,12 @@
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
     </row>
-    <row r="230" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>1856</v>
+        <v>1829</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>1857</v>
+        <v>1830</v>
       </c>
       <c r="C230" s="2">
         <v>1</v>
@@ -18249,25 +18425,27 @@
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>1858</v>
+        <v>1831</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>1859</v>
+        <v>1832</v>
       </c>
       <c r="C231" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-    </row>
-    <row r="232" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E231" s="2" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>1860</v>
+        <v>1833</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>1861</v>
+        <v>1834</v>
       </c>
       <c r="C232" s="2">
         <v>1</v>
@@ -18275,620 +18453,810 @@
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A234" s="3" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B234" s="3" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-    </row>
-    <row r="235" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A235" s="6" t="s">
-        <v>874</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>1864</v>
-      </c>
-      <c r="C235" s="6" t="s">
-        <v>1865</v>
-      </c>
-      <c r="D235" s="6" t="s">
-        <v>1866</v>
-      </c>
-      <c r="E235" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="C233" s="2">
+        <v>1</v>
+      </c>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="C234" s="2">
+        <v>1</v>
+      </c>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="C235" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>1867</v>
+        <v>1841</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D236" s="2">
-        <v>5</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>1869</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1842</v>
+      </c>
+      <c r="C236" s="2">
+        <v>1</v>
+      </c>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>1870</v>
+        <v>1843</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>1871</v>
-      </c>
-      <c r="D237" s="2">
-        <v>3</v>
-      </c>
+        <v>1844</v>
+      </c>
+      <c r="C237" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D237" s="2"/>
       <c r="E237" s="2"/>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>1872</v>
+        <v>1845</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>1873</v>
+        <v>1846</v>
+      </c>
+      <c r="C238" s="2">
+        <v>1</v>
       </c>
       <c r="D238" s="2">
         <v>2</v>
       </c>
       <c r="E238" s="2"/>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C239" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D239" s="2">
+        <v>0.25</v>
+      </c>
+      <c r="E239" s="2"/>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C240" s="2">
+        <v>2</v>
+      </c>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C241" s="2">
+        <v>1</v>
+      </c>
+      <c r="D241" s="2"/>
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C242" s="2">
+        <v>1</v>
+      </c>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+    </row>
+    <row r="243" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C243" s="2">
+        <v>1</v>
+      </c>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+    </row>
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C244" s="2">
+        <v>1</v>
+      </c>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+    </row>
+    <row r="245" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C245" s="2">
+        <v>1</v>
+      </c>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+    </row>
+    <row r="246" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C246" s="2">
+        <v>0</v>
+      </c>
+      <c r="D246" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A248" s="3" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>1862</v>
+      </c>
+      <c r="C248" s="4"/>
+      <c r="D248" s="4"/>
+      <c r="E248" s="4"/>
+      <c r="F248" s="4"/>
+      <c r="G248" s="4"/>
+    </row>
+    <row r="249" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A249" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D249" s="6" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E249" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D250" s="2">
+        <v>5</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D251" s="2">
+        <v>3</v>
+      </c>
+      <c r="E251" s="2"/>
+    </row>
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D252" s="2">
+        <v>2</v>
+      </c>
+      <c r="E252" s="2"/>
+    </row>
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C253" s="2" t="s">
         <v>1874</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C239" s="2" t="s">
+      <c r="D253" s="2">
+        <v>1</v>
+      </c>
+      <c r="E253" s="2"/>
+    </row>
+    <row r="254" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
         <v>1875</v>
       </c>
-      <c r="D239" s="2">
+      <c r="B254" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D254" s="2">
         <v>1</v>
       </c>
-      <c r="E239" s="2"/>
-    </row>
-    <row r="240" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
+      <c r="E254" s="2"/>
+    </row>
+    <row r="255" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
         <v>1876</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>1829</v>
-      </c>
-      <c r="D240" s="2">
+      <c r="B255" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D255" s="2">
         <v>1</v>
       </c>
-      <c r="E240" s="2"/>
-    </row>
-    <row r="241" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
-        <v>1877</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C241" s="2" t="s">
+      <c r="E255" s="2" t="s">
         <v>1878</v>
       </c>
-      <c r="D241" s="2">
+    </row>
+    <row r="256" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="D256" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="D257" s="2">
         <v>1</v>
       </c>
-      <c r="E241" s="2" t="s">
-        <v>1879</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="51" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
-        <v>1880</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>1881</v>
-      </c>
-      <c r="D242" s="2">
+      <c r="E257" s="2"/>
+    </row>
+    <row r="258" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="D258" s="2">
+        <v>2</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D259" s="2">
+        <v>4</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D260" s="2">
+        <v>2</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D261" s="2">
+        <v>1</v>
+      </c>
+      <c r="E261" s="2"/>
+    </row>
+    <row r="262" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="D262" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="D263" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E263" s="2"/>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D264" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D265" s="2">
         <v>0.5</v>
       </c>
-      <c r="E242" s="2" t="s">
-        <v>1882</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
-        <v>1883</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>1868</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>1884</v>
-      </c>
-      <c r="D243" s="2">
+      <c r="E265" s="2"/>
+    </row>
+    <row r="266" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D266" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D267" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D268" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D269" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D270" s="2">
+        <v>3</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D271" s="2">
+        <v>2</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D272" s="2">
         <v>1</v>
       </c>
-      <c r="E243" s="2"/>
-    </row>
-    <row r="244" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>1885</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>1887</v>
-      </c>
-      <c r="D244" s="2">
+      <c r="E272" s="2" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D273" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E273" s="2"/>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D274" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E274" s="2"/>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D275" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E275" s="2"/>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="D276" s="2">
+        <v>25</v>
+      </c>
+      <c r="E276" s="2"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="C278" s="4"/>
+      <c r="D278" s="4"/>
+      <c r="E278" s="4"/>
+      <c r="F278" s="4"/>
+      <c r="G278" s="4"/>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A279" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B282" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B283" s="2">
+        <v>12</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A285" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>1947</v>
+      </c>
+      <c r="C285" s="4"/>
+      <c r="D285" s="4"/>
+      <c r="E285" s="4"/>
+      <c r="F285" s="4"/>
+      <c r="G285" s="4"/>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A286" s="6" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>1949</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>1950</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B287" s="2">
+        <v>0</v>
+      </c>
+      <c r="C287" s="2">
+        <v>0</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B288" s="2">
+        <v>-3</v>
+      </c>
+      <c r="C288" s="2">
         <v>2</v>
       </c>
-      <c r="E244" s="2" t="s">
-        <v>1888</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5" ht="51" x14ac:dyDescent="0.25">
-      <c r="A245" s="2" t="s">
-        <v>1889</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>1839</v>
-      </c>
-      <c r="D245" s="2">
-        <v>4</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>1890</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>1892</v>
-      </c>
-      <c r="D246" s="2">
-        <v>2</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A247" s="2" t="s">
-        <v>1894</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>1895</v>
-      </c>
-      <c r="D247" s="2">
+      <c r="D288" s="2" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B289" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="C289" s="2">
         <v>1</v>
       </c>
-      <c r="E247" s="2"/>
-    </row>
-    <row r="248" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A248" s="2" t="s">
-        <v>1896</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>1897</v>
-      </c>
-      <c r="D248" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>1899</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D249" s="2">
-        <v>0.75</v>
-      </c>
-      <c r="E249" s="2"/>
-    </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>1902</v>
-      </c>
-      <c r="D250" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>1903</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A251" s="2" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>1905</v>
-      </c>
-      <c r="D251" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E251" s="2"/>
-    </row>
-    <row r="252" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A252" s="2" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>1907</v>
-      </c>
-      <c r="D252" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A253" s="2" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>1910</v>
-      </c>
-      <c r="D253" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>1911</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A254" s="2" t="s">
-        <v>1912</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>1913</v>
-      </c>
-      <c r="D254" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>1914</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A255" s="2" t="s">
-        <v>1915</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>1886</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>1916</v>
-      </c>
-      <c r="D255" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>1917</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A256" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>1825</v>
-      </c>
-      <c r="D256" s="2">
-        <v>3</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>1921</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>1919</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>1922</v>
-      </c>
-      <c r="D257" s="2">
-        <v>2</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
-        <v>1923</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>1925</v>
-      </c>
-      <c r="D258" s="2">
-        <v>1</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A259" s="2" t="s">
-        <v>1926</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>1927</v>
-      </c>
-      <c r="D259" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E259" s="2"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A260" s="2" t="s">
-        <v>1928</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D260" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E260" s="2"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>1924</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>1931</v>
-      </c>
-      <c r="D261" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E261" s="2"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>1932</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>1934</v>
-      </c>
-      <c r="D262" s="2">
-        <v>25</v>
-      </c>
-      <c r="E262" s="2"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A264" s="3" t="s">
-        <v>1935</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="4"/>
-      <c r="G264" s="4"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A265" s="6" t="s">
-        <v>874</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>742</v>
-      </c>
-      <c r="C265" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
-        <v>1937</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>1938</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>1939</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A267" s="2" t="s">
-        <v>1940</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>1941</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>1942</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>1943</v>
-      </c>
-      <c r="B268" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>1945</v>
-      </c>
-      <c r="B269" s="2">
-        <v>12</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>1946</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A271" s="3" t="s">
-        <v>1947</v>
-      </c>
-      <c r="B271" s="3" t="s">
-        <v>1948</v>
-      </c>
-      <c r="C271" s="4"/>
-      <c r="D271" s="4"/>
-      <c r="E271" s="4"/>
-      <c r="F271" s="4"/>
-      <c r="G271" s="4"/>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A272" s="6" t="s">
-        <v>1949</v>
-      </c>
-      <c r="B272" s="6" t="s">
-        <v>1950</v>
-      </c>
-      <c r="C272" s="6" t="s">
-        <v>1951</v>
-      </c>
-      <c r="D272" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A273" s="2" t="s">
-        <v>1952</v>
-      </c>
-      <c r="B273" s="2">
+      <c r="D289" s="2" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B290" s="2">
         <v>0</v>
       </c>
-      <c r="C273" s="2">
+      <c r="C290" s="2">
         <v>0</v>
       </c>
-      <c r="D273" s="2" t="s">
-        <v>1953</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>1954</v>
-      </c>
-      <c r="B274" s="2">
-        <v>-3</v>
-      </c>
-      <c r="C274" s="2">
-        <v>2</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>1955</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
-        <v>1956</v>
-      </c>
-      <c r="B275" s="2">
-        <v>-1.5</v>
-      </c>
-      <c r="C275" s="2">
-        <v>1</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>1957</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A276" s="2" t="s">
+      <c r="D290" s="2" t="s">
         <v>1958</v>
-      </c>
-      <c r="B276" s="2">
-        <v>0</v>
-      </c>
-      <c r="C276" s="2">
-        <v>0</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>1959</v>
       </c>
     </row>
   </sheetData>
@@ -19001,7 +19369,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>69</v>
@@ -19755,7 +20123,7 @@
         <v>63</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>177</v>
@@ -19799,7 +20167,7 @@
         <v>63</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>177</v>
@@ -19887,7 +20255,7 @@
         <v>63</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>177</v>
@@ -19931,7 +20299,7 @@
         <v>63</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>177</v>
@@ -19975,7 +20343,7 @@
         <v>63</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>177</v>
@@ -20243,7 +20611,7 @@
         <v>63</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>177</v>
@@ -20683,7 +21051,7 @@
         <v>63</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>85</v>
+        <v>2001</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>177</v>
@@ -20731,7 +21099,7 @@
         <v>63</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>85</v>
+        <v>2001</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>177</v>
@@ -20779,7 +21147,7 @@
         <v>63</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>85</v>
+        <v>2001</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>177</v>
@@ -20955,7 +21323,7 @@
         <v>63</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>85</v>
+        <v>2001</v>
       </c>
       <c r="H50" s="15" t="s">
         <v>177</v>
@@ -21269,7 +21637,7 @@
         <v>63</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>85</v>
+        <v>2000</v>
       </c>
       <c r="H57" s="15" t="s">
         <v>177</v>
@@ -21799,7 +22167,7 @@
         <v>63</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>85</v>
+        <v>2001</v>
       </c>
       <c r="H69" s="15" t="s">
         <v>61</v>
@@ -22241,7 +22609,7 @@
         <v>63</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H79" s="15" t="s">
         <v>649</v>
@@ -24607,7 +24975,7 @@
         <v>373</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F143" s="15" t="s">
         <v>67</v>
@@ -24855,7 +25223,7 @@
         <v>396</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>67</v>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8CEDBA-193B-44AD-83E1-FA7C8520DD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8930164-0AD5-4E3B-93E8-2E6FB0A3A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4603" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4612" uniqueCount="2020">
   <si>
     <t>3. Settings</t>
   </si>
@@ -6070,6 +6070,27 @@
   </si>
   <si>
     <t>No rate changed. Industrial / warehouse new build and extensions are split into offices and the main space (owner, 10 Oct 2026): new inputs OFFICES (Q1.3a share × GIFA; default GIFA × r.office_share) and PRODUCTION (Q1.3b Factory / production → the rest of the floor, Storage / warehouse → 0); new ratio office_share 0.10 (suggestion, AI estimate – verify). On those projects internal walls, internal doors, wall / floor / ceiling finishes, signage and data are measured on OFFICES, and heating, water, ventilation, power and builder's work on OFFICES + PRODUCTION. Every other building use and project type is measured on GIFA as before.</t>
+  </si>
+  <si>
+    <t>risk_level_low_max</t>
+  </si>
+  <si>
+    <t>Report risk level: risk + contingency % at or below this reads Low</t>
+  </si>
+  <si>
+    <t>Every report (label only; never changes the estimate)</t>
+  </si>
+  <si>
+    <t>risk_level_medium_max</t>
+  </si>
+  <si>
+    <t>Report risk level: at or below this reads Medium; above it, High</t>
+  </si>
+  <si>
+    <t>v5.23 — 11 Oct 2026</t>
+  </si>
+  <si>
+    <t>No figure the estimate uses changed. The last number the app held in its code now lives here: ▶ factors gains risk_level_low_max (11) and risk_level_medium_max (13) — the risk + contingency % at or below which the report's risk level reads Low or Medium (above: High). The app now also refuses this workbook if a prelims (A) or risk (E) BASE row loses its cap, the OH&amp;P (B) rows leave a works value uncovered, or the fee (C) BASE rows leave a design stage 0–4 uncovered — it no longer has backup percentages to fall back on.</t>
   </si>
 </sst>
 </file>
@@ -6696,7 +6717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C106"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -7391,223 +7412,231 @@
       <c r="B80" s="16"/>
       <c r="C80" s="34"/>
     </row>
-    <row r="81" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="s">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>2012</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="82" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A82" s="17" t="s">
-        <v>1998</v>
+        <v>2011</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>1999</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A83" s="17" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="17" t="s">
         <v>1969</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B84" s="17" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="84" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+    <row r="85" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A85" s="17" t="s">
         <v>1731</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>1732</v>
       </c>
     </row>
-    <row r="85" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A85" s="17" t="s">
+    <row r="86" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="s">
         <v>1733</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>1734</v>
       </c>
     </row>
-    <row r="86" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A86" s="17" t="s">
+    <row r="87" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A87" s="17" t="s">
         <v>1735</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B87" s="17" t="s">
         <v>1736</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A87" s="17" t="s">
-        <v>1737</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="88" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A88" s="17" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="89" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A89" s="17" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="90" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A90" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B90" s="17" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A91" s="17" t="s">
         <v>1743</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>1744</v>
       </c>
     </row>
-    <row r="91" spans="1:3" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
+    <row r="92" spans="1:3" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="17" t="s">
         <v>1745</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>1746</v>
       </c>
     </row>
-    <row r="92" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+    <row r="93" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="17" t="s">
         <v>1747</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B93" s="17" t="s">
         <v>1748</v>
       </c>
     </row>
-    <row r="93" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="17" t="s">
+    <row r="94" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="17" t="s">
         <v>1715</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B94" s="17" t="s">
         <v>1716</v>
       </c>
-      <c r="C93" s="60"/>
-    </row>
-    <row r="94" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="17" t="s">
+      <c r="C94" s="60"/>
+    </row>
+    <row r="95" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="17" t="s">
         <v>1689</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B95" s="17" t="s">
         <v>1718</v>
       </c>
-      <c r="C94" s="60"/>
-    </row>
-    <row r="95" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A95" s="17" t="s">
+      <c r="C95" s="60"/>
+    </row>
+    <row r="96" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A96" s="17" t="s">
         <v>1680</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B96" s="17" t="s">
         <v>1686</v>
       </c>
-      <c r="C95" s="60"/>
-    </row>
-    <row r="96" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A96" s="17" t="s">
+      <c r="C96" s="60"/>
+    </row>
+    <row r="97" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A97" s="17" t="s">
         <v>1678</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>1679</v>
       </c>
-      <c r="C96" s="60"/>
-    </row>
-    <row r="97" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+      <c r="C97" s="60"/>
+    </row>
+    <row r="98" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A98" s="17" t="s">
         <v>1619</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B98" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C97" s="60"/>
-    </row>
-    <row r="98" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A98" s="15" t="s">
+      <c r="C98" s="60"/>
+    </row>
+    <row r="99" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A99" s="15" t="s">
         <v>1608</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B99" s="17" t="s">
         <v>1609</v>
       </c>
-      <c r="C98" s="33"/>
-    </row>
-    <row r="99" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A99" s="15" t="s">
+      <c r="C99" s="33"/>
+    </row>
+    <row r="100" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A100" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B100" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C99" s="33"/>
-    </row>
-    <row r="100" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A100" s="15" t="s">
+      <c r="C100" s="33"/>
+    </row>
+    <row r="101" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A101" s="15" t="s">
         <v>1042</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B101" s="17" t="s">
         <v>1043</v>
       </c>
-      <c r="C100" s="33"/>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A101" s="15" t="s">
+      <c r="C101" s="33"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B102" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C101" s="33"/>
-    </row>
-    <row r="102" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A102" s="15" t="s">
+      <c r="C102" s="33"/>
+    </row>
+    <row r="103" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A103" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B103" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="33"/>
-    </row>
-    <row r="103" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A103" s="15" t="s">
+      <c r="C103" s="33"/>
+    </row>
+    <row r="104" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A104" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B104" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C103" s="33"/>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A104" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C104" s="33"/>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A105" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C105" s="33"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B105" s="17" t="s">
+      <c r="B106" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C105" s="33"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A106" s="15"/>
-      <c r="B106" s="17"/>
       <c r="C106" s="33"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="15"/>
+      <c r="B107" s="17"/>
+      <c r="C107" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14894,7 +14923,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G290"/>
+  <dimension ref="A1:G292"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -14944,8 +14973,8 @@
       <c r="A6" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B6" s="61" t="s">
-        <v>1404</v>
+      <c r="B6" s="61">
+        <v>5.23</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>744</v>
@@ -14956,7 +14985,7 @@
         <v>745</v>
       </c>
       <c r="B7" s="62">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -16897,80 +16926,74 @@
         <v>1982</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
+    <row r="141" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B141" s="2">
+        <v>11</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B142" s="2">
+        <v>13</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="3" t="s">
         <v>929</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B144" s="3" t="s">
         <v>1727</v>
       </c>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
-      <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="6" t="s">
+      <c r="C144" s="4"/>
+      <c r="D144" s="4"/>
+      <c r="E144" s="4"/>
+      <c r="F144" s="4"/>
+      <c r="G144" s="4"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="6" t="s">
         <v>750</v>
       </c>
-      <c r="B143" s="6" t="s">
+      <c r="B145" s="6" t="s">
         <v>930</v>
       </c>
-      <c r="C143" s="6" t="s">
+      <c r="C145" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="D145" s="6" t="s">
         <v>932</v>
       </c>
-      <c r="E143" s="6" t="s">
+      <c r="E145" s="6" t="s">
         <v>933</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="F145" s="6" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A144" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>937</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>1804</v>
-      </c>
-      <c r="E144" s="2">
-        <v>7</v>
-      </c>
-      <c r="F144" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>936</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>938</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>939</v>
-      </c>
-      <c r="E145" s="2">
-        <v>2</v>
-      </c>
-      <c r="F145" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>935</v>
       </c>
@@ -16978,13 +17001,13 @@
         <v>936</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>940</v>
+        <v>1804</v>
       </c>
       <c r="E146" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F146" s="2">
         <v>11</v>
@@ -17001,16 +17024,16 @@
         <v>938</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="E147" s="2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F147" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>935</v>
       </c>
@@ -17021,16 +17044,16 @@
         <v>938</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>1959</v>
+        <v>940</v>
       </c>
       <c r="E148" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F148" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="149" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>935</v>
       </c>
@@ -17041,7 +17064,7 @@
         <v>938</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>1960</v>
+        <v>941</v>
       </c>
       <c r="E149" s="2">
         <v>0.5</v>
@@ -17061,7 +17084,7 @@
         <v>938</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="E150" s="2">
         <v>0.5</v>
@@ -17081,7 +17104,7 @@
         <v>938</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="E151" s="2">
         <v>0.5</v>
@@ -17090,7 +17113,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>935</v>
       </c>
@@ -17101,7 +17124,7 @@
         <v>938</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>942</v>
+        <v>1961</v>
       </c>
       <c r="E152" s="2">
         <v>0.5</v>
@@ -17110,7 +17133,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>935</v>
       </c>
@@ -17121,7 +17144,7 @@
         <v>938</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1805</v>
+        <v>1962</v>
       </c>
       <c r="E153" s="2">
         <v>0.5</v>
@@ -17130,7 +17153,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="154" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>935</v>
       </c>
@@ -17141,7 +17164,7 @@
         <v>938</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>1806</v>
+        <v>942</v>
       </c>
       <c r="E154" s="2">
         <v>0.5</v>
@@ -17161,16 +17184,16 @@
         <v>938</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="E155" s="2">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F155" s="2">
         <v>11</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>935</v>
       </c>
@@ -17181,10 +17204,10 @@
         <v>938</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="E156" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F156" s="2">
         <v>11</v>
@@ -17201,13 +17224,13 @@
         <v>938</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="E157" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F157" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -17221,50 +17244,54 @@
         <v>938</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="E158" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F158" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>946</v>
+        <v>1809</v>
       </c>
       <c r="E159" s="2">
-        <v>11</v>
-      </c>
-      <c r="F159" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="F159" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>943</v>
+        <v>935</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>944</v>
+        <v>936</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>947</v>
+        <v>1810</v>
       </c>
       <c r="E160" s="2">
-        <v>9.5</v>
-      </c>
-      <c r="F160" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="F160" s="2">
+        <v>14</v>
+      </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
@@ -17277,46 +17304,46 @@
         <v>945</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E161" s="2">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="F161" s="2"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="E162" s="2">
-        <v>13.5</v>
+        <v>9.5</v>
       </c>
       <c r="F162" s="2"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="E163" s="2">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="F163" s="2"/>
     </row>
@@ -17331,10 +17358,10 @@
         <v>937</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E164" s="2">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="F164" s="2"/>
     </row>
@@ -17349,10 +17376,10 @@
         <v>937</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="E165" s="2">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="F165" s="2"/>
     </row>
@@ -17364,13 +17391,13 @@
         <v>950</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1037</v>
+        <v>953</v>
       </c>
       <c r="E166" s="2">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F166" s="2"/>
     </row>
@@ -17382,17 +17409,17 @@
         <v>950</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E167" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F167" s="2"/>
     </row>
-    <row r="168" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>949</v>
       </c>
@@ -17403,46 +17430,46 @@
         <v>938</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>956</v>
+        <v>1037</v>
       </c>
       <c r="E168" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="F168" s="2"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="E169" s="2">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="F169" s="2"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>957</v>
+        <v>949</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>958</v>
+        <v>950</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E170" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F170" s="2"/>
     </row>
@@ -17457,10 +17484,10 @@
         <v>937</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E171" s="2">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="F171" s="2"/>
     </row>
@@ -17475,10 +17502,10 @@
         <v>937</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E172" s="2">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F172" s="2"/>
     </row>
@@ -17493,10 +17520,10 @@
         <v>937</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="E173" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F173" s="2"/>
     </row>
@@ -17511,10 +17538,10 @@
         <v>937</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E174" s="2">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F174" s="2"/>
     </row>
@@ -17526,17 +17553,17 @@
         <v>958</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="E175" s="2">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="F175" s="2"/>
     </row>
-    <row r="176" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>957</v>
       </c>
@@ -17547,52 +17574,48 @@
         <v>937</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="E176" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F176" s="2"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="C177" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E177" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F177" s="2"/>
+    </row>
+    <row r="178" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>937</v>
       </c>
-      <c r="D177" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="E177" s="2">
-        <v>5</v>
-      </c>
-      <c r="F177" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A178" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>968</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>938</v>
-      </c>
       <c r="D178" s="2" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="E178" s="2">
-        <v>2</v>
-      </c>
-      <c r="F178" s="2">
-        <v>10</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="F178" s="2"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
@@ -17602,13 +17625,13 @@
         <v>968</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E179" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F179" s="2">
         <v>10</v>
@@ -17625,10 +17648,10 @@
         <v>938</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E180" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F180" s="2">
         <v>10</v>
@@ -17645,10 +17668,10 @@
         <v>938</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E181" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="F181" s="2">
         <v>10</v>
@@ -17665,10 +17688,10 @@
         <v>938</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E182" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="F182" s="2">
         <v>10</v>
@@ -17685,10 +17708,10 @@
         <v>938</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="E183" s="2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F183" s="2">
         <v>10</v>
@@ -17705,10 +17728,10 @@
         <v>938</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="E184" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F184" s="2">
         <v>10</v>
@@ -17725,7 +17748,7 @@
         <v>938</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="E185" s="2">
         <v>0.5</v>
@@ -17745,7 +17768,7 @@
         <v>938</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="E186" s="2">
         <v>0.5</v>
@@ -17765,10 +17788,10 @@
         <v>938</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E187" s="2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F187" s="2">
         <v>10</v>
@@ -17785,7 +17808,7 @@
         <v>938</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>939</v>
+        <v>978</v>
       </c>
       <c r="E188" s="2">
         <v>0.5</v>
@@ -17794,64 +17817,64 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>980</v>
+        <v>967</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>981</v>
+        <v>968</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="E189" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F189" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>984</v>
+        <v>967</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>985</v>
+        <v>968</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>986</v>
+        <v>938</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>987</v>
+        <v>939</v>
       </c>
       <c r="E190" s="2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F190" s="2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E191" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F191" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -17865,10 +17888,10 @@
         <v>986</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="E192" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F192" s="2">
         <v>12</v>
@@ -17885,10 +17908,10 @@
         <v>986</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="E193" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F193" s="2">
         <v>12</v>
@@ -17899,16 +17922,16 @@
         <v>984</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>986</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="E194" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F194" s="2">
         <v>12</v>
@@ -17919,16 +17942,16 @@
         <v>984</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>986</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E195" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F195" s="2">
         <v>12</v>
@@ -17945,10 +17968,10 @@
         <v>986</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="E196" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F196" s="2">
         <v>12</v>
@@ -17965,10 +17988,10 @@
         <v>986</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E197" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F197" s="2">
         <v>12</v>
@@ -17985,111 +18008,117 @@
         <v>986</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E198" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F198" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>995</v>
+      </c>
+      <c r="E199" s="2">
+        <v>4</v>
+      </c>
+      <c r="F199" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>986</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="E200" s="2">
+        <v>5</v>
+      </c>
+      <c r="F200" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
         <v>997</v>
       </c>
-      <c r="B199" s="2" t="s">
+      <c r="B201" s="2" t="s">
         <v>998</v>
       </c>
-      <c r="C199" s="2" t="s">
+      <c r="C201" s="2" t="s">
         <v>982</v>
       </c>
-      <c r="D199" s="2" t="s">
+      <c r="D201" s="2" t="s">
         <v>999</v>
       </c>
-      <c r="E199" s="2">
+      <c r="E201" s="2">
         <v>20</v>
       </c>
-      <c r="F199" s="2">
+      <c r="F201" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A201" s="3" t="s">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="3" t="s">
         <v>1000</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B203" s="3" t="s">
         <v>1001</v>
       </c>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-      <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A202" s="6" t="s">
+      <c r="C203" s="4"/>
+      <c r="D203" s="4"/>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4"/>
+      <c r="G203" s="4"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="6" t="s">
         <v>1002</v>
       </c>
-      <c r="B202" s="6" t="s">
+      <c r="B204" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="C202" s="6" t="s">
+      <c r="C204" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="D202" s="6" t="s">
+      <c r="D204" s="6" t="s">
         <v>1005</v>
       </c>
-      <c r="E202" s="6" t="s">
+      <c r="E204" s="6" t="s">
         <v>745</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>1011</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>1012</v>
+        <v>287</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>746</v>
@@ -18097,16 +18126,16 @@
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>746</v>
@@ -18114,16 +18143,16 @@
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>746</v>
@@ -18131,16 +18160,16 @@
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>746</v>
@@ -18148,16 +18177,16 @@
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>746</v>
@@ -18165,287 +18194,293 @@
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A212" s="30" t="s">
-        <v>729</v>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>1027</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>728</v>
+        <v>1028</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>1007</v>
       </c>
       <c r="D212" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A214" s="30" t="s">
+        <v>729</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D214" s="2" t="s">
         <v>1618</v>
       </c>
-      <c r="E212" s="30" t="s">
+      <c r="E214" s="30" t="s">
         <v>1617</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A214" s="3" t="s">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="3" t="s">
         <v>1038</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B216" s="3" t="s">
         <v>1039</v>
       </c>
-      <c r="C214" s="4"/>
-      <c r="D214" s="4"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A215" s="6" t="s">
+      <c r="C216" s="4"/>
+      <c r="D216" s="4"/>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4"/>
+      <c r="G216" s="4"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="B215" s="6" t="s">
+      <c r="B217" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="C215" s="6" t="s">
+      <c r="C217" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="D215" s="6" t="s">
+      <c r="D217" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
+    <row r="218" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
         <v>935</v>
       </c>
-      <c r="B216" s="2">
+      <c r="B218" s="2">
         <v>0.9</v>
       </c>
-      <c r="C216" s="2">
+      <c r="C218" s="2">
         <v>1.1499999999999999</v>
       </c>
-      <c r="D216" s="2" t="s">
+      <c r="D218" s="2" t="s">
         <v>1041</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
-        <v>943</v>
-      </c>
-      <c r="B217" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="C217" s="2">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>949</v>
-      </c>
-      <c r="B218" s="2">
-        <v>0.85</v>
-      </c>
-      <c r="C218" s="2">
-        <v>1.25</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="B219" s="2">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="C219" s="2">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B220" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="C220" s="2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B221" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="C221" s="2">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
         <v>1973</v>
       </c>
-      <c r="B220" s="2">
+      <c r="B222" s="2">
         <v>0.89</v>
       </c>
-      <c r="C220" s="2">
+      <c r="C222" s="2">
         <v>1.1100000000000001</v>
       </c>
-      <c r="D220" t="s">
+      <c r="D222" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A222" s="3" t="s">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="3" t="s">
         <v>1811</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B224" s="3" t="s">
         <v>1812</v>
       </c>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A223" s="6" t="s">
+      <c r="C224" s="4"/>
+      <c r="D224" s="4"/>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+      <c r="G224" s="4"/>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="B223" s="6" t="s">
+      <c r="B225" s="6" t="s">
         <v>1813</v>
       </c>
-      <c r="C223" s="6" t="s">
+      <c r="C225" s="6" t="s">
         <v>1814</v>
       </c>
-      <c r="D223" s="6" t="s">
+      <c r="D225" s="6" t="s">
         <v>1815</v>
       </c>
-      <c r="E223" s="6" t="s">
+      <c r="E225" s="6" t="s">
         <v>1816</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
-        <v>1817</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>1818</v>
-      </c>
-      <c r="C224" s="2">
-        <v>1</v>
-      </c>
-      <c r="D224" s="2"/>
-      <c r="E224" s="2"/>
-    </row>
-    <row r="225" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>1819</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="C225" s="2">
-        <v>3</v>
-      </c>
-      <c r="D225" s="2"/>
-      <c r="E225" s="2"/>
     </row>
     <row r="226" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>1821</v>
+        <v>1817</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
       <c r="C226" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>1824</v>
+        <v>1820</v>
       </c>
       <c r="C227" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D227" s="2"/>
-      <c r="E227" s="2" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E227" s="2"/>
+    </row>
+    <row r="228" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>1825</v>
+        <v>1821</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>1826</v>
+        <v>1822</v>
       </c>
       <c r="C228" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
     </row>
-    <row r="229" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>1827</v>
+        <v>1823</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="C229" s="2">
         <v>1</v>
       </c>
       <c r="D229" s="2"/>
-      <c r="E229" s="2"/>
-    </row>
-    <row r="230" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E229" s="2" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
       <c r="C230" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
     </row>
     <row r="231" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>1832</v>
+        <v>1828</v>
       </c>
       <c r="C231" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231" s="2"/>
-      <c r="E231" s="2" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E231" s="2"/>
+    </row>
+    <row r="232" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>1834</v>
+        <v>1830</v>
       </c>
       <c r="C232" s="2">
         <v>1</v>
@@ -18453,25 +18488,27 @@
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>1836</v>
+        <v>1832</v>
       </c>
       <c r="C233" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
+      <c r="E233" s="2" t="s">
+        <v>949</v>
+      </c>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="C234" s="2">
         <v>1</v>
@@ -18481,23 +18518,23 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>1840</v>
+        <v>1836</v>
       </c>
       <c r="C235" s="2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
       <c r="C236" s="2">
         <v>1</v>
@@ -18507,10 +18544,10 @@
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="C237" s="2">
         <v>0.5</v>
@@ -18518,81 +18555,81 @@
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
     </row>
-    <row r="238" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="C238" s="2">
         <v>1</v>
       </c>
-      <c r="D238" s="2">
-        <v>2</v>
-      </c>
+      <c r="D238" s="2"/>
       <c r="E238" s="2"/>
     </row>
-    <row r="239" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="C239" s="2">
         <v>0.5</v>
       </c>
-      <c r="D239" s="2">
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+    </row>
+    <row r="240" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="C240" s="2">
+        <v>1</v>
+      </c>
+      <c r="D240" s="2">
+        <v>2</v>
+      </c>
+      <c r="E240" s="2"/>
+    </row>
+    <row r="241" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C241" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="D241" s="2">
         <v>0.25</v>
       </c>
-      <c r="E239" s="2"/>
-    </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
+      <c r="E241" s="2"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
         <v>1849</v>
       </c>
-      <c r="B240" s="2" t="s">
+      <c r="B242" s="2" t="s">
         <v>1850</v>
       </c>
-      <c r="C240" s="2">
+      <c r="C242" s="2">
         <v>2</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>1852</v>
-      </c>
-      <c r="C241" s="2">
-        <v>1</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="E241" s="2"/>
-    </row>
-    <row r="242" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>1854</v>
-      </c>
-      <c r="C242" s="2">
-        <v>1</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
     </row>
-    <row r="243" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>1855</v>
+        <v>1851</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>1856</v>
+        <v>1852</v>
       </c>
       <c r="C243" s="2">
         <v>1</v>
@@ -18600,12 +18637,12 @@
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>1857</v>
+        <v>1853</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>1858</v>
+        <v>1854</v>
       </c>
       <c r="C244" s="2">
         <v>1</v>
@@ -18615,10 +18652,10 @@
     </row>
     <row r="245" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>1859</v>
+        <v>1855</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>1860</v>
+        <v>1856</v>
       </c>
       <c r="C245" s="2">
         <v>1</v>
@@ -18626,467 +18663,463 @@
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
     </row>
-    <row r="246" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="C246" s="2">
+        <v>1</v>
+      </c>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+    </row>
+    <row r="247" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C247" s="2">
+        <v>1</v>
+      </c>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+    </row>
+    <row r="248" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
         <v>1971</v>
       </c>
-      <c r="B246" s="2" t="s">
+      <c r="B248" s="2" t="s">
         <v>1972</v>
       </c>
-      <c r="C246" s="2">
+      <c r="C248" s="2">
         <v>0</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D248" s="2">
         <v>0.3</v>
       </c>
-      <c r="E246" s="2" t="s">
+      <c r="E248" s="2" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A248" s="3" t="s">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A250" s="3" t="s">
         <v>1861</v>
       </c>
-      <c r="B248" s="3" t="s">
+      <c r="B250" s="3" t="s">
         <v>1862</v>
       </c>
-      <c r="C248" s="4"/>
-      <c r="D248" s="4"/>
-      <c r="E248" s="4"/>
-      <c r="F248" s="4"/>
-      <c r="G248" s="4"/>
-    </row>
-    <row r="249" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A249" s="6" t="s">
+      <c r="C250" s="4"/>
+      <c r="D250" s="4"/>
+      <c r="E250" s="4"/>
+      <c r="F250" s="4"/>
+      <c r="G250" s="4"/>
+    </row>
+    <row r="251" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A251" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="B249" s="6" t="s">
+      <c r="B251" s="6" t="s">
         <v>1863</v>
       </c>
-      <c r="C249" s="6" t="s">
+      <c r="C251" s="6" t="s">
         <v>1864</v>
       </c>
-      <c r="D249" s="6" t="s">
+      <c r="D251" s="6" t="s">
         <v>1865</v>
       </c>
-      <c r="E249" s="6" t="s">
+      <c r="E251" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
+    <row r="252" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
         <v>1866</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="D250" s="2">
-        <v>5</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>1868</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A251" s="2" t="s">
-        <v>1869</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>1867</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>1870</v>
-      </c>
-      <c r="D251" s="2">
-        <v>3</v>
-      </c>
-      <c r="E251" s="2"/>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A252" s="2" t="s">
-        <v>1871</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>1867</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>1872</v>
+        <v>1824</v>
       </c>
       <c r="D252" s="2">
-        <v>2</v>
-      </c>
-      <c r="E252" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>1868</v>
+      </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>1873</v>
+        <v>1869</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>1867</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>1874</v>
+        <v>1870</v>
       </c>
       <c r="D253" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E253" s="2"/>
     </row>
-    <row r="254" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>1875</v>
+        <v>1871</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>1867</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>1828</v>
+        <v>1872</v>
       </c>
       <c r="D254" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E254" s="2"/>
     </row>
-    <row r="255" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>1876</v>
+        <v>1873</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>1867</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1877</v>
+        <v>1874</v>
       </c>
       <c r="D255" s="2">
         <v>1</v>
       </c>
-      <c r="E255" s="2" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="E255" s="2"/>
+    </row>
+    <row r="256" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>1867</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>1880</v>
+        <v>1828</v>
       </c>
       <c r="D256" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E256" s="2"/>
+    </row>
+    <row r="257" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>1882</v>
+        <v>1876</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>1867</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>1883</v>
+        <v>1877</v>
       </c>
       <c r="D257" s="2">
         <v>1</v>
       </c>
-      <c r="E257" s="2"/>
-    </row>
-    <row r="258" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="E257" s="2" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>1885</v>
+        <v>1867</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1886</v>
+        <v>1880</v>
       </c>
       <c r="D258" s="2">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>1887</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>1888</v>
+        <v>1882</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>1885</v>
+        <v>1867</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>1838</v>
+        <v>1883</v>
       </c>
       <c r="D259" s="2">
-        <v>4</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>1889</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E259" s="2"/>
     </row>
     <row r="260" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>1890</v>
+        <v>1884</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
       <c r="D260" s="2">
         <v>2</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>1893</v>
+        <v>1888</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>1894</v>
+        <v>1838</v>
       </c>
       <c r="D261" s="2">
-        <v>1</v>
-      </c>
-      <c r="E261" s="2"/>
-    </row>
-    <row r="262" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>1896</v>
+        <v>1891</v>
       </c>
       <c r="D262" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="263" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="D263" s="2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="E263" s="2"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>1900</v>
+        <v>1895</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
       <c r="D264" s="2">
         <v>1.5</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="265" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="D265" s="2">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E265" s="2"/>
     </row>
-    <row r="266" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="D266" s="2">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="267" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>1908</v>
+        <v>1903</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="D267" s="2">
         <v>0.5</v>
       </c>
-      <c r="E267" s="2" t="s">
-        <v>1910</v>
-      </c>
+      <c r="E267" s="2"/>
     </row>
     <row r="268" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>1911</v>
+        <v>1905</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>1912</v>
+        <v>1906</v>
       </c>
       <c r="D268" s="2">
         <v>0.5</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>1913</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="269" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>1914</v>
+        <v>1908</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>1885</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>1915</v>
+        <v>1909</v>
       </c>
       <c r="D269" s="2">
         <v>0.5</v>
       </c>
       <c r="E269" s="2" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D270" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D271" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E271" s="2" t="s">
         <v>1916</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>1917</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>1824</v>
-      </c>
-      <c r="D270" s="2">
-        <v>3</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>1919</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>1920</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>1918</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>1921</v>
-      </c>
-      <c r="D271" s="2">
-        <v>2</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>1919</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>1924</v>
+        <v>1824</v>
       </c>
       <c r="D272" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>1919</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="D273" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E273" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>1919</v>
+      </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>1923</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="D274" s="2">
-        <v>0.5</v>
-      </c>
-      <c r="E274" s="2"/>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>1923</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>1930</v>
+        <v>1926</v>
       </c>
       <c r="D275" s="2">
         <v>0.5</v>
@@ -19095,167 +19128,197 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="D276" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E276" s="2"/>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D277" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E277" s="2"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
         <v>1931</v>
       </c>
-      <c r="B276" s="2" t="s">
+      <c r="B278" s="2" t="s">
         <v>1932</v>
       </c>
-      <c r="C276" s="2" t="s">
+      <c r="C278" s="2" t="s">
         <v>1933</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D278" s="2">
         <v>25</v>
       </c>
-      <c r="E276" s="2"/>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A278" s="3" t="s">
+      <c r="E278" s="2"/>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A280" s="3" t="s">
         <v>1934</v>
       </c>
-      <c r="B278" s="3" t="s">
+      <c r="B280" s="3" t="s">
         <v>1935</v>
       </c>
-      <c r="C278" s="4"/>
-      <c r="D278" s="4"/>
-      <c r="E278" s="4"/>
-      <c r="F278" s="4"/>
-      <c r="G278" s="4"/>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A279" s="6" t="s">
+      <c r="C280" s="4"/>
+      <c r="D280" s="4"/>
+      <c r="E280" s="4"/>
+      <c r="F280" s="4"/>
+      <c r="G280" s="4"/>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" s="6" t="s">
         <v>874</v>
       </c>
-      <c r="B279" s="6" t="s">
+      <c r="B281" s="6" t="s">
         <v>742</v>
       </c>
-      <c r="C279" s="6" t="s">
+      <c r="C281" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A280" s="2" t="s">
+    <row r="282" spans="1:7" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
         <v>1936</v>
       </c>
-      <c r="B280" s="2" t="s">
+      <c r="B282" s="2" t="s">
         <v>1937</v>
       </c>
-      <c r="C280" s="2" t="s">
+      <c r="C282" s="2" t="s">
         <v>1938</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A281" s="2" t="s">
-        <v>1939</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>1940</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>1941</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="51" x14ac:dyDescent="0.25">
-      <c r="A282" s="2" t="s">
-        <v>1942</v>
-      </c>
-      <c r="B282" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>1943</v>
       </c>
     </row>
     <row r="283" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="51" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B284" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
         <v>1944</v>
       </c>
-      <c r="B283" s="2">
+      <c r="B285" s="2">
         <v>12</v>
       </c>
-      <c r="C283" s="2" t="s">
+      <c r="C285" s="2" t="s">
         <v>1945</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A285" s="3" t="s">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A287" s="3" t="s">
         <v>1946</v>
       </c>
-      <c r="B285" s="3" t="s">
+      <c r="B287" s="3" t="s">
         <v>1947</v>
       </c>
-      <c r="C285" s="4"/>
-      <c r="D285" s="4"/>
-      <c r="E285" s="4"/>
-      <c r="F285" s="4"/>
-      <c r="G285" s="4"/>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A286" s="6" t="s">
+      <c r="C287" s="4"/>
+      <c r="D287" s="4"/>
+      <c r="E287" s="4"/>
+      <c r="F287" s="4"/>
+      <c r="G287" s="4"/>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="6" t="s">
         <v>1948</v>
       </c>
-      <c r="B286" s="6" t="s">
+      <c r="B288" s="6" t="s">
         <v>1949</v>
       </c>
-      <c r="C286" s="6" t="s">
+      <c r="C288" s="6" t="s">
         <v>1950</v>
       </c>
-      <c r="D286" s="6" t="s">
+      <c r="D288" s="6" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A287" s="2" t="s">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
         <v>1951</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B289" s="2">
         <v>0</v>
       </c>
-      <c r="C287" s="2">
+      <c r="C289" s="2">
         <v>0</v>
       </c>
-      <c r="D287" s="2" t="s">
+      <c r="D289" s="2" t="s">
         <v>1952</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A288" s="2" t="s">
-        <v>1953</v>
-      </c>
-      <c r="B288" s="2">
-        <v>-3</v>
-      </c>
-      <c r="C288" s="2">
-        <v>2</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>1954</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A289" s="2" t="s">
-        <v>1955</v>
-      </c>
-      <c r="B289" s="2">
-        <v>-1.5</v>
-      </c>
-      <c r="C289" s="2">
-        <v>1</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>1956</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B290" s="2">
+        <v>-3</v>
+      </c>
+      <c r="C290" s="2">
+        <v>2</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B291" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="C291" s="2">
+        <v>1</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
         <v>1957</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B292" s="2">
         <v>0</v>
       </c>
-      <c r="C290" s="2">
+      <c r="C292" s="2">
         <v>0</v>
       </c>
-      <c r="D290" s="2" t="s">
+      <c r="D292" s="2" t="s">
         <v>1958</v>
       </c>
     </row>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8930164-0AD5-4E3B-93E8-2E6FB0A3A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D240E04B-B3F1-4686-84B7-AEB2FB97E1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Instructions" sheetId="6" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4612" uniqueCount="2020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4614" uniqueCount="2022">
   <si>
     <t>3. Settings</t>
   </si>
@@ -5892,21 +5892,12 @@
     <t>The client's design team does every stage.</t>
   </si>
   <si>
-    <t>Design and build (single stage)</t>
-  </si>
-  <si>
     <t>The contractor's team does Stage 4. Contractor's design 2% (Claycroft, Morgan Sindall D&amp;B: 2.1%).</t>
   </si>
   <si>
-    <t>Two-stage (PCSA)</t>
-  </si>
-  <si>
     <t>Stage 4 is shared with the contractor during the pre-construction stage.</t>
   </si>
   <si>
-    <t>Construction management</t>
-  </si>
-  <si>
     <t>Unchanged: the CM fee replaces part of the contractor's OH&amp;P (not modelled).</t>
   </si>
   <si>
@@ -6091,6 +6082,21 @@
   </si>
   <si>
     <t>No figure the estimate uses changed. The last number the app held in its code now lives here: ▶ factors gains risk_level_low_max (11) and risk_level_medium_max (13) — the risk + contingency % at or below which the report's risk level reads Low or Medium (above: High). The app now also refuses this workbook if a prelims (A) or risk (E) BASE row loses its cap, the OH&amp;P (B) rows leave a works value uncovered, or the fee (C) BASE rows leave a design stage 0–4 uncovered — it no longer has backup percentages to fall back on.</t>
+  </si>
+  <si>
+    <t>Design &amp; Build 1 Stage</t>
+  </si>
+  <si>
+    <t>Design &amp; Build 2 Stage</t>
+  </si>
+  <si>
+    <t>Management Contract / Construction Management</t>
+  </si>
+  <si>
+    <t>v5.24 — 11 Oct 2026</t>
+  </si>
+  <si>
+    <t>No figure changed. The route names in ▶ route_fees follow the RIBA Plan of Work 2020, as the Procurement Reference v2.3 now does: 'Design and build (single stage)' is 'Design &amp; Build 1 Stage', 'Two-stage (PCSA)' is 'Design &amp; Build 2 Stage', 'Construction management' is 'Management Contract / Construction Management'. The fee adjustments are unchanged.</t>
   </si>
 </sst>
 </file>
@@ -6717,7 +6723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C107"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -7412,231 +7418,239 @@
       <c r="B80" s="16"/>
       <c r="C80" s="34"/>
     </row>
-    <row r="81" spans="1:3" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
       <c r="A82" s="17" t="s">
-        <v>2011</v>
+        <v>2015</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>2012</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="83" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A83" s="17" t="s">
-        <v>1998</v>
+        <v>2008</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>1999</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="84" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A84" s="17" t="s">
-        <v>1969</v>
+        <v>1995</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A85" s="17" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="s">
         <v>1731</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>1732</v>
       </c>
     </row>
-    <row r="86" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A86" s="17" t="s">
+    <row r="87" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A87" s="17" t="s">
         <v>1733</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B87" s="17" t="s">
         <v>1734</v>
       </c>
     </row>
-    <row r="87" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A87" s="17" t="s">
+    <row r="88" spans="1:3" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A88" s="17" t="s">
         <v>1735</v>
       </c>
-      <c r="B87" s="17" t="s">
+      <c r="B88" s="17" t="s">
         <v>1736</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A88" s="17" t="s">
-        <v>1737</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="89" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A89" s="17" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="90" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A90" s="17" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="91" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A91" s="17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A92" s="17" t="s">
         <v>1743</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>1744</v>
       </c>
     </row>
-    <row r="92" spans="1:3" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+    <row r="93" spans="1:3" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="17" t="s">
         <v>1745</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B93" s="17" t="s">
         <v>1746</v>
       </c>
     </row>
-    <row r="93" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A93" s="17" t="s">
+    <row r="94" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A94" s="17" t="s">
         <v>1747</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B94" s="17" t="s">
         <v>1748</v>
       </c>
     </row>
-    <row r="94" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="17" t="s">
+    <row r="95" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="17" t="s">
         <v>1715</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B95" s="17" t="s">
         <v>1716</v>
       </c>
-      <c r="C94" s="60"/>
-    </row>
-    <row r="95" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="17" t="s">
+      <c r="C95" s="60"/>
+    </row>
+    <row r="96" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="17" t="s">
         <v>1689</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B96" s="17" t="s">
         <v>1718</v>
       </c>
-      <c r="C95" s="60"/>
-    </row>
-    <row r="96" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A96" s="17" t="s">
+      <c r="C96" s="60"/>
+    </row>
+    <row r="97" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A97" s="17" t="s">
         <v>1680</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>1686</v>
       </c>
-      <c r="C96" s="60"/>
-    </row>
-    <row r="97" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+      <c r="C97" s="60"/>
+    </row>
+    <row r="98" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A98" s="17" t="s">
         <v>1678</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B98" s="17" t="s">
         <v>1679</v>
       </c>
-      <c r="C97" s="60"/>
-    </row>
-    <row r="98" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A98" s="17" t="s">
+      <c r="C98" s="60"/>
+    </row>
+    <row r="99" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A99" s="17" t="s">
         <v>1619</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B99" s="17" t="s">
         <v>1621</v>
       </c>
-      <c r="C98" s="60"/>
-    </row>
-    <row r="99" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A99" s="15" t="s">
+      <c r="C99" s="60"/>
+    </row>
+    <row r="100" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A100" s="15" t="s">
         <v>1608</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B100" s="17" t="s">
         <v>1609</v>
       </c>
-      <c r="C99" s="33"/>
-    </row>
-    <row r="100" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A100" s="15" t="s">
+      <c r="C100" s="33"/>
+    </row>
+    <row r="101" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A101" s="15" t="s">
         <v>1051</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B101" s="17" t="s">
         <v>1052</v>
       </c>
-      <c r="C100" s="33"/>
-    </row>
-    <row r="101" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A101" s="15" t="s">
+      <c r="C101" s="33"/>
+    </row>
+    <row r="102" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A102" s="15" t="s">
         <v>1042</v>
       </c>
-      <c r="B101" s="17" t="s">
+      <c r="B102" s="17" t="s">
         <v>1043</v>
       </c>
-      <c r="C101" s="33"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" s="15" t="s">
+      <c r="C102" s="33"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B103" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C102" s="33"/>
-    </row>
-    <row r="103" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A103" s="15" t="s">
+      <c r="C103" s="33"/>
+    </row>
+    <row r="104" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A104" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B104" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="33"/>
-    </row>
-    <row r="104" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A104" s="15" t="s">
+      <c r="C104" s="33"/>
+    </row>
+    <row r="105" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A105" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B104" s="17" t="s">
+      <c r="B105" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C104" s="33"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A105" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B105" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C105" s="33"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A106" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B106" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="33"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B106" s="17" t="s">
+      <c r="B107" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C106" s="33"/>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A107" s="15"/>
-      <c r="B107" s="17"/>
       <c r="C107" s="33"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="15"/>
+      <c r="B108" s="17"/>
+      <c r="C108" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14974,7 +14988,7 @@
         <v>743</v>
       </c>
       <c r="B6" s="61">
-        <v>5.23</v>
+        <v>5.24</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>744</v>
@@ -16104,7 +16118,7 @@
         <v>858</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>859</v>
@@ -16160,30 +16174,30 @@
     </row>
     <row r="93" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D93" s="2" t="s">
         <v>2004</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>2005</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>2006</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>2007</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="C94" s="2">
         <v>0</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>2010</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -16694,7 +16708,7 @@
     </row>
     <row r="126" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>65</v>
@@ -16703,7 +16717,7 @@
         <v>25</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>10</v>
@@ -16711,7 +16725,7 @@
     </row>
     <row r="127" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>65</v>
@@ -16720,7 +16734,7 @@
         <v>0.1</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>10</v>
@@ -16775,189 +16789,189 @@
     </row>
     <row r="132" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="B132" s="2">
         <v>0.5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>1978</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="133" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="B133" s="2">
         <v>20</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="B134" s="2">
         <v>10</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="B135" s="2">
         <v>3</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="B136" s="2">
         <v>1</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="B137" s="2">
         <v>2</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="B138" s="2">
         <v>2</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="B139" s="2">
         <v>2</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="B140" s="2">
         <v>2</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="B141" s="2">
         <v>11</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="B142" s="2">
         <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>1982</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -17084,7 +17098,7 @@
         <v>938</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>1959</v>
+        <v>1956</v>
       </c>
       <c r="E150" s="2">
         <v>0.5</v>
@@ -17104,7 +17118,7 @@
         <v>938</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>1960</v>
+        <v>1957</v>
       </c>
       <c r="E151" s="2">
         <v>0.5</v>
@@ -17124,7 +17138,7 @@
         <v>938</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>1961</v>
+        <v>1958</v>
       </c>
       <c r="E152" s="2">
         <v>0.5</v>
@@ -17144,7 +17158,7 @@
         <v>938</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>1962</v>
+        <v>1959</v>
       </c>
       <c r="E153" s="2">
         <v>0.5</v>
@@ -18353,7 +18367,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="B222" s="2">
         <v>0.89</v>
@@ -18362,7 +18376,7 @@
         <v>1.1100000000000001</v>
       </c>
       <c r="D222" t="s">
-        <v>1974</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.25">
@@ -18691,10 +18705,10 @@
     </row>
     <row r="248" spans="1:7" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="C248" s="2">
         <v>0</v>
@@ -19282,7 +19296,7 @@
     </row>
     <row r="290" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>1953</v>
+        <v>2017</v>
       </c>
       <c r="B290" s="2">
         <v>-3</v>
@@ -19291,12 +19305,12 @@
         <v>2</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>1955</v>
+        <v>2018</v>
       </c>
       <c r="B291" s="2">
         <v>-1.5</v>
@@ -19305,12 +19319,12 @@
         <v>1</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>1957</v>
+        <v>2019</v>
       </c>
       <c r="B292" s="2">
         <v>0</v>
@@ -19319,7 +19333,7 @@
         <v>0</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>1958</v>
+        <v>1955</v>
       </c>
     </row>
   </sheetData>
@@ -19432,7 +19446,7 @@
         <v>63</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>69</v>
@@ -20186,7 +20200,7 @@
         <v>63</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>177</v>
@@ -20230,7 +20244,7 @@
         <v>63</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H24" s="15" t="s">
         <v>177</v>
@@ -20318,7 +20332,7 @@
         <v>63</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H26" s="15" t="s">
         <v>177</v>
@@ -20362,7 +20376,7 @@
         <v>63</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>177</v>
@@ -20406,7 +20420,7 @@
         <v>63</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>177</v>
@@ -20674,7 +20688,7 @@
         <v>63</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H34" s="15" t="s">
         <v>177</v>
@@ -21114,7 +21128,7 @@
         <v>63</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H44" s="15" t="s">
         <v>177</v>
@@ -21162,7 +21176,7 @@
         <v>63</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H45" s="15" t="s">
         <v>177</v>
@@ -21210,7 +21224,7 @@
         <v>63</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H46" s="15" t="s">
         <v>177</v>
@@ -21386,7 +21400,7 @@
         <v>63</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H50" s="15" t="s">
         <v>177</v>
@@ -21700,7 +21714,7 @@
         <v>63</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H57" s="15" t="s">
         <v>177</v>
@@ -22230,7 +22244,7 @@
         <v>63</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H69" s="15" t="s">
         <v>61</v>
@@ -22672,7 +22686,7 @@
         <v>63</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="H79" s="15" t="s">
         <v>649</v>
@@ -25038,7 +25052,7 @@
         <v>373</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="F143" s="15" t="s">
         <v>67</v>
@@ -25286,7 +25300,7 @@
         <v>396</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="F150" s="15" t="s">
         <v>67</v>

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4737" uniqueCount="2067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="2092">
   <si>
     <t>3. Settings</t>
   </si>
@@ -4896,7 +4896,7 @@
     <t>As 5.26a for flats and student rooms being rewired: chasing walls for new containment, holes through ceilings, infilling and making good. Added automatically</t>
   </si>
   <si>
-    <t>Tender – Lakeside S&amp;F (Sep 2026)</t>
+    <t xml:space="preserve">Tender – Project A (Sep 2026)</t>
   </si>
   <si>
     <t>S-0083-02</t>
@@ -4962,10 +4962,10 @@
     <t>S-0015-02</t>
   </si>
   <si>
-    <t>£32 (bids £29–£39) on 1,099 m², incl. removing the old insulation</t>
-  </si>
-  <si>
-    <t>£5,296 per kitchen (bids £4,538–£5,890): units supplied and fitted, sink and taps connected. New build columns not changed</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2.5a</t>
@@ -4989,46 +4989,46 @@
     <t>5.26a</t>
   </si>
   <si>
-    <t>Residential: £51 — see 3.2c</t>
-  </si>
-  <si>
-    <t>Residential: £30 — see 3.3b</t>
-  </si>
-  <si>
-    <t>£20 (bids £15–£26) for local pipework changes to new kitchens and bathrooms — confirms £19.5</t>
-  </si>
-  <si>
-    <t>Not comparable: the tender only covered works to the existing central battery system</t>
-  </si>
-  <si>
-    <t>Data alone £19.4 (bids £17–£29), residential — confirms £18. With TV aerial see 5.14b</t>
-  </si>
-  <si>
-    <t>Lump sum £76k (bids £61k–£84k) for estate amenity lighting incl. trenching; no external area to convert</t>
-  </si>
-  <si>
-    <t>Lakeside S&amp;F tender (29 Sep 2026): builder's work for the rewire of 49 flats and a house, median of 4 bids ÷ 0.94 = £27/m²; Basic and High scaled from 5.26a; New build columns = 5.26a</t>
-  </si>
-  <si>
-    <t>Lakeside S&amp;F tender (29 Sep 2026): data, telephone and TV aerial per flat plus communal cabling, median of 4 bids ÷ 0.94 = £24.5/m²; Basic and High scaled from 5.14a; New build columns = 5.14a</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A tender (29 Sep 2026): builder's work for the rewire of 49 flats and a house, median of 4 bids ÷ 0.94 = £27/m²; Basic and High scaled from 5.26a; New build columns = 5.26a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A tender (29 Sep 2026): data, telephone and TV aerial per flat plus communal cabling, median of 4 bids ÷ 0.94 = £24.5/m²; Basic and High scaled from 5.14a; New build columns = 5.14a</t>
   </si>
   <si>
     <t>Scope: Extract fans only</t>
   </si>
   <si>
-    <t>Lakeside S&amp;F tender (29 Sep 2026): bathroom and kitchen extract fans, ducting and electrical connections, median of 4 bids ÷ 0.94 = £18.5/m²; Basic and High scaled from 5.3a</t>
-  </si>
-  <si>
-    <t>Lakeside S&amp;F tender (29 Sep 2026): overboard and redecorate ceilings in flats and stair cores, median of 4 bids ÷ 0.94 = £30/m²; Basic and High scaled from 3.3a; New build columns = 3.3a</t>
-  </si>
-  <si>
-    <t>Lakeside S&amp;F tender (29 Sep 2026): latex screed, sheet vinyl and skirtings in flats and stair cores, median of 4 bids ÷ 0.94 = £51/m²; Std £50, Basic and High scaled from 3.2a; New build columns = 3.2a</t>
+    <t xml:space="preserve">Project A tender (29 Sep 2026): bathroom and kitchen extract fans, ducting and electrical connections, median of 4 bids ÷ 0.94 = £18.5/m²; Basic and High scaled from 5.3a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A tender (29 Sep 2026): overboard and redecorate ceilings in flats and stair cores, median of 4 bids ÷ 0.94 = £30/m²; Basic and High scaled from 3.3a; New build columns = 3.3a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A tender (29 Sep 2026): latex screed, sheet vinyl and skirtings in flats and stair cores, median of 4 bids ÷ 0.94 = £51/m²; Std £50, Basic and High scaled from 3.2a; New build columns = 3.2a</t>
   </si>
   <si>
     <t>Scope: Loft insulation only</t>
   </si>
   <si>
-    <t>Lakeside S&amp;F tender (29 Sep 2026): 1,099 m² of 300 mm quilt incl. removing old insulation, median of 4 bids ÷ 0.94 = £32/m²</t>
+    <t xml:space="preserve">Project A tender (29 Sep 2026): 1,099 m² of 300 mm quilt incl. removing old insulation, median of 4 bids ÷ 0.94 = £32/m²</t>
   </si>
   <si>
     <t>Scope: Full roof</t>
@@ -5037,160 +5037,160 @@
     <t>Scope: Full system</t>
   </si>
   <si>
-    <t>v4.5 0.5. No source recorded in v4.5 · Sep 2026: rates from the Lakeside S&amp;F tender returns (see 'Tender check' on '2. Rates')</t>
-  </si>
-  <si>
-    <t>v4.5 4.2-RES. No source recorded in v4.5 · Sep 2026: rates from the Lakeside S&amp;F tender returns (see 'Tender check' on '2. Rates')</t>
-  </si>
-  <si>
-    <t>v4.5 4.3. No source recorded in v4.5 · Sep 2026: rates from the Lakeside S&amp;F tender returns (see 'Tender check' on '2. Rates')</t>
-  </si>
-  <si>
-    <t>v4.5 5.7 switchgear + 5.8 wiring (no sub-distribution row for residential in v4.5) · Sep 2026: rates from the Lakeside S&amp;F tender returns (see 'Tender check' on '2. Rates')</t>
-  </si>
-  <si>
-    <t>Lakeside S&amp;F tender, Sep 2026: 50 dwellings on 3,306 m², one bathroom each</t>
+    <t xml:space="preserve">v4.5 0.5. No source recorded in v4.5 · Sep 2026: rates from the Project A tender returns (see 'Tender check' on '2. Rates')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.5 4.2-RES. No source recorded in v4.5 · Sep 2026: rates from the Project A tender returns (see 'Tender check' on '2. Rates')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.5 4.3. No source recorded in v4.5 · Sep 2026: rates from the Project A tender returns (see 'Tender check' on '2. Rates')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v4.5 5.7 switchgear + 5.8 wiring (no sub-distribution row for residential in v4.5) · Sep 2026: rates from the Project A tender returns (see 'Tender check' on '2. Rates')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A tender, Sep 2026: 50 dwellings on 3,306 m², one bathroom each</t>
   </si>
   <si>
     <t>Tender check</t>
   </si>
   <si>
-    <t>From the Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026); the figure and bid range are in the 'Tender check' column.</t>
+    <t/>
   </si>
   <si>
     <t>v5.7 — 30 Sept 2026</t>
   </si>
   <si>
-    <t>Lakeside S&amp;F tender returns (29 Sept 2026): five bids, four used (median ÷ 0.94 West Midlands factor, on 3,306 m² measured floor area). Changed, Refurb &amp; Fit-out columns only: strip-out £45 → £55; bathrooms £900 / £2,000 / £3,500 → £1,150 / £2,500 / £4,400; domestic kitchens £3,500 / £6,000 / £10,000 → £3,100 / £5,300 / £8,850; residential power (5.7b) £70 / £108 / £185 → £95 / £150 / £255. Added: residential rows (RES STU) for floor finishes (3.2c £50), ceilings (3.3b £30), data incl. TV aerial (5.14b £25) and builder's work (5.26b £27); options Roof — Loft insulation only (2.5b, £32/m² roof) and Ventilation — Extract fans only (5.3b, £19). Ratios: m2_per_dwelling 80 → 66, bathrooms_per_dwelling 1.2 → 1.0. New 'Tender check' column on '2. Rates' and price source 'Tender – Lakeside S&amp;F (Sep 2026)'. Confirmed and kept: wall finishes, water (visible fittings), fire alarm, data, fire stopping (Basic).</t>
+    <t/>
   </si>
   <si>
     <t>v5.8 — 1 Oct 2026</t>
   </si>
   <si>
-    <t>CS: £48 (bids £45–£51) for insulated render to part of the façade of an occupied 4-storey building. With the brick remedials under it (see 7.1a): £97 (bids £70–£122). Scaffold extra (see 2.7).</t>
-  </si>
-  <si>
-    <t>CS: £210 (bids £192–£228) for triple-glazed windows, curtain walling and doors on a whole 4-storey building (openings ≈ 16% of GIFA, ≈ £1,330/m² of opening), incl. take-out, closers, fire barriers, reveals, boards and decs (≈ 30% on top of supply and fit). 17% above High. The low bid left out the curtain walling. Scaffold for envelope works (in the bids' prelims): £42 (bids £35–£49) per m² GIFA, extra to 2.5a, 2.6 and 2.7. Out-turn: window design development added £86k (3.3% of the contract sum) after award.</t>
-  </si>
-  <si>
-    <t>CS: £224 (bids £210–£238) for the whole M&amp;E package of an air source heat pump conversion of an occupied academic building: heat pumps replacing gas boilers, LTHW alterations, coils to 6 AHUs, about 160 radiators, BMS and ventilation (no breakdown). Std 5.1b + 5.5 = £93. Heat pumps: 3 × 118 kW (N+1, about 240 kW duty, about 69 W/m² after the fabric works), so about £1,800–2,100 per kW installed for the whole M&amp;E package.</t>
-  </si>
-  <si>
-    <t>Residential rewire: £27 — see 5.26b. CS: £8 (bids £6–£10), 2.5–4.6% of M&amp;E, for a heat pump conversion (plant room, pipework and radiators).</t>
-  </si>
-  <si>
-    <t>CS: £48 (bids £25–£71) for brick remedials before rendering: slab edges exposed, new stainless steel angles and cavity trays, remedial ties, movement joints, repointing.</t>
-  </si>
-  <si>
-    <t>Evidence only, no rates changed. Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; mean of two bids × 1.07 ÷ 0.94, on 3,495 m² GIA and 699 m² of roof) added to the Tender check column for 2.5a roof, 2.6 external walls, 2.7 windows (with the scaffold figure), 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs, with the final out-turn (July 2026) and CPW's heat pump sizes. The Tender check header and its note above now cover more than one project. Suggested for the owner to decide: roof Std about £300 (Computer Science £313, Claycroft £627–£704); air source heat pump full system Std about £190; a scaffold item of about £40/m² GIFA for envelope works; triple glazing about £210/m² GIFA (an option, or High).</t>
-  </si>
-  <si>
-    <t>Whitefields rate (£ per this row's unit, this workbook's basis: Total Reclaims contract 2026, excl. the contractor's prelims and OH&amp;P, ÷ 0.94 × 1.014. Evidence only — the app does not read it)</t>
-  </si>
-  <si>
-    <t>Whitefields rate</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>v5.9 — 2 Oct 2026</t>
   </si>
   <si>
-    <t>Tender check (this row's unit, on this workbook's basis. Unlabelled = Lakeside S&amp;F, Sep 2026: median of 4 bids ÷ 0.94. CS = Computer Science decarbonisation, Mar 2024: 2 bids × 1.07 ÷ 0.94. WF = Whitefields demolition, Total Reclaims contract 2026: line items × 1.014 ÷ 0.94 — the figure is also in column R. CC = Claycroft refurbishment, Morgan Sindall G4 contract May 2025: packages × 1.034 ÷ 0.94 — the figure is also in column S)</t>
-  </si>
-  <si>
-    <t>Claycroft rate (£ per this row's unit, this workbook's basis: Morgan Sindall G4 contract, May 2025 — sub-contract packages excl. Morgan Sindall's prelims, risk, fee and design, × 1.034 ÷ 0.94, on 17,172 m² GIA measured. 2.10 fire stopping is the forecast out-turn (Mace Val 16, Sep 2026). Evidence only — the app does not read it)</t>
-  </si>
-  <si>
-    <t>£54 (bids £36–£56) for a partial strip-out: finishes, fittings, redundant electrics and protection CC: £51.4 on the Claycroft G4 contract (Cawarden, £801,990): full strip-out of three occupied student blocks, 17,172 m² GIA. Three bids £802k–£928k.</t>
-  </si>
-  <si>
-    <t>Loft insulation only: £32 — see 2.5b. CS: £313 (bids £288–£338) per m² of roof re-covered (699 m², less than the footprint) for a flat warm-roof overlay on the kept asphalt: AVCL, 120 mm PIR, two-layer felt, insulated upstands, new copings, ballast relaid. Scaffold extra (see 2.7). Claycroft pitched re-roof £627–£704. CC: £517 per m² of roof plan (5,747 m² footprint) on the G4 contract: strip concrete tiles, top-hat spacers, Euroclad secret-fix metal over-roof, hips and verges, new eaves, gutters and soffits (£596 per m of eaves), incl. Metclad's design and prelims; excl. the bay-window cladding and scaffold (scaffold £99 per m² of plan). Forecast out-turn with roof timber remedials £601. Tiled like-for-like alternative about £460 (Stage 3).</t>
-  </si>
-  <si>
-    <t>£13.5 (bids £7–£32) for local fire stopping only — in line with Basic £15 CC: £96 forecast out-turn (Mace Val 16, Sep 2026; £88 if the Claycroft 2 CE replaces its provisional sum), against £22 for the £350k provisional sum in the G4 contract. By block: Claycroft 1 £53 (final); Claycroft 3 £76 (measured: about 18 seals per bed at about £42 each; access 22% of the cost); Claycroft 2 £135–£155 (under review). Excludes £1.30m of compartment-wall head remediation on Claycroft 3, which included a 16-week delay.</t>
-  </si>
-  <si>
-    <t>£72 (bids £60–£84) incl. bathroom wall cladding, kitchen tiling and full redecoration — confirms £75 CC: £99 on the G4 contract: decoration (RE Martin, £1.02m; three bids £1.02m–£1.16m), making good (£274k) and PVC hygienic wall cladding (£251k). Includes painting ceilings and doors.</t>
-  </si>
-  <si>
-    <t>£51 (bids £48–£59). New build columns copied from 3.2a CC: £38 on the G4 contract: carpet and vinyl (Active, £506k; three bids £506k–£660k), Claycroft 2 corridor and lobby floors (£88k) and screed (£4.5k).</t>
-  </si>
-  <si>
-    <t>£30 (bids £21–£36). New build columns copied from 3.3a CC: £70 on the G4 contract: ceilings and partitions package (Ace, £1.10m; three bids £1.10m–£1.23m) — replacement plasterboard ceilings (two layers of fire-line board on top floors), stair soffits and some partitions, not split. Claycroft replaced its ceilings, so compare with 3.3a.</t>
-  </si>
-  <si>
-    <t>£2,563 per bathroom (bids £2,322–£4,440); standard suite alone £2,460. New build columns not changed CC: £3,869 per bathroom on the G4 contract, Claycroft 1 (135 bathroom units): IPS and vanity (Inscape) plus WC, basin and bath with taps, incl. assisted-bathroom changes. Water and drainage connections are in 5.2a; PVC wall cladding is in 3.1.</t>
-  </si>
-  <si>
-    <t>CC: £64 on the G4 contract: joinery package (Mansard, £994k; two bids £994k–£1.04m) — bathroom joinery (boxings, bath panels, shelves) 67%, bedroom joinery (wardrobe alterations, shelving) 21%, other incl. signage 12%.</t>
-  </si>
-  <si>
-    <t>CC: £39 on the G4 contract: domestic hot and cold water (riser pipework and valves, bathroom connections, DHW plate heat exchangers and pumps) and drainage (bathroom connections to stacks, SVP terminations). A partial replacement, not a full installation. Sanitaryware is in 4.2a.</t>
-  </si>
-  <si>
-    <t>Residential extract-only scope: £18.5 — see 5.3b CC: forecast out-turn £92 (Mace Val 16) for bathroom extract incl. new ductwork and roof-mounted fans added by CE in Claycroft 1 (£182k) and Claycroft 2 (£865k). The contract figure is on 5.3b.</t>
-  </si>
-  <si>
-    <t>£18.5 (bids £13–£23), incl. the electrical connection to each fan CC: £28 on the G4 contract: new branch connections, dampers and grilles to the existing bathroom extract, duct cleaning and flow checks, plus fire dampers (£124k). Forecast out-turn £92 once new ductwork and roof fans were added — see 5.3a.</t>
-  </si>
-  <si>
-    <t>CC: £4.3 on the G4 contract: interfaces from the existing BEMS to the new fire alarm and DHW controls only.</t>
-  </si>
-  <si>
-    <t>Power + lighting £186 (bids £157–£253) less lighting 5.8a £33 = £153; incl. landlord panels and sub-mains per block. New build columns not changed CC: £158 on the G4 contract: full rewire — LV switch panels and distribution boards (£1.10m), containment (£366k), small power (£669k), isolation and strip-out of the old installation (£158k) and earthing. Electrical total with lighting, fire alarm and data: £355.</t>
-  </si>
-  <si>
-    <t>Not separable in the tender — checked together with 5.7b CC: £113 on the G4 contract for general, emergency and external lighting together (£1.66m, not split) — compare with 5.8a + 5.9 (£33 + £10).</t>
-  </si>
-  <si>
-    <t>£18.6 (bids £18–£21), residential — confirms £18 CC: £65 on the G4 contract: new fire alarm throughout three blocks of student flats (£949k). Disabled refuge and assisted-WC alarms add £8.5 (not in this figure).</t>
-  </si>
-  <si>
-    <t>£24.5 incl. TV aerial system (bids £22–£39). New build columns copied from 5.14a CC: £19 on the G4 contract: voice and data (£284k); no TV aerial system.</t>
-  </si>
-  <si>
-    <t>Not comparable: the tender only had doorbells and door-entry infrastructure CC: £4.5 on the G4 contract: access control (£52k) and CCTV (£14k) only.</t>
-  </si>
-  <si>
-    <t>CC: £112,850 per lift on the G4 contract: one passenger lift removed and replaced in Claycroft 3 (Morris Vermaport, £102,588 incl. design).</t>
-  </si>
-  <si>
-    <t>£27 (bids £18–£55): chasing and making good for a full rewire of occupied flats. New build columns copied from 5.26a CC: £11 on the G4 contract: builder's work assessed by Morgan Sindall at 2.2% of M&amp;E (£172k); more builder's work is priced inside the M&amp;E lines.</t>
-  </si>
-  <si>
-    <t>CC: no contract figure. The forecast out-turn (Mace Val 16) adds £2.65m of structural and fabric defect remediation, £164 on this basis — mostly a £2.14m budget for Claycroft 2, found only as each block was opened up.</t>
-  </si>
-  <si>
-    <t>Lakeside Staff &amp; Family Flats tender returns (29 Sept 2026) converted to this workbook's basis: the median of the four credible bids (BSN, Chiel, Harrabin, William Gough with its kitchen error corrected; Watkin Jones excluded at twice the field) ÷ 0.94 West Midlands factor, per this row's unit, on 3,306 m² measured floor area (49 flats, the Warden's house and nine stair cores). Excludes the contractors' preliminaries and OH&amp;P. Lines starting 'CS:' are the Computer Science Building decarbonisation tender returns (Harrabin and Chiel, March 2024; two bids, so the mean): tender × 1.07 (to Q3 2026) ÷ 0.94, on 3,495 m² GIA (UoW Estates CAD outlines) and 699 m² of roof. Evidence only: no rate was changed for them in v5.8. Final out-turn (financial statement, July 2026): construction £2.73m, +3.4% on a £2.64m contract; total project £3.13m excl. VAT. WF lines: Whitefields demolition (17 blocks, UoW main campus), the Total Reclaims contract (tendered Feb 2026, Option 2) — the figure is also in column R, Whitefields rate. CC lines: the Claycroft student residences refurbishment (679 beds, three occupied blocks, UoW main campus), Morgan Sindall G4 contract (May 2025, SCAPE) — the figure is also in column S, Claycroft rate.</t>
-  </si>
-  <si>
-    <t>Claycroft rate</t>
-  </si>
-  <si>
-    <t>Column S on '2. Rates': the Claycroft student residences refurbishment figure for that row (Morgan Sindall, Tier 1, SCAPE Lot 4, NEC ECC; G4 contract £20,955,523, May 2025), in the row's unit and on this workbook's basis — sub-contract package values without Morgan Sindall's prelims, risk, fee and design, × 1.034 to Q3 2026, ÷ 0.94 West Midlands factor. m² GIFA uses 17,172 m² GIA and m² roof the 5,747 m² footprint, both measured from the UoW Estates fire plans; bathrooms use Claycroft 1 (135 bathroom units). M&amp;E rows include their share (6.5%) of the M&amp;E design, prelims and testing. 2.10 fire stopping is the forecast out-turn (Mace Val 16, Sep 2026; ÷ 0.94, not rebased), because the contract held only a £350k provisional sum. Evidence only: the app does not read this column and no rate changed.</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>v5.10 — 3 Oct 2026</t>
   </si>
   <si>
-    <t>Evidence only, no rates changed. New column S 'Claycroft rate' on '2. Rates' and CC lines in Tender check, from the Claycroft refurbishment (Morgan Sindall G4 contract £20.96m, May 2025; Mace Val 16 forecast final account £27.96m, +33%; 17,172 m² GIA measured, 679 beds): strip-out £51; metal over-roof £517/m² roof; fire stopping £96 (out-turn); wall finishes £99; floor finishes £38; ceilings £70; bathrooms £3,869 each; fixed joinery £64; water and drainage £39; extract £28; power £158; lighting incl. emergency £113; fire alarm £65; data £19; passenger lift £112,850; BWIC £11. Not on '2. Rates': scaffold £33/m² GIA; Morgan Sindall prelims 11.3% of works, fee 2.2%, risk 2.8%, design 2.1%; client risk and contingency 21.5% of contract, exceeded by the forecast growth (structural and fabric defects £2.65m, fire stopping incl. compartment-wall heads £2.63m, M&amp;E £1.40m, roof £0.55m).</t>
-  </si>
-  <si>
-    <t>Column R on '2. Rates': the Whitefields demolition contract figure for that row (Total Reclaims, £525,676; AFC £532,445 at FS 16, Jul 2026), in the row's unit and on this workbook's basis — line items without the contractor's prelims and OH&amp;P, ÷ 0.94 West Midlands factor, × 1.014 to Q3 2026. Quantities from the owner: 17 blocks, 3,740 m² GIA (about 220 m² each over ground and first floors), 2,210 m² footprint (about 130 m² each), 8,000 m² site. Evidence only: the app does not read this column and no rate changed.</t>
-  </si>
-  <si>
-    <t>Evidence only, no rates changed. New column R 'Whitefields rate' on '2. Rates' and WF lines in Tender check, from the Whitefields demolition contract (Total Reclaims £525,676; AFC £532,445 at FS 16, Jul 2026; 3,740 m² GIA, 2,210 m² footprint, 8,000 m² site): 0.1 asbestos £8.1/m² GIFA; 0.2 demolition incl. disconnections £73/m² demolished; 0.7 service diversions £36/m² footprint (254 m water-main replacement); 8.10 topsoil and seed £2.1/m². Not on '2. Rates': the contractor's prelims incl. hoarding were 16.8% of works and OH&amp;P 15%; professional fees 28% of construction (asbestos surveys £43k, ecology £33k), UoW Estates fees 4%, contingency 7%; construction 15–16 weeks on site.</t>
-  </si>
-  <si>
-    <t>WF: £8.1 on the contract (Total Reclaims, £28,050 to the asbestos BoQ) over 3,740 m² GIA (17 blocks × about 220 m², owner's figures). Five bids on the same BoQ: £8.1–£42.5, median £12.7. Mace's pre-tender allowance was £85,000 (£24.5). The R&amp;D survey (£9,400) was a fee.</t>
-  </si>
-  <si>
-    <t>WF: £73 per m² demolished on the contract, 3,740 m² GIA (17 blocks × about 220 m², owner's figures): soft strip, demolish, slabs and foundations £34; disconnecting and cutting back drainage, water, gas, electrical and telecoms, plus Trinity / Honeywell fire alarm, security and metering removal, £39. Core demolition across five bids £34–£70 (median £46). About £15k per block. Excludes the water-main replacement (0.7) and the contractor's own £15k provisional sums for the Trinity / Honeywell work, which those quotes replace.</t>
-  </si>
-  <si>
-    <t>WF: £36 per m² footprint on the contract (17 × about 130 m² = 2,210 m² footprint): replacing 254 m of ductile iron water main across the site in MDPE, with temporary water, trenching, stone surround and tarmac reinstatement (£74k; about £315/m of main). £44 with the changes pending at FS 16, Jul 2026 (trial pits on the district heating and water mains, out-of-hours water works: £16.7k).</t>
-  </si>
-  <si>
-    <t>WF: £2.1 per m² over the 8,000 m² site (contract £15.4k): topsoil and grass seed to the UoW Grounds specification only — no planting or maintenance. Five bids £2.1–£11.2, median £3.2.</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>SUGGEST: S-0020 Fire stopping · SUGGEST: S-0047 Emergency lighting · SUGGEST: S-0001 Asbestos removal</t>
@@ -5214,7 +5214,7 @@
     <t>Project rate columns (T–Z)</t>
   </si>
   <si>
-    <t>Columns T–Y on '2. Rates' hold the other real projects' figures in the row's unit and on this workbook's basis, beside Whitefields (R) and Claycroft (S): T Lakeside S&amp;F (tender Sep 2026, median of 4 bids); U Computer Science decarbonisation (tender Mar 2024, mean of 2 bids); V Scarman Public Toilets Phase 2 (HIGH spec, tender Apr 2026, median of 6 bids; per m² over the 71 m² toilet area); W Co-op grocery store fit-out (Kingfisher contract Aug 2025, 885 m²); X IBRB café servery (Senevo winning bid 2025, 72 m² café, 28 m² servery); Y Riley Court Psychology full refurbishment (Maris signed contract £9.15m, GMP Nov 2024, GIFA 3,850 m²). Each excludes the contractor's prelims, OH&amp;P and design, rebased to Q3 2026 and ÷ 0.94 West Midlands. Column Z is the average of R–Y for the row. Projects differ in scope and specification, so expect spread. Not on '2. Rates': scaffold for envelope works £42 (CS) and £33 (Claycroft) per m² GIFA; retail refrigeration £379 and retailer equipment £373 per m² (Co-op); preliminaries Lakeside ~9%, Whitefields 16.8%, Claycroft 11.3%, Scarman 14%, Co-op 7.2%, IBRB 17.7%, Riley Court 5.5% (+4% contractor PM and design). Evidence only: the app does not read these columns and no rate changed. Column AA is Claude's suggested Refurb &amp; Fit-out Standard rate for each row with evidence, and AB the reason (Raise / Lower / Keep). They are suggestions for the owner only: the app does not read them, and a rate changes only when the owner edits the rate columns.</t>
+    <t/>
   </si>
   <si>
     <t>v5.19 — 9 Oct 2026</t>
@@ -5226,7 +5226,7 @@
     <t>v5.18 — 8 Oct 2026</t>
   </si>
   <si>
-    <t>Professional fees by procurement route: new ▶ route_fees on '3. Settings'. Design and build: client fees −3 points and contractor's design 2% of construction (Claycroft D&amp;B 2.1%); two-stage (PCSA): −1.5 and 1%; traditional and construction management unchanged. Only while Stage 4 is still to do. The preferred route comes from the Procurement Reference.</t>
+    <t xml:space="preserve">Professional fees by procurement route: new ▶ route_fees on '3. Settings'. Design and build: client fees −3 points and contractor's design 2% of construction (Project D D&amp;B 2.1%); two-stage (PCSA): −1.5 and 1%; traditional and construction management unchanged. Only while Stage 4 is still to do. The preferred route comes from the Procurement Reference.</t>
   </si>
   <si>
     <t>v5.17 — 8 Oct 2026</t>
@@ -5262,31 +5262,31 @@
     <t>v5.12 — 4 Oct 2026</t>
   </si>
   <si>
-    <t>Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Lakeside tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
+    <t xml:space="preserve">Rates updated from the owner's review of the v5.11 suggestions (column AA marked green = accept, amber = owner's figure, red = no change). 25 rows changed; each row's Basic, Standard, High and New build Std / High move by the same ratio as Standard (new Std ÷ old Std), rounded. Std (Refurb &amp; Fit-out): demolition 130→100; roof 110→190; external walls 60→100; windows 120→140; internal walls 110→150; internal doors 60→100; floor finishes 75→85; ceilings 50→80; staff kitchenette 4,000→6,000; signage 10→12; catering kitchen 690→1,000; ASHP full system 78→190 and district heating full system 54→120 (now figures, not = 5.1a × factor; their plant-only / radiators-only rows still follow by formula); water and drainage 65→80; ventilation 45→75 (owner); extract fans 19→22; BMS 15→25; lighting 33→80 (5.8b follows at 75%); fire alarm 18→35; data 18→20; security 15→20; passenger lift 40,000→60,000 (owner); builder's work 18→12; foul drainage 6→10 (owner); external utilities 10→25. Kept: toilets and accessible WCs (owner: no change) and the 20 'keep' rows; 5.2b visible-fittings water fixed at its figures (19.5 Std, Project A tender) so it does not follow 5.2a. Changed rows' Source = 'Your figure'.</t>
   </si>
   <si>
     <t>v5.11 — 4 Oct 2026</t>
   </si>
   <si>
-    <t>Evidence only, no rates changed. Six more project columns on '2. Rates' beside Whitefields (R) and Claycroft (S), each a plain figure in the row's unit on this workbook's basis: T Lakeside S&amp;F (15 rows), U Computer Science (6), V Scarman Public Toilets Phase 2, high spec (12), W Co-op store fit-out (19), X IBRB café (7), Y Riley Court Psychology refurbishment (27, from the signed contract CSA). Column Z averages R–Y on 47 rows. Row 24 explains the columns and lists the evidence that has no row (scaffold, retail refrigeration and equipment, preliminaries %). Columns AA–AB: Claude's suggested Refurb &amp; Fit-out Std rate and the reason, on all 47 rows (25 raise, 2 lower, 20 keep).</t>
-  </si>
-  <si>
-    <t>Lakeside rate (£ per this row's unit, this workbook's basis: Lakeside Staff &amp; Family Flats refurbishment, tender Sep 2026, median of 4 bids ÷ 0.94. Evidence only — the app does not read it)</t>
-  </si>
-  <si>
-    <t>Computer Science rate (£ per this row's unit, this workbook's basis: CS Building decarbonisation, tender Mar 2024, mean of 2 bids × 1.07 ÷ 0.94; roof per m² footprint; 5.1b is the whole M&amp;E package. Evidence only)</t>
-  </si>
-  <si>
-    <t>Scarman rate (£ per this row's unit, this workbook's basis: Scarman Public Toilets Phase 2, HIGH specification, tender Apr 2026, median of 6 bids × 1.007 ÷ 0.94; per m² figures over the 71 m² toilet area only. Evidence only)</t>
-  </si>
-  <si>
-    <t>Co-op rate (£ per this row's unit, this workbook's basis: Co-op grocery store fit-out, Kingfisher CSA, contract Aug 2025 × 1.03 ÷ 0.94, over 885 m². Evidence only)</t>
-  </si>
-  <si>
-    <t>IBRB café rate (£ per this row's unit, this workbook's basis: IBRB café servery fit-out, Senevo winning bid 2025 × 1.035 ÷ 0.94, over 72 m² (catering kitchen per 28 m² servery). Evidence only)</t>
-  </si>
-  <si>
-    <t>Riley Court rate (£ per this row's unit, this workbook's basis: Psychology building full refurbishment, Maris signed contract CSA £9.15m, GMP Nov 2024 × 1.05 ÷ 0.94, GIFA 3,850 m². Evidence only)</t>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Average of project rates (mean of columns R–Y that hold a figure for this row. Projects differ in scope and specification, so read it with the column notes. Evidence only — the app does not read it)</t>
@@ -5298,142 +5298,142 @@
     <t>Reason for the suggestion</t>
   </si>
   <si>
-    <t>Keep. Matches Mace pre-tender allowance (£24.5); one low tender (£8) is not enough to cut it.</t>
-  </si>
-  <si>
-    <t>Lower. Whitefields £73 on simple 2-storey masonry; £100 leaves room for framed or taller buildings.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside, Claycroft, Co-op and Riley Court all £49–55. Scarman and IBRB are tiny jobs.</t>
+    <t xml:space="preserve">Keep. Matches the cost consultant pre-tender allowance (£24.5); one low tender (£8) is not enough to cut it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower. Project C £73 on simple 2-storey masonry; £100 leaves room for framed or taller buildings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A, Project D, Project F and Project H all £49–55. Project E and Project G are tiny jobs.</t>
   </si>
   <si>
     <t>Keep. One water-main job (£36); diversions are too site-specific to move the rate.</t>
   </si>
   <si>
-    <t>Raise. Computer Science £182 per m² footprint. Claycroft metal over-roof £517 is a High case.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside tender.</t>
-  </si>
-  <si>
-    <t>Raise. CS part render £48; Riley Court full envelope upgrade £171 (cladding, insulated linings).</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court new windows £147; CS triple glazing £210 (High). Co-op was refinish only.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £247 (acoustic academic partitions); Co-op £26 was a light shop fit-out.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £164, Scarman £99; Co-op £9 reused most doors.</t>
-  </si>
-  <si>
-    <t>Keep. Most projects £3–24; Claycroft £96 out-turn (surveyed occupied residential) is a High case.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £72, Claycroft £99, Riley Court £39 (decoration only). Scarman is toilet-area only.</t>
-  </si>
-  <si>
-    <t>Raise slightly. Riley Court £95 full replacement; Co-op £22 kept its floor. Scarman is toilet-area only.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £51, Claycroft £38.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £110 new suspended ceilings; Co-op £21 painted soffits only.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £30; Claycroft £70 was full replacement (High case).</t>
+    <t xml:space="preserve">Raise. Project B £182 per m² footprint. Project D metal over-roof £517 is a High case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A tender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project B part render £48; Project H full envelope upgrade £171 (cladding, insulated linings).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H new windows £147; Project B triple glazing £210 (High). Project F was refinish only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £247 (acoustic academic partitions); Project F £26 was a light shop fit-out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £164, Project E £99; Project F £9 reused most doors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Most projects £3–24; Project D £96 out-turn (surveyed occupied residential) is a High case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £72, Project D £99, Project H £39 (decoration only). Project E is toilet-area only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise slightly. Project H £95 full replacement; Project F £22 kept its floor. Project E is toilet-area only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £51, Project D £38.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £110 new suspended ceilings; Project F £21 painted soffits only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £30; Project D £70 was full replacement (High case).</t>
   </si>
   <si>
     <t>Keep as is (owner, 4 Oct 2026).</t>
   </si>
   <si>
-    <t>Keep. Lakeside £2,563; Claycroft £3,869 sits between Std and High.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside tender £5,296.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court about £10,300 per tea point (8 assumed); your own review said £5,500.</t>
-  </si>
-  <si>
-    <t>Keep. Riley Court £42, Claycroft £64, Co-op £7.</t>
-  </si>
-  <si>
-    <t>Raise slightly. Riley Court £12, Co-op £16 (incl. graphics).</t>
-  </si>
-  <si>
-    <t>Raise. IBRB café servery £1,438 (bespoke stainless) = High; your own review said Std £1,000.</t>
+    <t xml:space="preserve">Keep. Project A £2,563; Project D £3,869 sits between Std and High.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A tender £5,296.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H about £10,300 per tea point (8 assumed); your own review said £5,500.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project H £42, Project D £64, Project F £7.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise slightly. Project H £12, Project F £16 (incl. graphics).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project G café servery £1,438 (bespoke stainless) = High; your own review said Std £1,000.</t>
   </si>
   <si>
     <t>Raise. CS whole heat pump M&amp;E package £224; enter as a figure, not = 5.1a × factor.</t>
   </si>
   <si>
-    <t>Raise. Riley Court £135 incl. new LTHW pipework, radiators and pumps off district heating.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £105, IBRB £124 (small café); Claycroft £39 and Co-op £18 were partial.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £20.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court MVHR £172, Co-op £73, Claycroft out-turn £92.</t>
-  </si>
-  <si>
-    <t>Raise slightly. Lakeside £18.5, Claycroft £28; Scarman £62 is toilet-area only.</t>
-  </si>
-  <si>
-    <t>Keep. Riley Court £34 and Co-op £40 cooled only some rooms; no whole-building evidence.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £59 (full BMS budget); Co-op £11.5; Claycroft £4 interfaces only.</t>
-  </si>
-  <si>
-    <t>Keep. Riley Court £131, Scarman £97, Co-op £89. IBRB £218 is one supply on a small room.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £153, Claycroft £158.</t>
+    <t xml:space="preserve">Raise. Project H £135 incl. new LTHW pipework, radiators and pumps off district heating.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £105, Project G £124 (small café); Project D £39 and Project F £18 were partial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £20.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H MVHR £172, Project F £73, Project D out-turn £92.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise slightly. Project A £18.5, Project D £28; Project E £62 is toilet-area only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project H £34 and Project F £40 cooled only some rooms; no whole-building evidence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £59 (full BMS budget); Project F £11.5; Project D £4 interfaces only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project H £131, Project E £97, Project F £89. Project G £218 is one supply on a small room.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £153, Project D £158.</t>
   </si>
   <si>
     <t>Raise. Five projects £51–198 (median £84); £33 is far too low.</t>
   </si>
   <si>
-    <t>Raise. Riley Court £44, Claycroft £65, Scarman £77 for new systems; Lakeside £19 was partial.</t>
-  </si>
-  <si>
-    <t>Raise slightly. Lakeside £19, Riley Court £34, IBRB £5.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £24.5, Claycroft £19.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £22, Co-op £58 (retail CCTV and alarm); Claycroft £4.5 minimal.</t>
-  </si>
-  <si>
-    <t>Raise. Claycroft £112,850 for a replacement passenger lift; £40,000 is a third of that.</t>
-  </si>
-  <si>
-    <t>Lower. CS £8, Co-op £3; most builder's work sits inside the M&amp;E prices.</t>
-  </si>
-  <si>
-    <t>Keep. Lakeside £27 (rewire of occupied flats); Claycroft £11.</t>
+    <t xml:space="preserve">Raise. Project H £44, Project D £65, Project E £77 for new systems; Project A £19 was partial.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise slightly. Project A £19, Project H £34, Project G £5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £24.5, Project D £19.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £22, Project F £58 (retail CCTV and alarm); Project D £4.5 minimal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project D £112,850 for a replacement passenger lift; £40,000 is a third of that.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower. Project B £8, Project F £3; most builder's work sits inside the M&amp;E prices.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project A £27 (rewire of occupied flats); Project D £11.</t>
   </si>
   <si>
     <t>Keep. CS brick remedials £48.</t>
   </si>
   <si>
-    <t>Keep. Riley Court £54.</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £35 for new internal below-ground drainage (one project).</t>
-  </si>
-  <si>
-    <t>Raise. Riley Court £68 for new district heating and water mains (one project; site-specific).</t>
-  </si>
-  <si>
-    <t>Keep. Whitefields £2 was topsoil and seed only, not planting.</t>
+    <t xml:space="preserve">Keep. Project H £54.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £35 for new internal below-ground drainage (one project).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raise. Project H £68 for new district heating and water mains (one project; site-specific).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep. Project C £2 was topsoil and seed only, not planting.</t>
   </si>
   <si>
     <t>Base 7% — vacant, no restrictions, relaxed programme</t>
@@ -5883,7 +5883,7 @@
     <t>The client's design team does every stage.</t>
   </si>
   <si>
-    <t>The contractor's team does Stage 4. Contractor's design 2% (Claycroft, Morgan Sindall D&amp;B: 2.1%).</t>
+    <t/>
   </si>
   <si>
     <t>Stage 4 is shared with the contractor during the pre-construction stage.</t>
@@ -6232,6 +6232,81 @@
   </si>
   <si>
     <t>New build roof and external walls (owner, 12 Oct 2026). v5.12 moved each changed row's New build columns by the refurbishment evidence ratio, with no new-build evidence; roof and external walls ended up above Spon's new-build range and go back to their v5.11 rates: roof 2.5a 380/518 → 220/300 (Spon's £181–£258), external walls 2.6a 367/567 → 220/340 (Spon's £75–£338). Tested on the 30 batch-4 scenarios: residential, office and mixed-use new build come back into their expected ranges. Ceilings, lighting and fire alarm were also above Spon's but were kept: lowering them pushed healthcare, hotel, student and education projects below range. Refurb &amp; Fit-out columns unchanged; industrial has its own roof and wall rows (v5.25).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender check (column Q on '2. Rates'): cleared in v5.28. The bid-level evidence behind the calibrated rates is held offline by the owner. The per-project figures stay in columns R–Y as Projects A–H (anonymised), each in the row's unit on this workbook's basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project C rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column R on '2. Rates': Project C (demolition of low-rise residential blocks, 2026). The contract figure for that row, in the row's unit and on this workbook's basis: line items without the contractor's prelims and OH&amp;P, ÷ 0.94 West Midlands factor, × 1.014 to Q3 2026. Evidence only: the app does not read this column and no rate changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project D rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column S on '2. Rates': Project D (large occupied student-residence refurbishment, contract 2025). Sub-contract package values without the main contractor's prelims, risk, fee and design, × 1.034 to Q3 2026, ÷ 0.94 West Midlands factor, on the measured GIA. M&amp;E rows include their share (6.5%) of the M&amp;E design, prelims and testing. 2.10 fire stopping is the forecast out-turn, because the contract held only a provisional sum. Evidence only: the app does not read this column and no rate changed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns T–Y on '2. Rates' hold the other projects' figures (anonymised) in the row's unit and on this workbook's basis, beside Project C (R) and Project D (S): T Project A — occupied residential refurbishment (tender 2026, median of 4 bids); U Project B — decarbonisation refurbishment (tender 2024, mean of 2 bids); V Project E — high-specification WC refurbishment (tender 2026, median of 6 bids; per m² over the WC area only); W Project F — retail fit-out (contract 2025); X Project G — small café servery fit-out (2025; catering kitchen per m² of servery); Y Project H — full refurbishment of an academic building (contract 2024). Each excludes the contractor's prelims, OH&amp;P and design, rebased to Q3 2026 and ÷ 0.94 West Midlands. Column Z is the average of R–Y for the row. Projects differ in scope and specification, so expect spread. Not on '2. Rates': scaffold for envelope works about £33–£42 per m² GIFA; preliminaries on these projects about 5.5–18% of works, the smallest jobs highest. Evidence only: the app does not read these columns and no rate changed. Column AA is a suggested Refurb &amp; Fit-out Standard rate for each row with evidence, and AB the reason (Raise / Lower / Keep). They are suggestions for the owner only: the app does not read them, and a rate changes only when the owner edits the rate columns.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender – Project A (Sep 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From the Project A tender returns (occupied residential refurbishment, Sep 2026): median of the credible bids on this workbook's basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. Six more project columns on '2. Rates' beside Project C (R) and Project D (S), each a plain figure in the row's unit on this workbook's basis: T Project A (15 rows), U Project B (6), V Project E, high spec (12), W Project F (19), X Project G (7), Y Project H (27). Column Z averages R–Y on 47 rows. Row 24 explains the columns. Columns AA–AB: suggested Refurb &amp; Fit-out Std rate and the reason, on all 47 rows (25 raise, 2 lower, 20 keep).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. New column S on '2. Rates' (now 'Project D rate'), from a large occupied student-residence refurbishment (contract 2025), per row's unit: strip-out £51; metal over-roof £517/m² roof; fire stopping £96 (out-turn); wall finishes £99; floor finishes £38; ceilings £70; bathrooms £3,869 each; fixed joinery £64; water and drainage £39; extract £28; power £158; lighting incl. emergency £113; fire alarm £65; data £19; passenger lift £112,850; BWIC £11. Not on '2. Rates': scaffold about £33/m² GIA; main contractor's prelims about 11% of works.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. New column R on '2. Rates' (now 'Project C rate'), from a demolition contract (2026): 0.1 asbestos £8.1/m² GIFA; 0.2 demolition incl. disconnections £73/m² demolished; 0.7 service diversions £36/m² footprint; 8.10 topsoil and seed £2.1/m². Not on '2. Rates': the contractor's prelims incl. hoarding about 17% of works and OH&amp;P about 15%; about 15–16 weeks on site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence only, no rates changed. Project B (decarbonisation refurbishment) tender returns, 2024 (mean of two bids × 1.07 ÷ 0.94), added as evidence for 2.5a roof, 2.6 external walls, 2.7 windows, 5.1b air source heat pump, 5.26a builder's work and 7.1a repairs. Suggested for the owner to decide: roof Std about £300; air source heat pump full system Std about £190; a scaffold item of about £40/m² GIFA for envelope works; triple glazing about £210/m² GIFA (an option, or High).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A tender returns (occupied residential refurbishment, Sep 2026): four credible bids used (median ÷ 0.94 West Midlands factor, on the measured floor area). Changed, Refurb &amp; Fit-out columns only: strip-out £45 → £55; bathrooms £900 / £2,000 / £3,500 → £1,150 / £2,500 / £4,400; domestic kitchens £3,500 / £6,000 / £10,000 → £3,100 / £5,300 / £8,850; residential power (5.7b) £70 / £108 / £185 → £95 / £150 / £255. Added: residential rows (RES STU) for floor finishes (3.2c £50), ceilings (3.3b £30), data incl. TV aerial (5.14b £25) and builder's work (5.26b £27); options Roof — Loft insulation only (2.5b, £32/m² roof) and Ventilation — Extract fans only (5.3b, £19). Ratios: m2_per_dwelling 80 → 66, bathrooms_per_dwelling 1.2 → 1.0. New 'Tender check' column on '2. Rates' and price source 'Tender – Project A (Sep 2026)'. Confirmed and kept: wall finishes, water (visible fittings), fire alarm, data, fire stopping (Basic).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tender check (cleared in v5.28: the bid-level evidence is held offline by the owner. The per-project figures are in columns R–Y, Projects A–H)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project C rate (£ per this row's unit, this workbook's basis: demolition contract 2026, excl. the contractor's prelims and OH&amp;P, ÷ 0.94 × 1.014. Evidence only — the app does not read it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project D rate (£ per this row's unit, this workbook's basis: occupied student-residence refurbishment, contract 2025 — sub-contract packages excl. the main contractor's prelims, risk, fee and design, × 1.034 ÷ 0.94. 2.10 fire stopping is the forecast out-turn. Evidence only — the app does not read it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project A rate (£ per this row's unit, this workbook's basis: occupied residential refurbishment, tender Sep 2026, median of 4 bids ÷ 0.94. Evidence only — the app does not read it)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project B rate (£ per this row's unit, this workbook's basis: decarbonisation refurbishment, tender 2024, mean of 2 bids × 1.07 ÷ 0.94; roof per m² footprint; 5.1b is the whole M&amp;E package. Evidence only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project E rate (£ per this row's unit, this workbook's basis: high-specification WC refurbishment, tender 2026, median of 6 bids × 1.007 ÷ 0.94; per m² figures over the WC area only. Evidence only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project F rate (£ per this row's unit, this workbook's basis: retail fit-out, contract 2025 × 1.03 ÷ 0.94. Evidence only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project G rate (£ per this row's unit, this workbook's basis: small café servery fit-out, 2025 × 1.035 ÷ 0.94; catering kitchen per m² of servery. Evidence only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project H rate (£ per this row's unit, this workbook's basis: full refurbishment of an academic building, contract 2024 × 1.05 ÷ 0.94. Evidence only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The contractor's team does Stage 4. Contractor's design 2% (Project D, design and build: 2.1%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v5.28 — 16 Oct 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence columns anonymised. No rate, option, rule or formula changed.</t>
   </si>
 </sst>
 </file>
@@ -6858,7 +6933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBCD35-3C7D-4CAC-A46E-6C3CC3E31849}">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C112"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.7109375" style="8" customWidth="1"/>
@@ -7036,25 +7111,25 @@
         <v>1673</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1709</v>
+        <v>2067</v>
       </c>
       <c r="C21" s="33"/>
     </row>
     <row r="22" spans="1:3" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
-        <v>1685</v>
+        <v>2068</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1714</v>
+        <v>2069</v>
       </c>
       <c r="C22" s="33"/>
     </row>
     <row r="23" spans="1:3" ht="91.35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
-        <v>1710</v>
+        <v>2070</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1711</v>
+        <v>2071</v>
       </c>
       <c r="C23" s="33"/>
     </row>
@@ -7063,7 +7138,7 @@
         <v>1726</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>1727</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -7120,10 +7195,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
-        <v>1621</v>
+        <v>2073</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>1674</v>
+        <v>2074</v>
       </c>
       <c r="C31" s="33"/>
     </row>
@@ -7553,263 +7628,271 @@
       <c r="B80" s="16"/>
       <c r="C80" s="34"/>
     </row>
-    <row r="81" spans="1:2" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A81" s="17" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A82" s="17" t="s">
         <v>2065</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B82" s="17" t="s">
         <v>2066</v>
       </c>
     </row>
-    <row r="82" spans="1:2" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="17" t="s">
+    <row r="83" spans="1:2" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A83" s="17" t="s">
         <v>2061</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B83" s="17" t="s">
         <v>2062</v>
       </c>
     </row>
-    <row r="83" spans="1:2" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="17" t="s">
+    <row r="84" spans="1:2" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="17" t="s">
         <v>2058</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B84" s="17" t="s">
         <v>2059</v>
       </c>
     </row>
-    <row r="84" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A84" s="17" t="s">
+    <row r="85" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A85" s="17" t="s">
         <v>2017</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B85" s="17" t="s">
         <v>2018</v>
       </c>
     </row>
-    <row r="85" spans="1:2" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A85" s="17" t="s">
+    <row r="86" spans="1:2" s="54" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A86" s="17" t="s">
         <v>2012</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B86" s="17" t="s">
         <v>2013</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="17" t="s">
-        <v>2005</v>
-      </c>
-      <c r="B86" s="17" t="s">
-        <v>2006</v>
       </c>
     </row>
     <row r="87" spans="1:2" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A87" s="17" t="s">
-        <v>1992</v>
+        <v>2005</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>1993</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="88" spans="1:2" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A88" s="17" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B88" s="17" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="17" t="s">
         <v>1963</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B89" s="17" t="s">
         <v>1964</v>
       </c>
     </row>
-    <row r="89" spans="1:2" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A89" s="17" t="s">
+    <row r="90" spans="1:2" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A90" s="17" t="s">
         <v>1728</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B90" s="17" t="s">
         <v>1729</v>
       </c>
     </row>
-    <row r="90" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A90" s="17" t="s">
+    <row r="91" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A91" s="17" t="s">
         <v>1730</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B91" s="17" t="s">
         <v>1731</v>
       </c>
     </row>
-    <row r="91" spans="1:2" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
+    <row r="92" spans="1:2" s="54" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A92" s="17" t="s">
         <v>1732</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B92" s="17" t="s">
         <v>1733</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
-        <v>1734</v>
-      </c>
-      <c r="B92" s="17" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="93" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A93" s="17" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="94" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A94" s="17" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="95" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A95" s="17" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B95" s="17" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" s="54" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A96" s="17" t="s">
         <v>1740</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B96" s="17" t="s">
         <v>1741</v>
       </c>
     </row>
-    <row r="96" spans="1:2" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A96" s="17" t="s">
+    <row r="97" spans="1:2" s="54" customFormat="1" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A97" s="17" t="s">
         <v>1742</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B97" s="17" t="s">
         <v>1743</v>
       </c>
     </row>
-    <row r="97" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+    <row r="98" spans="1:3" s="54" customFormat="1" ht="63.75" x14ac:dyDescent="0.2">
+      <c r="A98" s="17" t="s">
         <v>1744</v>
       </c>
-      <c r="B97" s="17" t="s">
-        <v>1745</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="17" t="s">
+      <c r="B98" s="17" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" s="54" customFormat="1" ht="104.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="17" t="s">
         <v>1712</v>
       </c>
-      <c r="B98" s="17" t="s">
-        <v>1713</v>
-      </c>
-      <c r="C98" s="60"/>
-    </row>
-    <row r="99" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="17" t="s">
+      <c r="B99" s="17" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C99" s="60"/>
+    </row>
+    <row r="100" spans="1:3" s="54" customFormat="1" ht="89.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="17" t="s">
         <v>1686</v>
       </c>
-      <c r="B99" s="17" t="s">
-        <v>1715</v>
-      </c>
-      <c r="C99" s="60"/>
-    </row>
-    <row r="100" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A100" s="17" t="s">
+      <c r="B100" s="17" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C100" s="60"/>
+    </row>
+    <row r="101" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A101" s="17" t="s">
         <v>1677</v>
       </c>
-      <c r="B100" s="17" t="s">
-        <v>1683</v>
-      </c>
-      <c r="C100" s="60"/>
-    </row>
-    <row r="101" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A101" s="17" t="s">
+      <c r="B101" s="17" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C101" s="60"/>
+    </row>
+    <row r="102" spans="1:3" s="54" customFormat="1" ht="89.25" x14ac:dyDescent="0.2">
+      <c r="A102" s="17" t="s">
         <v>1675</v>
       </c>
-      <c r="B101" s="17" t="s">
-        <v>1676</v>
-      </c>
-      <c r="C101" s="60"/>
-    </row>
-    <row r="102" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
-      <c r="A102" s="17" t="s">
+      <c r="B102" s="17" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C102" s="60"/>
+    </row>
+    <row r="103" spans="1:3" s="54" customFormat="1" ht="76.5" x14ac:dyDescent="0.2">
+      <c r="A103" s="17" t="s">
         <v>1616</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B103" s="17" t="s">
         <v>1618</v>
       </c>
-      <c r="C102" s="60"/>
-    </row>
-    <row r="103" spans="1:3" ht="102" x14ac:dyDescent="0.2">
-      <c r="A103" s="15" t="s">
+      <c r="C103" s="60"/>
+    </row>
+    <row r="104" spans="1:3" ht="102" x14ac:dyDescent="0.2">
+      <c r="A104" s="15" t="s">
         <v>1605</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B104" s="17" t="s">
         <v>1606</v>
       </c>
-      <c r="C103" s="33"/>
-    </row>
-    <row r="104" spans="1:3" ht="51" x14ac:dyDescent="0.2">
-      <c r="A104" s="15" t="s">
+      <c r="C104" s="33"/>
+    </row>
+    <row r="105" spans="1:3" ht="51" x14ac:dyDescent="0.2">
+      <c r="A105" s="15" t="s">
         <v>1048</v>
       </c>
-      <c r="B104" s="17" t="s">
+      <c r="B105" s="17" t="s">
         <v>1049</v>
       </c>
-      <c r="C104" s="33"/>
-    </row>
-    <row r="105" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A105" s="15" t="s">
+      <c r="C105" s="33"/>
+    </row>
+    <row r="106" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A106" s="15" t="s">
         <v>1039</v>
       </c>
-      <c r="B105" s="17" t="s">
+      <c r="B106" s="17" t="s">
         <v>1040</v>
       </c>
-      <c r="C105" s="33"/>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A106" s="15" t="s">
+      <c r="C106" s="33"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B106" s="17" t="s">
+      <c r="B107" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C106" s="33"/>
-    </row>
-    <row r="107" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A107" s="15" t="s">
+      <c r="C107" s="33"/>
+    </row>
+    <row r="108" spans="1:3" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A108" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B107" s="17" t="s">
+      <c r="B108" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="33"/>
-    </row>
-    <row r="108" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A108" s="15" t="s">
+      <c r="C108" s="33"/>
+    </row>
+    <row r="109" spans="1:3" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A109" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B108" s="17" t="s">
+      <c r="B109" s="17" t="s">
         <v>28</v>
-      </c>
-      <c r="C108" s="33"/>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A109" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>30</v>
       </c>
       <c r="C109" s="33"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B110" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="33"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B110" s="17" t="s">
+      <c r="B111" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C110" s="33"/>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A111" s="15"/>
-      <c r="B111" s="17"/>
       <c r="C111" s="33"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="15"/>
+      <c r="B112" s="17"/>
+      <c r="C112" s="33"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7906,31 +7989,31 @@
         <v>1608</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>1687</v>
+        <v>2080</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>1684</v>
+        <v>2081</v>
       </c>
       <c r="S5" s="12" t="s">
-        <v>1688</v>
+        <v>2082</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>1746</v>
+        <v>2083</v>
       </c>
       <c r="U5" s="12" t="s">
-        <v>1747</v>
+        <v>2084</v>
       </c>
       <c r="V5" s="12" t="s">
-        <v>1748</v>
+        <v>2085</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>1749</v>
+        <v>2086</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>1750</v>
+        <v>2087</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>1751</v>
+        <v>2088</v>
       </c>
       <c r="Z5" s="12" t="s">
         <v>1752</v>
@@ -7999,9 +8082,7 @@
       <c r="O7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="Q7" s="22" t="s">
-        <v>1716</v>
-      </c>
+      <c r="Q7" s="22"/>
       <c r="R7" s="22">
         <v>8.1</v>
       </c>
@@ -8054,9 +8135,7 @@
       <c r="O8" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="Q8" s="22" t="s">
-        <v>1717</v>
-      </c>
+      <c r="Q8" s="22"/>
       <c r="R8" s="22">
         <v>73.3</v>
       </c>
@@ -8109,9 +8188,7 @@
       <c r="O9" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="Q9" s="22" t="s">
-        <v>1689</v>
-      </c>
+      <c r="Q9" s="22"/>
       <c r="S9" s="22">
         <v>51.4</v>
       </c>
@@ -8292,9 +8369,7 @@
       <c r="O13" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="Q13" s="22" t="s">
-        <v>1718</v>
-      </c>
+      <c r="Q13" s="22"/>
       <c r="R13" s="22">
         <v>36.299999999999997</v>
       </c>
@@ -8958,9 +9033,7 @@
       <c r="O29" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="Q29" s="22" t="s">
-        <v>1690</v>
-      </c>
+      <c r="Q29" s="22"/>
       <c r="S29" s="22">
         <v>516.9</v>
       </c>
@@ -9070,9 +9143,7 @@
         <v>1642</v>
       </c>
       <c r="P31"/>
-      <c r="Q31" s="22" t="s">
-        <v>1643</v>
-      </c>
+      <c r="Q31" s="22"/>
       <c r="T31" s="22">
         <v>32</v>
       </c>
@@ -9131,9 +9202,7 @@
       <c r="O32" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="Q32" s="22" t="s">
-        <v>1678</v>
-      </c>
+      <c r="Q32" s="22"/>
       <c r="U32" s="22">
         <v>48</v>
       </c>
@@ -9246,9 +9315,7 @@
       <c r="O34" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="Q34" s="22" t="s">
-        <v>1679</v>
-      </c>
+      <c r="Q34" s="22"/>
       <c r="U34" s="22">
         <v>210</v>
       </c>
@@ -9488,9 +9555,7 @@
       <c r="O38" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="Q38" s="22" t="s">
-        <v>1691</v>
-      </c>
+      <c r="Q38" s="22"/>
       <c r="S38" s="22">
         <v>95.8</v>
       </c>
@@ -9580,9 +9645,7 @@
       <c r="O40" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="Q40" s="22" t="s">
-        <v>1692</v>
-      </c>
+      <c r="Q40" s="22"/>
       <c r="S40" s="22">
         <v>99.3</v>
       </c>
@@ -9658,9 +9721,7 @@
       <c r="O41" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="Q41" s="22" t="s">
-        <v>1652</v>
-      </c>
+      <c r="Q41" s="22"/>
       <c r="V41" s="22">
         <v>177</v>
       </c>
@@ -9773,9 +9834,7 @@
         <v>1637</v>
       </c>
       <c r="P43"/>
-      <c r="Q43" s="22" t="s">
-        <v>1693</v>
-      </c>
+      <c r="Q43" s="22"/>
       <c r="S43" s="22">
         <v>38.4</v>
       </c>
@@ -9837,9 +9896,7 @@
       <c r="O44" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="Q44" s="22" t="s">
-        <v>1653</v>
-      </c>
+      <c r="Q44" s="22"/>
       <c r="V44" s="22">
         <v>129</v>
       </c>
@@ -9903,9 +9960,7 @@
         <v>1634</v>
       </c>
       <c r="P45"/>
-      <c r="Q45" s="22" t="s">
-        <v>1694</v>
-      </c>
+      <c r="Q45" s="22"/>
       <c r="S45" s="22">
         <v>70.400000000000006</v>
       </c>
@@ -10153,9 +10208,7 @@
       <c r="O50" s="52" t="s">
         <v>253</v>
       </c>
-      <c r="Q50" s="22" t="s">
-        <v>1695</v>
-      </c>
+      <c r="Q50" s="22"/>
       <c r="S50" s="22">
         <v>3869</v>
       </c>
@@ -10311,9 +10364,7 @@
       <c r="O53" s="52" t="s">
         <v>266</v>
       </c>
-      <c r="Q53" s="49" t="s">
-        <v>1644</v>
-      </c>
+      <c r="Q53" s="49"/>
       <c r="T53" s="22">
         <v>5296</v>
       </c>
@@ -10432,9 +10483,7 @@
       <c r="O55" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="Q55" s="22" t="s">
-        <v>1696</v>
-      </c>
+      <c r="Q55" s="22"/>
       <c r="S55" s="22">
         <v>63.7</v>
       </c>
@@ -11155,9 +11204,7 @@
       <c r="O71" s="59" t="s">
         <v>370</v>
       </c>
-      <c r="Q71" s="22" t="s">
-        <v>1680</v>
-      </c>
+      <c r="Q71" s="22"/>
       <c r="U71" s="22">
         <v>224</v>
       </c>
@@ -11876,9 +11923,7 @@
       <c r="O85" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="Q85" s="22" t="s">
-        <v>1697</v>
-      </c>
+      <c r="Q85" s="22"/>
       <c r="S85" s="22">
         <v>38.9</v>
       </c>
@@ -11949,9 +11994,7 @@
       <c r="O86" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="Q86" s="22" t="s">
-        <v>1654</v>
-      </c>
+      <c r="Q86" s="22"/>
       <c r="T86" s="22">
         <v>20</v>
       </c>
@@ -12012,9 +12055,7 @@
       <c r="O87" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="Q87" s="22" t="s">
-        <v>1698</v>
-      </c>
+      <c r="Q87" s="22"/>
       <c r="W87" s="22">
         <v>73.099999999999994</v>
       </c>
@@ -12075,9 +12116,7 @@
         <v>1630</v>
       </c>
       <c r="P88"/>
-      <c r="Q88" s="22" t="s">
-        <v>1699</v>
-      </c>
+      <c r="Q88" s="22"/>
       <c r="S88" s="22">
         <v>28.2</v>
       </c>
@@ -12203,9 +12242,7 @@
       <c r="O90" s="24" t="s">
         <v>427</v>
       </c>
-      <c r="Q90" s="22" t="s">
-        <v>1700</v>
-      </c>
+      <c r="Q90" s="22"/>
       <c r="S90" s="22">
         <v>4.3</v>
       </c>
@@ -12462,9 +12499,7 @@
       <c r="O95" s="24" t="s">
         <v>449</v>
       </c>
-      <c r="Q95" s="22" t="s">
-        <v>1701</v>
-      </c>
+      <c r="Q95" s="22"/>
       <c r="S95" s="22">
         <v>157.69999999999999</v>
       </c>
@@ -12571,9 +12606,7 @@
       <c r="O97" s="24" t="s">
         <v>454</v>
       </c>
-      <c r="Q97" s="22" t="s">
-        <v>1702</v>
-      </c>
+      <c r="Q97" s="22"/>
       <c r="S97" s="22">
         <v>113.2</v>
       </c>
@@ -12692,9 +12725,7 @@
       <c r="O99" s="24" t="s">
         <v>462</v>
       </c>
-      <c r="Q99" s="22" t="s">
-        <v>1655</v>
-      </c>
+      <c r="Q99" s="22"/>
     </row>
     <row r="100" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A100" s="23" t="s">
@@ -12976,9 +13007,7 @@
       <c r="O106" s="24" t="s">
         <v>489</v>
       </c>
-      <c r="Q106" s="22" t="s">
-        <v>1703</v>
-      </c>
+      <c r="Q106" s="22"/>
       <c r="S106" s="22">
         <v>64.7</v>
       </c>
@@ -13135,9 +13164,7 @@
       <c r="O109" s="24" t="s">
         <v>510</v>
       </c>
-      <c r="Q109" s="22" t="s">
-        <v>1656</v>
-      </c>
+      <c r="Q109" s="22"/>
       <c r="T109" s="22">
         <v>19.399999999999999</v>
       </c>
@@ -13201,9 +13228,7 @@
         <v>1625</v>
       </c>
       <c r="P110"/>
-      <c r="Q110" s="22" t="s">
-        <v>1704</v>
-      </c>
+      <c r="Q110" s="22"/>
       <c r="S110" s="22">
         <v>19.3</v>
       </c>
@@ -13265,9 +13290,7 @@
       <c r="O111" s="24" t="s">
         <v>517</v>
       </c>
-      <c r="Q111" s="22" t="s">
-        <v>1705</v>
-      </c>
+      <c r="Q111" s="22"/>
       <c r="S111" s="22">
         <v>4.5</v>
       </c>
@@ -13334,9 +13357,7 @@
       <c r="O112" s="24" t="s">
         <v>522</v>
       </c>
-      <c r="Q112" s="22" t="s">
-        <v>1706</v>
-      </c>
+      <c r="Q112" s="22"/>
       <c r="S112" s="22">
         <v>112847</v>
       </c>
@@ -14084,9 +14105,7 @@
       <c r="O130" s="24" t="s">
         <v>727</v>
       </c>
-      <c r="Q130" s="22" t="s">
-        <v>1681</v>
-      </c>
+      <c r="Q130" s="22"/>
       <c r="U130" s="22">
         <v>8</v>
       </c>
@@ -14145,9 +14164,7 @@
         <v>1622</v>
       </c>
       <c r="P131"/>
-      <c r="Q131" s="22" t="s">
-        <v>1707</v>
-      </c>
+      <c r="Q131" s="22"/>
       <c r="S131" s="22">
         <v>11</v>
       </c>
@@ -14228,9 +14245,7 @@
       <c r="O133" s="24" t="s">
         <v>606</v>
       </c>
-      <c r="Q133" s="22" t="s">
-        <v>1682</v>
-      </c>
+      <c r="Q133" s="22"/>
       <c r="U133" s="22">
         <v>48</v>
       </c>
@@ -14344,9 +14359,7 @@
       <c r="O135" s="24" t="s">
         <v>618</v>
       </c>
-      <c r="Q135" s="22" t="s">
-        <v>1708</v>
-      </c>
+      <c r="Q135" s="22"/>
     </row>
     <row r="136" spans="1:28" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A136" s="21" t="s">
@@ -15083,9 +15096,7 @@
       <c r="O152" s="24" t="s">
         <v>689</v>
       </c>
-      <c r="Q152" s="22" t="s">
-        <v>1719</v>
-      </c>
+      <c r="Q152" s="22"/>
       <c r="R152" s="22">
         <v>2.1</v>
       </c>
@@ -15363,9 +15374,7 @@
       <c r="O158" s="24" t="s">
         <v>715</v>
       </c>
-      <c r="Q158" s="22" t="s">
-        <v>1657</v>
-      </c>
+      <c r="Q158" s="22"/>
     </row>
     <row r="159" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A159" s="21" t="s">
@@ -15416,7 +15425,7 @@
   <autoFilter ref="A5:O159" xr:uid="{61613224-FE41-4C03-8B46-4109509C3076}"/>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" sqref="M6:M159" xr:uid="{793A7B5B-A444-437A-BF69-7D12AB43CAD4}">
-      <formula1>"Your figure,Spon's-based (approved),Kept after Spon's check,Older workbook (v4.5),Unverified †,Tender – Lakeside S&amp;F (Sep 2026)"</formula1>
+      <formula1>"Your figure,Spon's-based (approved),Kept after Spon's check,Older workbook (v4.5),Unverified †,Tender – Project A (Sep 2026)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15476,7 +15485,7 @@
         <v>740</v>
       </c>
       <c r="B6" s="61">
-        <v>5.27</v>
+        <v>5.28</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>741</v>
@@ -15487,7 +15496,7 @@
         <v>742</v>
       </c>
       <c r="B7" s="62">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="C7" s="2"/>
     </row>
@@ -19793,7 +19802,7 @@
         <v>2</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>1950</v>
+        <v>2089</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">

--- a/NRM1_Cost_Estimate_Tool_v5_2.xlsx
+++ b/NRM1_Cost_Estimate_Tool_v5_2.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nabil\estates-ai-tool\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34D8564-CBDA-4FC5-ADDE-F5C9F9BFC5E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -2268,7 +2263,7 @@
     <t>Owner</t>
   </si>
   <si>
-    <t>Nabil Kayali</t>
+    <t>Projento</t>
   </si>
   <si>
     <t>▶ building_uses</t>
@@ -4608,7 +4603,7 @@
     <t>Q1.2 options. The rate column read for each specification level. The Code is what '2. Rates' and '4. Scope rules' uses</t>
   </si>
   <si>
-    <t>Prices and scope of works for Projento, in four sheets. Prepared by Nabil Kayali.</t>
+    <t>Prices and scope of works for Projento, in four sheets. Prepared by Projento.</t>
   </si>
   <si>
     <t>THE FOUR SHEETS</t>
